--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAA9284-9768-9447-AFF4-77AE8C542A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C1D50-9114-9D4B-BDF9-9EDA1CE2B0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14260" yWindow="700" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="42">
   <si>
     <t>總計</t>
   </si>
@@ -213,6 +213,13 @@
   </si>
   <si>
     <t>02/22~02/28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W10</t>
+  </si>
+  <si>
+    <t>0301-0307</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1057,7 +1064,11 @@
       <c r="BM1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="BU1" s="26"/>
+      <c r="BU1" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="BV1" s="26"/>
+      <c r="BX1" s="25"/>
       <c r="CC1" s="26"/>
       <c r="CK1" s="26"/>
       <c r="CS1" s="26"/>
@@ -1117,6 +1128,9 @@
       <c r="BQ2" s="21"/>
       <c r="BR2" s="21"/>
       <c r="BS2" s="21"/>
+      <c r="BU2" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="BV2" s="21"/>
       <c r="BX2" s="21"/>
       <c r="BY2" s="21"/>
@@ -1235,7 +1249,9 @@
       <c r="BQ4" s="16"/>
       <c r="BR4" s="16"/>
       <c r="BS4" s="16"/>
-      <c r="BU4" s="19"/>
+      <c r="BU4" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="BV4" s="19"/>
       <c r="BW4" s="18"/>
       <c r="BX4" s="17"/>
@@ -1463,13 +1479,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BT5" s="38"/>
-      <c r="BU5" s="14"/>
-      <c r="BV5" s="32"/>
-      <c r="BW5" s="15"/>
+      <c r="BU5" s="14">
+        <v>75</v>
+      </c>
+      <c r="BV5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="BW5" s="15">
+        <v>5435</v>
+      </c>
       <c r="BX5" s="33"/>
-      <c r="BY5" s="10"/>
-      <c r="BZ5" s="12"/>
-      <c r="CA5" s="11"/>
+      <c r="BY5" s="10">
+        <f t="shared" ref="BY5:BY36" si="20">BW5-BO5</f>
+        <v>-1955</v>
+      </c>
+      <c r="BZ5" s="12">
+        <f t="shared" ref="BZ5:BZ65" si="21">BX5-BP5</f>
+        <v>0</v>
+      </c>
+      <c r="CA5" s="11" t="e">
+        <f t="shared" ref="CA5:CA65" si="22">(BX5-BP5)/BP5</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CB5" s="38"/>
       <c r="CC5" s="14"/>
       <c r="CD5" s="32"/>
@@ -1667,11 +1698,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU6" s="14"/>
-      <c r="BV6" s="32"/>
+      <c r="BV6" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW6" s="15">
+        <v>13</v>
+      </c>
       <c r="BX6" s="33"/>
-      <c r="BY6" s="10"/>
-      <c r="BZ6" s="12"/>
-      <c r="CA6" s="11"/>
+      <c r="BY6" s="10">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="BZ6" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA6" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC6" s="14"/>
       <c r="CD6" s="32"/>
       <c r="CF6" s="33"/>
@@ -1881,10 +1926,27 @@
         <v>-0.27316272233810168</v>
       </c>
       <c r="BU7" s="14"/>
-      <c r="BV7" s="13"/>
-      <c r="BX7" s="12"/>
-      <c r="BZ7" s="12"/>
-      <c r="CA7" s="11"/>
+      <c r="BV7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW7" s="10">
+        <v>192</v>
+      </c>
+      <c r="BX7" s="12">
+        <v>227552.38095164995</v>
+      </c>
+      <c r="BY7" s="10">
+        <f t="shared" si="20"/>
+        <v>-86</v>
+      </c>
+      <c r="BZ7" s="12">
+        <f t="shared" si="21"/>
+        <v>-57867.619047510001</v>
+      </c>
+      <c r="CA7" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.20274549452624313</v>
+      </c>
       <c r="CC7" s="14"/>
       <c r="CD7" s="13"/>
       <c r="CF7" s="12"/>
@@ -2091,10 +2153,27 @@
         <v>7.6898623054787755E-3</v>
       </c>
       <c r="BU8" s="14"/>
-      <c r="BV8" s="13"/>
-      <c r="BX8" s="12"/>
-      <c r="BZ8" s="12"/>
-      <c r="CA8" s="11"/>
+      <c r="BV8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW8" s="10">
+        <v>251</v>
+      </c>
+      <c r="BX8" s="12">
+        <v>308536.19047602999</v>
+      </c>
+      <c r="BY8" s="10">
+        <f t="shared" si="20"/>
+        <v>-121</v>
+      </c>
+      <c r="BZ8" s="12">
+        <f t="shared" si="21"/>
+        <v>-153353.33333329996</v>
+      </c>
+      <c r="CA8" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.33201301486241308</v>
+      </c>
       <c r="CC8" s="14"/>
       <c r="CD8" s="13"/>
       <c r="CF8" s="12"/>
@@ -2301,10 +2380,27 @@
         <v>-0.25372116379116078</v>
       </c>
       <c r="BU9" s="14"/>
-      <c r="BV9" s="13"/>
-      <c r="BX9" s="12"/>
-      <c r="BZ9" s="12"/>
-      <c r="CA9" s="11"/>
+      <c r="BV9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW9" s="10">
+        <v>73</v>
+      </c>
+      <c r="BX9" s="12">
+        <v>487876.19047616998</v>
+      </c>
+      <c r="BY9" s="10">
+        <f t="shared" si="20"/>
+        <v>-41</v>
+      </c>
+      <c r="BZ9" s="12">
+        <f t="shared" si="21"/>
+        <v>-270775.23809522</v>
+      </c>
+      <c r="CA9" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.35691653359845976</v>
+      </c>
       <c r="CC9" s="14"/>
       <c r="CD9" s="13"/>
       <c r="CF9" s="12"/>
@@ -2511,10 +2607,27 @@
         <v>-0.23270361180381943</v>
       </c>
       <c r="BU10" s="14"/>
-      <c r="BV10" s="13"/>
-      <c r="BX10" s="12"/>
-      <c r="BZ10" s="12"/>
-      <c r="CA10" s="11"/>
+      <c r="BV10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW10" s="10">
+        <v>36</v>
+      </c>
+      <c r="BX10" s="12">
+        <v>459904.76190469001</v>
+      </c>
+      <c r="BY10" s="10">
+        <f t="shared" si="20"/>
+        <v>-26</v>
+      </c>
+      <c r="BZ10" s="12">
+        <f t="shared" si="21"/>
+        <v>-487522.85714281996</v>
+      </c>
+      <c r="CA10" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.51457530616739655</v>
+      </c>
       <c r="CC10" s="14"/>
       <c r="CD10" s="13"/>
       <c r="CF10" s="12"/>
@@ -2706,10 +2819,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU11" s="14"/>
-      <c r="BV11" s="13"/>
+      <c r="BV11" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="BX11" s="12"/>
-      <c r="BZ11" s="12"/>
-      <c r="CA11" s="11"/>
+      <c r="BY11" s="10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA11" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC11" s="14"/>
       <c r="CD11" s="13"/>
       <c r="CF11" s="12"/>
@@ -2916,10 +3041,27 @@
         <v>-0.23439211391018619</v>
       </c>
       <c r="BU12" s="14"/>
-      <c r="BV12" s="13"/>
-      <c r="BX12" s="12"/>
-      <c r="BZ12" s="12"/>
-      <c r="CA12" s="11"/>
+      <c r="BV12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW12" s="10">
+        <v>8</v>
+      </c>
+      <c r="BX12" s="12">
+        <v>39020</v>
+      </c>
+      <c r="BY12" s="10">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="BZ12" s="12">
+        <f t="shared" si="21"/>
+        <v>-2920</v>
+      </c>
+      <c r="CA12" s="11">
+        <f t="shared" si="22"/>
+        <v>-6.9623271340009535E-2</v>
+      </c>
       <c r="CC12" s="14"/>
       <c r="CD12" s="13"/>
       <c r="CF12" s="12"/>
@@ -3126,10 +3268,27 @@
         <v>0.47106204120936085</v>
       </c>
       <c r="BU13" s="14"/>
-      <c r="BV13" s="13"/>
-      <c r="BX13" s="12"/>
-      <c r="BZ13" s="12"/>
-      <c r="CA13" s="11"/>
+      <c r="BV13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BW13" s="10">
+        <v>19</v>
+      </c>
+      <c r="BX13" s="12">
+        <v>590671.42857137998</v>
+      </c>
+      <c r="BY13" s="10">
+        <f t="shared" si="20"/>
+        <v>-9</v>
+      </c>
+      <c r="BZ13" s="12">
+        <f t="shared" si="21"/>
+        <v>-704290.47619042988</v>
+      </c>
+      <c r="CA13" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.54386964867508925</v>
+      </c>
       <c r="CC13" s="14"/>
       <c r="CD13" s="13"/>
       <c r="CF13" s="12"/>
@@ -3336,10 +3495,27 @@
         <v>9.5011876484390537E-3</v>
       </c>
       <c r="BU14" s="14"/>
-      <c r="BV14" s="13"/>
-      <c r="BX14" s="12"/>
-      <c r="BZ14" s="12"/>
-      <c r="CA14" s="11"/>
+      <c r="BV14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BW14" s="10">
+        <v>45</v>
+      </c>
+      <c r="BX14" s="12">
+        <v>809714.28571423003</v>
+      </c>
+      <c r="BY14" s="10">
+        <f t="shared" si="20"/>
+        <v>-20</v>
+      </c>
+      <c r="BZ14" s="12">
+        <f t="shared" si="21"/>
+        <v>-647428.57142851036</v>
+      </c>
+      <c r="CA14" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.44431372549018977</v>
+      </c>
       <c r="CC14" s="14"/>
       <c r="CD14" s="13"/>
       <c r="CF14" s="12"/>
@@ -3546,10 +3722,27 @@
         <v>-0.39926865046477711</v>
       </c>
       <c r="BU15" s="14"/>
-      <c r="BV15" s="13"/>
-      <c r="BX15" s="12"/>
-      <c r="BZ15" s="12"/>
-      <c r="CA15" s="11"/>
+      <c r="BV15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW15" s="10">
+        <v>65</v>
+      </c>
+      <c r="BX15" s="12">
+        <v>2409999.99999996</v>
+      </c>
+      <c r="BY15" s="10">
+        <f t="shared" si="20"/>
+        <v>-36</v>
+      </c>
+      <c r="BZ15" s="12">
+        <f t="shared" si="21"/>
+        <v>-1099025.7142857104</v>
+      </c>
+      <c r="CA15" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.31319967528634601</v>
+      </c>
       <c r="CC15" s="14"/>
       <c r="CD15" s="13"/>
       <c r="CF15" s="12"/>
@@ -3756,13 +3949,28 @@
         <f t="shared" si="19"/>
         <v>-0.22660794204027213</v>
       </c>
-      <c r="BU16" s="9"/>
+      <c r="BU16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="BV16" s="9"/>
-      <c r="BW16" s="8"/>
-      <c r="BX16" s="7"/>
-      <c r="BY16" s="27"/>
-      <c r="BZ16" s="28"/>
-      <c r="CA16" s="29"/>
+      <c r="BW16" s="8">
+        <v>689</v>
+      </c>
+      <c r="BX16" s="7">
+        <v>5333275.23809411</v>
+      </c>
+      <c r="BY16" s="27">
+        <f t="shared" si="20"/>
+        <v>-337</v>
+      </c>
+      <c r="BZ16" s="28">
+        <f t="shared" si="21"/>
+        <v>-3423183.8095235005</v>
+      </c>
+      <c r="CA16" s="29">
+        <f t="shared" si="22"/>
+        <v>-0.39093242952524898</v>
+      </c>
       <c r="CC16" s="9"/>
       <c r="CD16" s="9"/>
       <c r="CE16" s="8"/>
@@ -3974,13 +4182,28 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BU17" s="14"/>
-      <c r="BV17" s="32"/>
-      <c r="BW17" s="15"/>
+      <c r="BU17" s="14">
+        <v>76</v>
+      </c>
+      <c r="BV17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="BW17" s="15">
+        <v>4024</v>
+      </c>
       <c r="BX17" s="33"/>
-      <c r="BY17" s="10"/>
-      <c r="BZ17" s="12"/>
-      <c r="CA17" s="11"/>
+      <c r="BY17" s="10">
+        <f t="shared" si="20"/>
+        <v>-959</v>
+      </c>
+      <c r="BZ17" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA17" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC17" s="14"/>
       <c r="CD17" s="32"/>
       <c r="CE17" s="15"/>
@@ -4175,12 +4398,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU18" s="14"/>
-      <c r="BV18" s="32"/>
-      <c r="BW18" s="15"/>
+      <c r="BV18" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW18" s="15">
+        <v>5</v>
+      </c>
       <c r="BX18" s="33"/>
-      <c r="BY18" s="10"/>
-      <c r="BZ18" s="12"/>
-      <c r="CA18" s="11"/>
+      <c r="BY18" s="10">
+        <f t="shared" si="20"/>
+        <v>-5</v>
+      </c>
+      <c r="BZ18" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA18" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC18" s="14"/>
       <c r="CD18" s="32"/>
       <c r="CE18" s="15"/>
@@ -4393,10 +4629,27 @@
         <v>-0.40229982991138469</v>
       </c>
       <c r="BU19" s="14"/>
-      <c r="BV19" s="13"/>
-      <c r="BX19" s="12"/>
-      <c r="BZ19" s="12"/>
-      <c r="CA19" s="11"/>
+      <c r="BV19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW19" s="10">
+        <v>120</v>
+      </c>
+      <c r="BX19" s="12">
+        <v>117983.80952329002</v>
+      </c>
+      <c r="BY19" s="10">
+        <f t="shared" si="20"/>
+        <v>-68</v>
+      </c>
+      <c r="BZ19" s="12">
+        <f t="shared" si="21"/>
+        <v>-62403.809523599892</v>
+      </c>
+      <c r="CA19" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.34594286378034994</v>
+      </c>
       <c r="CC19" s="14"/>
       <c r="CD19" s="13"/>
       <c r="CF19" s="12"/>
@@ -4603,10 +4856,27 @@
         <v>-0.10915594739108885</v>
       </c>
       <c r="BU20" s="14"/>
-      <c r="BV20" s="13"/>
-      <c r="BX20" s="12"/>
-      <c r="BZ20" s="12"/>
-      <c r="CA20" s="11"/>
+      <c r="BV20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW20" s="10">
+        <v>211</v>
+      </c>
+      <c r="BX20" s="12">
+        <v>205681.90476174001</v>
+      </c>
+      <c r="BY20" s="10">
+        <f t="shared" si="20"/>
+        <v>-35</v>
+      </c>
+      <c r="BZ20" s="12">
+        <f t="shared" si="21"/>
+        <v>-52608.571428639989</v>
+      </c>
+      <c r="CA20" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.203679873159022</v>
+      </c>
       <c r="CC20" s="14"/>
       <c r="CD20" s="13"/>
       <c r="CF20" s="12"/>
@@ -4813,10 +5083,27 @@
         <v>-0.31753840506358594</v>
       </c>
       <c r="BU21" s="14"/>
-      <c r="BV21" s="13"/>
-      <c r="BX21" s="12"/>
-      <c r="BZ21" s="12"/>
-      <c r="CA21" s="11"/>
+      <c r="BV21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW21" s="10">
+        <v>60</v>
+      </c>
+      <c r="BX21" s="12">
+        <v>438952.38095237</v>
+      </c>
+      <c r="BY21" s="10">
+        <f t="shared" si="20"/>
+        <v>-9</v>
+      </c>
+      <c r="BZ21" s="12">
+        <f t="shared" si="21"/>
+        <v>-28485.7142857</v>
+      </c>
+      <c r="CA21" s="11">
+        <f t="shared" si="22"/>
+        <v>-6.0940078645477097E-2</v>
+      </c>
       <c r="CC21" s="14"/>
       <c r="CD21" s="13"/>
       <c r="CF21" s="12"/>
@@ -5023,10 +5310,27 @@
         <v>0.14891696750902086</v>
       </c>
       <c r="BU22" s="14"/>
-      <c r="BV22" s="13"/>
-      <c r="BX22" s="12"/>
-      <c r="BZ22" s="12"/>
-      <c r="CA22" s="11"/>
+      <c r="BV22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW22" s="10">
+        <v>38</v>
+      </c>
+      <c r="BX22" s="12">
+        <v>432095.23809518002</v>
+      </c>
+      <c r="BY22" s="10">
+        <f t="shared" si="20"/>
+        <v>-14</v>
+      </c>
+      <c r="BZ22" s="12">
+        <f t="shared" si="21"/>
+        <v>-295333.33333329996</v>
+      </c>
+      <c r="CA22" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.40599633411888447</v>
+      </c>
       <c r="CC22" s="14"/>
       <c r="CD22" s="13"/>
       <c r="CF22" s="12"/>
@@ -5228,10 +5532,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU23" s="14"/>
-      <c r="BV23" s="13"/>
+      <c r="BV23" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="BX23" s="12"/>
-      <c r="BZ23" s="12"/>
-      <c r="CA23" s="11"/>
+      <c r="BY23" s="10">
+        <f t="shared" si="20"/>
+        <v>-1</v>
+      </c>
+      <c r="BZ23" s="12">
+        <f t="shared" si="21"/>
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="CA23" s="11">
+        <f t="shared" si="22"/>
+        <v>-1</v>
+      </c>
       <c r="CC23" s="14"/>
       <c r="CD23" s="13"/>
       <c r="CF23" s="12"/>
@@ -5438,10 +5754,27 @@
         <v>-0.30938878386893509</v>
       </c>
       <c r="BU24" s="14"/>
-      <c r="BV24" s="13"/>
-      <c r="BX24" s="12"/>
-      <c r="BZ24" s="12"/>
-      <c r="CA24" s="11"/>
+      <c r="BV24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW24" s="10">
+        <v>8</v>
+      </c>
+      <c r="BX24" s="12">
+        <v>45620</v>
+      </c>
+      <c r="BY24" s="10">
+        <f t="shared" si="20"/>
+        <v>-2</v>
+      </c>
+      <c r="BZ24" s="12">
+        <f t="shared" si="21"/>
+        <v>-9180</v>
+      </c>
+      <c r="CA24" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.16751824817518249</v>
+      </c>
       <c r="CC24" s="14"/>
       <c r="CD24" s="13"/>
       <c r="CF24" s="12"/>
@@ -5648,10 +5981,27 @@
         <v>-7.3246864310158602E-2</v>
       </c>
       <c r="BU25" s="14"/>
-      <c r="BV25" s="13"/>
-      <c r="BX25" s="12"/>
-      <c r="BZ25" s="12"/>
-      <c r="CA25" s="11"/>
+      <c r="BV25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BW25" s="10">
+        <v>5</v>
+      </c>
+      <c r="BX25" s="12">
+        <v>183142.85714283001</v>
+      </c>
+      <c r="BY25" s="10">
+        <f t="shared" si="20"/>
+        <v>-2</v>
+      </c>
+      <c r="BZ25" s="12">
+        <f t="shared" si="21"/>
+        <v>-126480.95238095001</v>
+      </c>
+      <c r="CA25" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.40849879269777506</v>
+      </c>
       <c r="CC25" s="14"/>
       <c r="CD25" s="13"/>
       <c r="CF25" s="12"/>
@@ -5858,10 +6208,27 @@
         <v>-0.15274712510163477</v>
       </c>
       <c r="BU26" s="14"/>
-      <c r="BV26" s="13"/>
-      <c r="BX26" s="12"/>
-      <c r="BZ26" s="12"/>
-      <c r="CA26" s="11"/>
+      <c r="BV26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BW26" s="10">
+        <v>24</v>
+      </c>
+      <c r="BX26" s="12">
+        <v>391142.85714281001</v>
+      </c>
+      <c r="BY26" s="10">
+        <f t="shared" si="20"/>
+        <v>-17</v>
+      </c>
+      <c r="BZ26" s="12">
+        <f t="shared" si="21"/>
+        <v>-303523.80952378991</v>
+      </c>
+      <c r="CA26" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.43693446668496028</v>
+      </c>
       <c r="CC26" s="14"/>
       <c r="CD26" s="13"/>
       <c r="CF26" s="12"/>
@@ -6068,10 +6435,27 @@
         <v>-0.50023044629872815</v>
       </c>
       <c r="BU27" s="14"/>
-      <c r="BV27" s="13"/>
-      <c r="BX27" s="12"/>
-      <c r="BZ27" s="12"/>
-      <c r="CA27" s="11"/>
+      <c r="BV27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW27" s="10">
+        <v>19</v>
+      </c>
+      <c r="BX27" s="12">
+        <v>661047.61904760008</v>
+      </c>
+      <c r="BY27" s="10">
+        <f t="shared" si="20"/>
+        <v>-29</v>
+      </c>
+      <c r="BZ27" s="12">
+        <f t="shared" si="21"/>
+        <v>-840520.95238092984</v>
+      </c>
+      <c r="CA27" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.55976195051904498</v>
+      </c>
       <c r="CC27" s="14"/>
       <c r="CD27" s="13"/>
       <c r="CF27" s="12"/>
@@ -6278,13 +6662,28 @@
         <f t="shared" si="19"/>
         <v>-0.3163182338597369</v>
       </c>
-      <c r="BU28" s="9"/>
+      <c r="BU28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="BV28" s="9"/>
-      <c r="BW28" s="8"/>
-      <c r="BX28" s="7"/>
-      <c r="BY28" s="27"/>
-      <c r="BZ28" s="28"/>
-      <c r="CA28" s="29"/>
+      <c r="BW28" s="8">
+        <v>485</v>
+      </c>
+      <c r="BX28" s="7">
+        <v>2475666.6666658204</v>
+      </c>
+      <c r="BY28" s="27">
+        <f t="shared" si="20"/>
+        <v>-177</v>
+      </c>
+      <c r="BZ28" s="28">
+        <f t="shared" si="21"/>
+        <v>-1727394.2857140489</v>
+      </c>
+      <c r="CA28" s="29">
+        <f t="shared" si="22"/>
+        <v>-0.41098482874390835</v>
+      </c>
       <c r="CC28" s="9"/>
       <c r="CD28" s="9"/>
       <c r="CE28" s="8"/>
@@ -6496,13 +6895,28 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BU29" s="14"/>
-      <c r="BV29" s="32"/>
-      <c r="BW29" s="15"/>
+      <c r="BU29" s="14">
+        <v>77</v>
+      </c>
+      <c r="BV29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="BW29" s="15">
+        <v>2748</v>
+      </c>
       <c r="BX29" s="33"/>
-      <c r="BY29" s="10"/>
-      <c r="BZ29" s="12"/>
-      <c r="CA29" s="11"/>
+      <c r="BY29" s="10">
+        <f t="shared" si="20"/>
+        <v>-1935</v>
+      </c>
+      <c r="BZ29" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA29" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC29" s="14"/>
       <c r="CD29" s="32"/>
       <c r="CE29" s="15"/>
@@ -6697,12 +7111,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU30" s="14"/>
-      <c r="BV30" s="32"/>
-      <c r="BW30" s="15"/>
+      <c r="BV30" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW30" s="15">
+        <v>1</v>
+      </c>
       <c r="BX30" s="33"/>
-      <c r="BY30" s="10"/>
-      <c r="BZ30" s="12"/>
-      <c r="CA30" s="11"/>
+      <c r="BY30" s="10">
+        <f t="shared" si="20"/>
+        <v>-2</v>
+      </c>
+      <c r="BZ30" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA30" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC30" s="14"/>
       <c r="CD30" s="32"/>
       <c r="CE30" s="15"/>
@@ -6915,10 +7342,27 @@
         <v>-0.69061918262377398</v>
       </c>
       <c r="BU31" s="14"/>
-      <c r="BV31" s="13"/>
-      <c r="BX31" s="12"/>
-      <c r="BZ31" s="12"/>
-      <c r="CA31" s="11"/>
+      <c r="BV31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW31" s="10">
+        <v>101</v>
+      </c>
+      <c r="BX31" s="12">
+        <v>103318.09523764004</v>
+      </c>
+      <c r="BY31" s="10">
+        <f t="shared" si="20"/>
+        <v>15</v>
+      </c>
+      <c r="BZ31" s="12">
+        <f t="shared" si="21"/>
+        <v>13731.428571340031</v>
+      </c>
+      <c r="CA31" s="11">
+        <f t="shared" si="22"/>
+        <v>0.15327535985335874</v>
+      </c>
       <c r="CC31" s="14"/>
       <c r="CD31" s="13"/>
       <c r="CF31" s="12"/>
@@ -7125,10 +7569,27 @@
         <v>-0.46647913093212878</v>
       </c>
       <c r="BU32" s="14"/>
-      <c r="BV32" s="13"/>
-      <c r="BX32" s="12"/>
-      <c r="BZ32" s="12"/>
-      <c r="CA32" s="11"/>
+      <c r="BV32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW32" s="10">
+        <v>77</v>
+      </c>
+      <c r="BX32" s="12">
+        <v>83135.238095119988</v>
+      </c>
+      <c r="BY32" s="10">
+        <f t="shared" si="20"/>
+        <v>-50</v>
+      </c>
+      <c r="BZ32" s="12">
+        <f t="shared" si="21"/>
+        <v>-27951.428571450029</v>
+      </c>
+      <c r="CA32" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.25161821315016214</v>
+      </c>
       <c r="CC32" s="14"/>
       <c r="CD32" s="13"/>
       <c r="CF32" s="12"/>
@@ -7335,10 +7796,27 @@
         <v>-0.74130275582027172</v>
       </c>
       <c r="BU33" s="14"/>
-      <c r="BV33" s="13"/>
-      <c r="BX33" s="12"/>
-      <c r="BZ33" s="12"/>
-      <c r="CA33" s="11"/>
+      <c r="BV33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW33" s="10">
+        <v>30</v>
+      </c>
+      <c r="BX33" s="12">
+        <v>209238.09523807</v>
+      </c>
+      <c r="BY33" s="10">
+        <f t="shared" si="20"/>
+        <v>13</v>
+      </c>
+      <c r="BZ33" s="12">
+        <f t="shared" si="21"/>
+        <v>107971.42857141</v>
+      </c>
+      <c r="CA33" s="11">
+        <f t="shared" si="22"/>
+        <v>1.0662089720679766</v>
+      </c>
       <c r="CC33" s="14"/>
       <c r="CD33" s="13"/>
       <c r="CF33" s="12"/>
@@ -7545,10 +8023,27 @@
         <v>-0.88106872199585995</v>
       </c>
       <c r="BU34" s="14"/>
-      <c r="BV34" s="13"/>
-      <c r="BX34" s="12"/>
-      <c r="BZ34" s="12"/>
-      <c r="CA34" s="11"/>
+      <c r="BV34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW34" s="10">
+        <v>19</v>
+      </c>
+      <c r="BX34" s="12">
+        <v>237714.28571423003</v>
+      </c>
+      <c r="BY34" s="10">
+        <f t="shared" si="20"/>
+        <v>16</v>
+      </c>
+      <c r="BZ34" s="12">
+        <f t="shared" si="21"/>
+        <v>200857.14285710003</v>
+      </c>
+      <c r="CA34" s="11">
+        <f t="shared" si="22"/>
+        <v>5.4496124031015132</v>
+      </c>
       <c r="CC34" s="14"/>
       <c r="CD34" s="13"/>
       <c r="CF34" s="12"/>
@@ -7740,10 +8235,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU35" s="14"/>
-      <c r="BV35" s="13"/>
+      <c r="BV35" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="BX35" s="12"/>
-      <c r="BZ35" s="12"/>
-      <c r="CA35" s="11"/>
+      <c r="BY35" s="10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="BZ35" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA35" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC35" s="14"/>
       <c r="CD35" s="13"/>
       <c r="CF35" s="12"/>
@@ -7940,10 +8447,27 @@
         <v>-1</v>
       </c>
       <c r="BU36" s="14"/>
-      <c r="BV36" s="13"/>
-      <c r="BX36" s="12"/>
-      <c r="BZ36" s="12"/>
-      <c r="CA36" s="11"/>
+      <c r="BV36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW36" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX36" s="12">
+        <v>8414.2857142800003</v>
+      </c>
+      <c r="BY36" s="10">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
+      <c r="BZ36" s="12">
+        <f t="shared" si="21"/>
+        <v>8414.2857142800003</v>
+      </c>
+      <c r="CA36" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC36" s="14"/>
       <c r="CD36" s="13"/>
       <c r="CF36" s="12"/>
@@ -8145,10 +8669,27 @@
         <v>-1</v>
       </c>
       <c r="BU37" s="14"/>
-      <c r="BV37" s="13"/>
-      <c r="BX37" s="12"/>
-      <c r="BZ37" s="12"/>
-      <c r="CA37" s="11"/>
+      <c r="BV37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BW37" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX37" s="12">
+        <v>26147.619047609998</v>
+      </c>
+      <c r="BY37" s="10">
+        <f t="shared" ref="BY37:BY65" si="23">BW37-BO37</f>
+        <v>1</v>
+      </c>
+      <c r="BZ37" s="12">
+        <f t="shared" si="21"/>
+        <v>26147.619047609998</v>
+      </c>
+      <c r="CA37" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC37" s="14"/>
       <c r="CD37" s="13"/>
       <c r="CF37" s="12"/>
@@ -8355,10 +8896,27 @@
         <v>-0.65568436038236833</v>
       </c>
       <c r="BU38" s="14"/>
-      <c r="BV38" s="13"/>
-      <c r="BX38" s="12"/>
-      <c r="BZ38" s="12"/>
-      <c r="CA38" s="11"/>
+      <c r="BV38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BW38" s="10">
+        <v>9</v>
+      </c>
+      <c r="BX38" s="12">
+        <v>154190.47619044999</v>
+      </c>
+      <c r="BY38" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="BZ38" s="12">
+        <f t="shared" si="21"/>
+        <v>-7047.6190476200136</v>
+      </c>
+      <c r="CA38" s="11">
+        <f t="shared" si="22"/>
+        <v>-4.3709391612534981E-2</v>
+      </c>
       <c r="CC38" s="14"/>
       <c r="CD38" s="13"/>
       <c r="CF38" s="12"/>
@@ -8565,10 +9123,27 @@
         <v>-0.86873362772607421</v>
       </c>
       <c r="BU39" s="14"/>
-      <c r="BV39" s="13"/>
-      <c r="BX39" s="12"/>
-      <c r="BZ39" s="12"/>
-      <c r="CA39" s="11"/>
+      <c r="BV39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW39" s="10">
+        <v>11</v>
+      </c>
+      <c r="BX39" s="12">
+        <v>379739.04761903</v>
+      </c>
+      <c r="BY39" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="BZ39" s="12">
+        <f t="shared" si="21"/>
+        <v>119453.33333333</v>
+      </c>
+      <c r="CA39" s="11">
+        <f t="shared" si="22"/>
+        <v>0.45893157702160037</v>
+      </c>
       <c r="CC39" s="14"/>
       <c r="CD39" s="13"/>
       <c r="CF39" s="12"/>
@@ -8775,13 +9350,28 @@
         <f t="shared" si="19"/>
         <v>-0.79832661540908778</v>
       </c>
-      <c r="BU40" s="9"/>
+      <c r="BU40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="BV40" s="9"/>
-      <c r="BW40" s="8"/>
-      <c r="BX40" s="7"/>
-      <c r="BY40" s="27"/>
-      <c r="BZ40" s="28"/>
-      <c r="CA40" s="29"/>
+      <c r="BW40" s="8">
+        <v>249</v>
+      </c>
+      <c r="BX40" s="7">
+        <v>1201897.14285643</v>
+      </c>
+      <c r="BY40" s="27">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="BZ40" s="28">
+        <f t="shared" si="21"/>
+        <v>441576.19047599996</v>
+      </c>
+      <c r="CA40" s="29">
+        <f t="shared" si="22"/>
+        <v>0.5807760381895346</v>
+      </c>
       <c r="CC40" s="9"/>
       <c r="CD40" s="9"/>
       <c r="CE40" s="8"/>
@@ -8993,13 +9583,28 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BU41" s="14"/>
-      <c r="BV41" s="32"/>
-      <c r="BW41" s="15"/>
+      <c r="BU41" s="14">
+        <v>81</v>
+      </c>
+      <c r="BV41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="BW41" s="15">
+        <v>1054</v>
+      </c>
       <c r="BX41" s="33"/>
-      <c r="BY41" s="10"/>
-      <c r="BZ41" s="12"/>
-      <c r="CA41" s="11"/>
+      <c r="BY41" s="10">
+        <f t="shared" si="23"/>
+        <v>-543</v>
+      </c>
+      <c r="BZ41" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA41" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC41" s="14"/>
       <c r="CD41" s="32"/>
       <c r="CE41" s="15"/>
@@ -9194,12 +9799,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU42" s="14"/>
-      <c r="BV42" s="32"/>
-      <c r="BW42" s="15"/>
+      <c r="BV42" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW42" s="15">
+        <v>5</v>
+      </c>
       <c r="BX42" s="33"/>
-      <c r="BY42" s="10"/>
-      <c r="BZ42" s="12"/>
-      <c r="CA42" s="11"/>
+      <c r="BY42" s="10">
+        <f t="shared" si="23"/>
+        <v>-4</v>
+      </c>
+      <c r="BZ42" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA42" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC42" s="14"/>
       <c r="CD42" s="32"/>
       <c r="CE42" s="15"/>
@@ -9412,10 +10030,27 @@
         <v>-0.4944105274513973</v>
       </c>
       <c r="BU43" s="14"/>
-      <c r="BV43" s="13"/>
-      <c r="BX43" s="12"/>
-      <c r="BZ43" s="12"/>
-      <c r="CA43" s="11"/>
+      <c r="BV43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW43" s="10">
+        <v>78</v>
+      </c>
+      <c r="BX43" s="12">
+        <v>82412.380952079999</v>
+      </c>
+      <c r="BY43" s="10">
+        <f t="shared" si="23"/>
+        <v>-55</v>
+      </c>
+      <c r="BZ43" s="12">
+        <f t="shared" si="21"/>
+        <v>-29190.47619034996</v>
+      </c>
+      <c r="CA43" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.26155671044421785</v>
+      </c>
       <c r="CC43" s="14"/>
       <c r="CD43" s="13"/>
       <c r="CF43" s="12"/>
@@ -9622,10 +10257,27 @@
         <v>-0.51833782066373879</v>
       </c>
       <c r="BU44" s="14"/>
-      <c r="BV44" s="13"/>
-      <c r="BX44" s="12"/>
-      <c r="BZ44" s="12"/>
-      <c r="CA44" s="11"/>
+      <c r="BV44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW44" s="10">
+        <v>85</v>
+      </c>
+      <c r="BX44" s="12">
+        <v>90152.380952249994</v>
+      </c>
+      <c r="BY44" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="BZ44" s="12">
+        <f t="shared" si="21"/>
+        <v>13993.333333309987</v>
+      </c>
+      <c r="CA44" s="11">
+        <f t="shared" si="22"/>
+        <v>0.18373829204542183</v>
+      </c>
       <c r="CC44" s="14"/>
       <c r="CD44" s="13"/>
       <c r="CF44" s="12"/>
@@ -9832,10 +10484,27 @@
         <v>-0.70297883346984991</v>
       </c>
       <c r="BU45" s="14"/>
-      <c r="BV45" s="13"/>
-      <c r="BX45" s="12"/>
-      <c r="BZ45" s="12"/>
-      <c r="CA45" s="11"/>
+      <c r="BV45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW45" s="10">
+        <v>14</v>
+      </c>
+      <c r="BX45" s="12">
+        <v>92723.80952380001</v>
+      </c>
+      <c r="BY45" s="10">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="BZ45" s="12">
+        <f t="shared" si="21"/>
+        <v>-12266.666666670004</v>
+      </c>
+      <c r="CA45" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.11683599419452342</v>
+      </c>
       <c r="CC45" s="14"/>
       <c r="CD45" s="13"/>
       <c r="CF45" s="12"/>
@@ -10042,10 +10711,27 @@
         <v>-0.80548328997402319</v>
       </c>
       <c r="BU46" s="14"/>
-      <c r="BV46" s="13"/>
-      <c r="BX46" s="12"/>
-      <c r="BZ46" s="12"/>
-      <c r="CA46" s="11"/>
+      <c r="BV46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW46" s="10">
+        <v>10</v>
+      </c>
+      <c r="BX46" s="12">
+        <v>111428.57142854</v>
+      </c>
+      <c r="BY46" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="BZ46" s="12">
+        <f t="shared" si="21"/>
+        <v>18857.142857140003</v>
+      </c>
+      <c r="CA46" s="11">
+        <f t="shared" si="22"/>
+        <v>0.20370370370373575</v>
+      </c>
       <c r="CC46" s="14"/>
       <c r="CD46" s="13"/>
       <c r="CF46" s="12"/>
@@ -10237,10 +10923,22 @@
         <v>-1</v>
       </c>
       <c r="BU47" s="14"/>
-      <c r="BV47" s="13"/>
+      <c r="BV47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="BX47" s="12"/>
-      <c r="BZ47" s="12"/>
-      <c r="CA47" s="11"/>
+      <c r="BY47" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BZ47" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA47" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC47" s="14"/>
       <c r="CD47" s="13"/>
       <c r="CF47" s="12"/>
@@ -10447,10 +11145,27 @@
         <v>0.21039603960396039</v>
       </c>
       <c r="BU48" s="14"/>
-      <c r="BV48" s="13"/>
-      <c r="BX48" s="12"/>
-      <c r="BZ48" s="12"/>
-      <c r="CA48" s="11"/>
+      <c r="BV48" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW48" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX48" s="12">
+        <v>6290</v>
+      </c>
+      <c r="BY48" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="BZ48" s="12">
+        <f t="shared" si="21"/>
+        <v>-3490</v>
+      </c>
+      <c r="CA48" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.35685071574642124</v>
+      </c>
       <c r="CC48" s="14"/>
       <c r="CD48" s="13"/>
       <c r="CF48" s="12"/>
@@ -10657,10 +11372,27 @@
         <v>-0.35376532399299676</v>
       </c>
       <c r="BU49" s="14"/>
-      <c r="BV49" s="13"/>
-      <c r="BX49" s="12"/>
-      <c r="BZ49" s="12"/>
-      <c r="CA49" s="11"/>
+      <c r="BV49" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BW49" s="10">
+        <v>2</v>
+      </c>
+      <c r="BX49" s="12">
+        <v>52168.571428559997</v>
+      </c>
+      <c r="BY49" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="BZ49" s="12">
+        <f t="shared" si="21"/>
+        <v>-53260.000000000015</v>
+      </c>
+      <c r="CA49" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.50517615176157249</v>
+      </c>
       <c r="CC49" s="14"/>
       <c r="CD49" s="13"/>
       <c r="CF49" s="12"/>
@@ -10867,10 +11599,27 @@
         <v>-0.370431893687731</v>
       </c>
       <c r="BU50" s="14"/>
-      <c r="BV50" s="13"/>
-      <c r="BX50" s="12"/>
-      <c r="BZ50" s="12"/>
-      <c r="CA50" s="11"/>
+      <c r="BV50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BW50" s="10">
+        <v>10</v>
+      </c>
+      <c r="BX50" s="12">
+        <v>166761.90476188</v>
+      </c>
+      <c r="BY50" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="BZ50" s="12">
+        <f t="shared" si="21"/>
+        <v>-85904.761904750019</v>
+      </c>
+      <c r="CA50" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.33999246136449529</v>
+      </c>
       <c r="CC50" s="14"/>
       <c r="CD50" s="13"/>
       <c r="CF50" s="12"/>
@@ -11077,10 +11826,27 @@
         <v>-0.53633584195672268</v>
       </c>
       <c r="BU51" s="14"/>
-      <c r="BV51" s="13"/>
-      <c r="BX51" s="12"/>
-      <c r="BZ51" s="12"/>
-      <c r="CA51" s="11"/>
+      <c r="BV51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW51" s="10">
+        <v>12</v>
+      </c>
+      <c r="BX51" s="12">
+        <v>370285.7142857</v>
+      </c>
+      <c r="BY51" s="10">
+        <f t="shared" si="23"/>
+        <v>-12</v>
+      </c>
+      <c r="BZ51" s="12">
+        <f t="shared" si="21"/>
+        <v>-380761.90476189996</v>
+      </c>
+      <c r="CA51" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.50697438498605774</v>
+      </c>
       <c r="CC51" s="14"/>
       <c r="CD51" s="13"/>
       <c r="CF51" s="12"/>
@@ -11287,13 +12053,28 @@
         <f t="shared" si="19"/>
         <v>-0.55880220138141679</v>
       </c>
-      <c r="BU52" s="9"/>
+      <c r="BU52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="BV52" s="9"/>
-      <c r="BW52" s="8"/>
-      <c r="BX52" s="7"/>
-      <c r="BY52" s="27"/>
-      <c r="BZ52" s="28"/>
-      <c r="CA52" s="29"/>
+      <c r="BW52" s="8">
+        <v>212</v>
+      </c>
+      <c r="BX52" s="7">
+        <v>972223.33333280997</v>
+      </c>
+      <c r="BY52" s="27">
+        <f t="shared" si="23"/>
+        <v>-72</v>
+      </c>
+      <c r="BZ52" s="28">
+        <f t="shared" si="21"/>
+        <v>-532023.33333321998</v>
+      </c>
+      <c r="CA52" s="29">
+        <f t="shared" si="22"/>
+        <v>-0.35368091226180448</v>
+      </c>
       <c r="CC52" s="9"/>
       <c r="CD52" s="9"/>
       <c r="CE52" s="8"/>
@@ -11479,13 +12260,26 @@
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BU53" s="14"/>
-      <c r="BV53" s="32"/>
+      <c r="BU53" s="14">
+        <v>84</v>
+      </c>
+      <c r="BV53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
-      <c r="BY53" s="10"/>
-      <c r="BZ53" s="12"/>
-      <c r="CA53" s="11"/>
+      <c r="BY53" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BZ53" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA53" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC53" s="14"/>
       <c r="CD53" s="32"/>
       <c r="CE53" s="15"/>
@@ -11680,12 +12474,25 @@
         <v>#DIV/0!</v>
       </c>
       <c r="BU54" s="14"/>
-      <c r="BV54" s="32"/>
-      <c r="BW54" s="15"/>
+      <c r="BV54" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="BW54" s="15">
+        <v>0</v>
+      </c>
       <c r="BX54" s="33"/>
-      <c r="BY54" s="10"/>
-      <c r="BZ54" s="12"/>
-      <c r="CA54" s="11"/>
+      <c r="BY54" s="10">
+        <f t="shared" si="23"/>
+        <v>-3</v>
+      </c>
+      <c r="BZ54" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA54" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC54" s="14"/>
       <c r="CD54" s="32"/>
       <c r="CE54" s="15"/>
@@ -11898,10 +12705,27 @@
         <v>-0.44601866659768874</v>
       </c>
       <c r="BU55" s="14"/>
-      <c r="BV55" s="13"/>
-      <c r="BX55" s="12"/>
-      <c r="BZ55" s="12"/>
-      <c r="CA55" s="11"/>
+      <c r="BV55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW55" s="10">
+        <v>118</v>
+      </c>
+      <c r="BX55" s="12">
+        <v>102147.61904713005</v>
+      </c>
+      <c r="BY55" s="10">
+        <f t="shared" si="23"/>
+        <v>-32</v>
+      </c>
+      <c r="BZ55" s="12">
+        <f t="shared" si="21"/>
+        <v>-40700.952380859933</v>
+      </c>
+      <c r="CA55" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.28492376209290476</v>
+      </c>
       <c r="CC55" s="14"/>
       <c r="CD55" s="13"/>
       <c r="CF55" s="12"/>
@@ -12108,10 +12932,27 @@
         <v>-0.36623753444049517</v>
       </c>
       <c r="BU56" s="14"/>
-      <c r="BV56" s="13"/>
-      <c r="BX56" s="12"/>
-      <c r="BZ56" s="12"/>
-      <c r="CA56" s="11"/>
+      <c r="BV56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW56" s="10">
+        <v>89</v>
+      </c>
+      <c r="BX56" s="12">
+        <v>100334.28571419</v>
+      </c>
+      <c r="BY56" s="10">
+        <f t="shared" si="23"/>
+        <v>-15</v>
+      </c>
+      <c r="BZ56" s="12">
+        <f t="shared" si="21"/>
+        <v>1315.2380952300009</v>
+      </c>
+      <c r="CA56" s="11">
+        <f t="shared" si="22"/>
+        <v>1.3282677695419092E-2</v>
+      </c>
       <c r="CC56" s="14"/>
       <c r="CD56" s="13"/>
       <c r="CF56" s="12"/>
@@ -12318,10 +13159,27 @@
         <v>-0.22394639079967674</v>
       </c>
       <c r="BU57" s="14"/>
-      <c r="BV57" s="13"/>
-      <c r="BX57" s="12"/>
-      <c r="BZ57" s="12"/>
-      <c r="CA57" s="11"/>
+      <c r="BV57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW57" s="10">
+        <v>19</v>
+      </c>
+      <c r="BX57" s="12">
+        <v>131247.61904760002</v>
+      </c>
+      <c r="BY57" s="10">
+        <f t="shared" si="23"/>
+        <v>-7</v>
+      </c>
+      <c r="BZ57" s="12">
+        <f t="shared" si="21"/>
+        <v>-35076.190476189979</v>
+      </c>
+      <c r="CA57" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.21089097572150597</v>
+      </c>
       <c r="CC57" s="14"/>
       <c r="CD57" s="13"/>
       <c r="CF57" s="12"/>
@@ -12528,10 +13386,27 @@
         <v>-0.56947510131002288</v>
       </c>
       <c r="BU58" s="14"/>
-      <c r="BV58" s="13"/>
-      <c r="BX58" s="12"/>
-      <c r="BZ58" s="12"/>
-      <c r="CA58" s="11"/>
+      <c r="BV58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="BW58" s="10">
+        <v>4</v>
+      </c>
+      <c r="BX58" s="12">
+        <v>42476.190476169999</v>
+      </c>
+      <c r="BY58" s="10">
+        <f t="shared" si="23"/>
+        <v>-11</v>
+      </c>
+      <c r="BZ58" s="12">
+        <f t="shared" si="21"/>
+        <v>-137523.80952379003</v>
+      </c>
+      <c r="CA58" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.76402116402122544</v>
+      </c>
       <c r="CC58" s="14"/>
       <c r="CD58" s="13"/>
       <c r="CF58" s="12"/>
@@ -12718,10 +13593,22 @@
         <v>-1</v>
       </c>
       <c r="BU59" s="14"/>
-      <c r="BV59" s="13"/>
+      <c r="BV59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="BX59" s="12"/>
-      <c r="BZ59" s="12"/>
-      <c r="CA59" s="11"/>
+      <c r="BY59" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="BZ59" s="12">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="CA59" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC59" s="14"/>
       <c r="CD59" s="13"/>
       <c r="CF59" s="12"/>
@@ -12923,10 +13810,27 @@
         <v>-1</v>
       </c>
       <c r="BU60" s="14"/>
-      <c r="BV60" s="13"/>
-      <c r="BX60" s="12"/>
-      <c r="BZ60" s="12"/>
-      <c r="CA60" s="11"/>
+      <c r="BV60" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW60" s="10">
+        <v>1</v>
+      </c>
+      <c r="BX60" s="12">
+        <v>6290</v>
+      </c>
+      <c r="BY60" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="BZ60" s="12">
+        <f t="shared" si="21"/>
+        <v>6290</v>
+      </c>
+      <c r="CA60" s="11" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CC60" s="14"/>
       <c r="CD60" s="13"/>
       <c r="CF60" s="12"/>
@@ -13133,10 +14037,27 @@
         <v>0.31658002664489721</v>
       </c>
       <c r="BU61" s="14"/>
-      <c r="BV61" s="13"/>
-      <c r="BX61" s="12"/>
-      <c r="BZ61" s="12"/>
-      <c r="CA61" s="11"/>
+      <c r="BV61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="BW61" s="10">
+        <v>3</v>
+      </c>
+      <c r="BX61" s="12">
+        <v>83142.857142840003</v>
+      </c>
+      <c r="BY61" s="10">
+        <f t="shared" si="23"/>
+        <v>-3</v>
+      </c>
+      <c r="BZ61" s="12">
+        <f t="shared" si="21"/>
+        <v>-156857.14285712002</v>
+      </c>
+      <c r="CA61" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.65357142857144235</v>
+      </c>
       <c r="CC61" s="14"/>
       <c r="CD61" s="13"/>
       <c r="CF61" s="12"/>
@@ -13343,10 +14264,27 @@
         <v>-0.52635078969245108</v>
       </c>
       <c r="BU62" s="14"/>
-      <c r="BV62" s="13"/>
-      <c r="BX62" s="12"/>
-      <c r="BZ62" s="12"/>
-      <c r="CA62" s="11"/>
+      <c r="BV62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BW62" s="10">
+        <v>10</v>
+      </c>
+      <c r="BX62" s="12">
+        <v>217142.85714284002</v>
+      </c>
+      <c r="BY62" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="BZ62" s="12">
+        <f t="shared" si="21"/>
+        <v>-54190.47619044999</v>
+      </c>
+      <c r="CA62" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.19971919971913504</v>
+      </c>
       <c r="CC62" s="14"/>
       <c r="CD62" s="13"/>
       <c r="CF62" s="12"/>
@@ -13553,10 +14491,27 @@
         <v>-0.44671217712177086</v>
       </c>
       <c r="BU63" s="14"/>
-      <c r="BV63" s="13"/>
-      <c r="BX63" s="12"/>
-      <c r="BZ63" s="12"/>
-      <c r="CA63" s="11"/>
+      <c r="BV63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW63" s="10">
+        <v>14</v>
+      </c>
+      <c r="BX63" s="12">
+        <v>456340.95238093007</v>
+      </c>
+      <c r="BY63" s="10">
+        <f t="shared" si="23"/>
+        <v>-9</v>
+      </c>
+      <c r="BZ63" s="12">
+        <f t="shared" si="21"/>
+        <v>-257663.80952380993</v>
+      </c>
+      <c r="CA63" s="11">
+        <f t="shared" si="22"/>
+        <v>-0.36087127603525215</v>
+      </c>
       <c r="CC63" s="14"/>
       <c r="CD63" s="13"/>
       <c r="CF63" s="12"/>
@@ -13763,13 +14718,28 @@
         <f t="shared" si="19"/>
         <v>-0.41896596283920917</v>
       </c>
-      <c r="BU64" s="9"/>
+      <c r="BU64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="BV64" s="9"/>
-      <c r="BW64" s="8"/>
-      <c r="BX64" s="7"/>
-      <c r="BY64" s="27"/>
-      <c r="BZ64" s="28"/>
-      <c r="CA64" s="29"/>
+      <c r="BW64" s="8">
+        <v>258</v>
+      </c>
+      <c r="BX64" s="7">
+        <v>1139122.3809517003</v>
+      </c>
+      <c r="BY64" s="27">
+        <f t="shared" si="23"/>
+        <v>-82</v>
+      </c>
+      <c r="BZ64" s="28">
+        <f t="shared" si="21"/>
+        <v>-674407.14285698975</v>
+      </c>
+      <c r="CA64" s="29">
+        <f t="shared" si="22"/>
+        <v>-0.371875469355818</v>
+      </c>
       <c r="CC64" s="9"/>
       <c r="CD64" s="9"/>
       <c r="CE64" s="8"/>
@@ -13982,13 +14952,28 @@
         <f t="shared" si="19"/>
         <v>-0.38648650423627268</v>
       </c>
-      <c r="BU65" s="4"/>
+      <c r="BU65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="BV65" s="4"/>
-      <c r="BW65" s="3"/>
-      <c r="BX65" s="2"/>
-      <c r="BY65" s="6"/>
-      <c r="BZ65" s="5"/>
-      <c r="CA65" s="30"/>
+      <c r="BW65" s="3">
+        <v>1893</v>
+      </c>
+      <c r="BX65" s="2">
+        <v>11122184.761900868</v>
+      </c>
+      <c r="BY65" s="6">
+        <f t="shared" si="23"/>
+        <v>-669</v>
+      </c>
+      <c r="BZ65" s="5">
+        <f t="shared" si="21"/>
+        <v>-5915432.3809517622</v>
+      </c>
+      <c r="CA65" s="30">
+        <f t="shared" si="22"/>
+        <v>-0.34719833949510465</v>
+      </c>
       <c r="CC65" s="4"/>
       <c r="CD65" s="4"/>
       <c r="CE65" s="3"/>
@@ -14019,7 +15004,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="107" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14031,7 +15016,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14043,7 +15028,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14055,7 +15040,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14067,7 +15052,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14079,7 +15064,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14091,7 +15076,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14103,7 +15088,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14115,7 +15100,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14127,7 +15112,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{F92DB01E-9288-5849-81E4-35B4E2C95774}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14139,7 +15124,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{DDBF6E41-C389-2344-92BB-6A5E3B3BC008}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{DDBF6E41-C389-2344-92BB-6A5E3B3BC008}">
             <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14151,7 +15136,7 @@
           <xm:sqref>CG5:CI65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -14163,7 +15148,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C1D50-9114-9D4B-BDF9-9EDA1CE2B0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E89D6D7-7DC1-8342-A9AE-28713FCD6FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14260" yWindow="700" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -219,7 +219,7 @@
     <t>26Q2W10</t>
   </si>
   <si>
-    <t>0301-0307</t>
+    <t>03/01-03/07</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E89D6D7-7DC1-8342-A9AE-28713FCD6FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C51973-D898-7F49-B3CA-EC205B978CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14260" yWindow="700" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5720" yWindow="7660" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="42">
   <si>
     <t>總計</t>
   </si>
@@ -1185,79 +1185,195 @@
       <c r="G4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="17"/>
-      <c r="AC4" s="16"/>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="16"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="17"/>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="16"/>
+      <c r="I4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="S4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="V4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="AO4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AP4" s="19"/>
-      <c r="AQ4" s="18"/>
-      <c r="AR4" s="17"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="16"/>
-      <c r="AU4" s="16"/>
+      <c r="AP4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="AW4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="AX4" s="19"/>
-      <c r="AY4" s="18"/>
-      <c r="AZ4" s="17"/>
-      <c r="BA4" s="16"/>
-      <c r="BB4" s="16"/>
-      <c r="BC4" s="16"/>
+      <c r="AX4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BA4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BE4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BF4" s="19"/>
-      <c r="BG4" s="18"/>
-      <c r="BH4" s="17"/>
-      <c r="BI4" s="16"/>
-      <c r="BJ4" s="16"/>
-      <c r="BK4" s="16"/>
+      <c r="BF4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BG4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BH4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BI4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BM4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BN4" s="19"/>
-      <c r="BO4" s="18"/>
-      <c r="BP4" s="17"/>
-      <c r="BQ4" s="16"/>
-      <c r="BR4" s="16"/>
-      <c r="BS4" s="16"/>
+      <c r="BN4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BP4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BR4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="BU4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="BV4" s="19"/>
-      <c r="BW4" s="18"/>
-      <c r="BX4" s="17"/>
-      <c r="BY4" s="16"/>
-      <c r="BZ4" s="16"/>
-      <c r="CA4" s="16"/>
+      <c r="BV4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BX4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="BY4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="CC4" s="19"/>
       <c r="CD4" s="19"/>
       <c r="CE4" s="18"/>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C51973-D898-7F49-B3CA-EC205B978CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE5153-9DA8-AD4E-9EFD-EC02B1CCAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5720" yWindow="7660" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="3360" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="44">
   <si>
     <t>總計</t>
   </si>
@@ -220,6 +220,14 @@
   </si>
   <si>
     <t>03/01-03/07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/08~03/14</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +559,12 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1069,7 +1082,11 @@
       </c>
       <c r="BV1" s="26"/>
       <c r="BX1" s="25"/>
-      <c r="CC1" s="26"/>
+      <c r="CC1" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="CD1" s="26"/>
+      <c r="CF1" s="25"/>
       <c r="CK1" s="26"/>
       <c r="CS1" s="26"/>
     </row>
@@ -1136,7 +1153,9 @@
       <c r="BY2" s="21"/>
       <c r="BZ2" s="21"/>
       <c r="CA2" s="21"/>
-      <c r="CC2" s="22"/>
+      <c r="CC2" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="CD2" s="21"/>
       <c r="CF2" s="21"/>
       <c r="CG2" s="21"/>
@@ -1374,13 +1393,27 @@
       <c r="CA4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="CC4" s="19"/>
-      <c r="CD4" s="19"/>
-      <c r="CE4" s="18"/>
-      <c r="CF4" s="17"/>
-      <c r="CG4" s="16"/>
-      <c r="CH4" s="16"/>
-      <c r="CI4" s="16"/>
+      <c r="CC4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CD4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CE4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="CK4" s="19"/>
       <c r="CL4" s="19"/>
       <c r="CM4" s="18"/>
@@ -1618,13 +1651,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CB5" s="38"/>
-      <c r="CC5" s="14"/>
-      <c r="CD5" s="32"/>
-      <c r="CE5" s="15"/>
+      <c r="CC5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CD5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE5" s="15">
+        <v>6486</v>
+      </c>
       <c r="CF5" s="33"/>
-      <c r="CG5" s="10"/>
-      <c r="CH5" s="12"/>
-      <c r="CI5" s="11"/>
+      <c r="CG5" s="10">
+        <f t="shared" ref="CG5:CG65" si="23">CE5-BW5</f>
+        <v>1051</v>
+      </c>
+      <c r="CH5" s="12">
+        <f t="shared" ref="CH5:CH65" si="24">CF5-BX5</f>
+        <v>0</v>
+      </c>
+      <c r="CI5" s="11" t="e">
+        <f t="shared" ref="CI5:CI65" si="25">(CF5-BX5)/BX5</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CJ5" s="38"/>
       <c r="CK5" s="14"/>
       <c r="CL5" s="32"/>
@@ -1834,11 +1882,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC6" s="14"/>
-      <c r="CD6" s="32"/>
+      <c r="CD6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CF6" s="33"/>
-      <c r="CG6" s="10"/>
-      <c r="CH6" s="12"/>
-      <c r="CI6" s="11"/>
+      <c r="CG6" s="10">
+        <f t="shared" si="23"/>
+        <v>-13</v>
+      </c>
+      <c r="CH6" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI6" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK6" s="14"/>
       <c r="CL6" s="32"/>
       <c r="CN6" s="33"/>
@@ -2064,10 +2123,27 @@
         <v>-0.20274549452624313</v>
       </c>
       <c r="CC7" s="14"/>
-      <c r="CD7" s="13"/>
-      <c r="CF7" s="12"/>
-      <c r="CH7" s="12"/>
-      <c r="CI7" s="11"/>
+      <c r="CD7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE7" s="10">
+        <v>186</v>
+      </c>
+      <c r="CF7" s="12">
+        <v>218509.52380868993</v>
+      </c>
+      <c r="CG7" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="CH7" s="12">
+        <f t="shared" si="24"/>
+        <v>-9042.8571429600124</v>
+      </c>
+      <c r="CI7" s="11">
+        <f t="shared" si="25"/>
+        <v>-3.9739672708067282E-2</v>
+      </c>
       <c r="CK7" s="14"/>
       <c r="CL7" s="13"/>
       <c r="CN7" s="12"/>
@@ -2291,10 +2367,27 @@
         <v>-0.33201301486241308</v>
       </c>
       <c r="CC8" s="14"/>
-      <c r="CD8" s="13"/>
-      <c r="CF8" s="12"/>
-      <c r="CH8" s="12"/>
-      <c r="CI8" s="11"/>
+      <c r="CD8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE8" s="10">
+        <v>233</v>
+      </c>
+      <c r="CF8" s="12">
+        <v>280382.85714268993</v>
+      </c>
+      <c r="CG8" s="10">
+        <f t="shared" si="23"/>
+        <v>-18</v>
+      </c>
+      <c r="CH8" s="12">
+        <f t="shared" si="24"/>
+        <v>-28153.333333340066</v>
+      </c>
+      <c r="CI8" s="11">
+        <f t="shared" si="25"/>
+        <v>-9.1248074625875322E-2</v>
+      </c>
       <c r="CK8" s="14"/>
       <c r="CL8" s="13"/>
       <c r="CN8" s="12"/>
@@ -2518,10 +2611,27 @@
         <v>-0.35691653359845976</v>
       </c>
       <c r="CC9" s="14"/>
-      <c r="CD9" s="13"/>
-      <c r="CF9" s="12"/>
-      <c r="CH9" s="12"/>
-      <c r="CI9" s="11"/>
+      <c r="CD9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE9" s="10">
+        <v>75</v>
+      </c>
+      <c r="CF9" s="12">
+        <v>497857.14285712998</v>
+      </c>
+      <c r="CG9" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH9" s="12">
+        <f t="shared" si="24"/>
+        <v>9980.9523809599923</v>
+      </c>
+      <c r="CI9" s="11">
+        <f t="shared" si="25"/>
+        <v>2.0457961621817462E-2</v>
+      </c>
       <c r="CK9" s="14"/>
       <c r="CL9" s="13"/>
       <c r="CN9" s="12"/>
@@ -2745,10 +2855,27 @@
         <v>-0.51457530616739655</v>
       </c>
       <c r="CC10" s="14"/>
-      <c r="CD10" s="13"/>
-      <c r="CF10" s="12"/>
-      <c r="CH10" s="12"/>
-      <c r="CI10" s="11"/>
+      <c r="CD10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE10" s="10">
+        <v>39</v>
+      </c>
+      <c r="CF10" s="12">
+        <v>521999.99999993003</v>
+      </c>
+      <c r="CG10" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH10" s="12">
+        <f t="shared" si="24"/>
+        <v>62095.238095240027</v>
+      </c>
+      <c r="CI10" s="11">
+        <f t="shared" si="25"/>
+        <v>0.13501760198801455</v>
+      </c>
       <c r="CK10" s="14"/>
       <c r="CL10" s="13"/>
       <c r="CN10" s="12"/>
@@ -2952,10 +3079,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC11" s="14"/>
-      <c r="CD11" s="13"/>
+      <c r="CD11" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF11" s="12"/>
-      <c r="CH11" s="12"/>
-      <c r="CI11" s="11"/>
+      <c r="CG11" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH11" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI11" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK11" s="14"/>
       <c r="CL11" s="13"/>
       <c r="CN11" s="12"/>
@@ -3179,10 +3318,27 @@
         <v>-6.9623271340009535E-2</v>
       </c>
       <c r="CC12" s="14"/>
-      <c r="CD12" s="13"/>
-      <c r="CF12" s="12"/>
-      <c r="CH12" s="12"/>
-      <c r="CI12" s="11"/>
+      <c r="CD12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE12" s="10">
+        <v>6</v>
+      </c>
+      <c r="CF12" s="12">
+        <v>36740</v>
+      </c>
+      <c r="CG12" s="10">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="CH12" s="12">
+        <f t="shared" si="24"/>
+        <v>-2280</v>
+      </c>
+      <c r="CI12" s="11">
+        <f t="shared" si="25"/>
+        <v>-5.84315735520246E-2</v>
+      </c>
       <c r="CK12" s="14"/>
       <c r="CL12" s="13"/>
       <c r="CN12" s="12"/>
@@ -3406,10 +3562,27 @@
         <v>-0.54386964867508925</v>
       </c>
       <c r="CC13" s="14"/>
-      <c r="CD13" s="13"/>
-      <c r="CF13" s="12"/>
-      <c r="CH13" s="12"/>
-      <c r="CI13" s="11"/>
+      <c r="CD13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE13" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>689619.04761897994</v>
+      </c>
+      <c r="CG13" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="CH13" s="12">
+        <f t="shared" si="24"/>
+        <v>98947.619047599961</v>
+      </c>
+      <c r="CI13" s="11">
+        <f t="shared" si="25"/>
+        <v>0.16751719189620934</v>
+      </c>
       <c r="CK13" s="14"/>
       <c r="CL13" s="13"/>
       <c r="CN13" s="12"/>
@@ -3633,10 +3806,27 @@
         <v>-0.44431372549018977</v>
       </c>
       <c r="CC14" s="14"/>
-      <c r="CD14" s="13"/>
-      <c r="CF14" s="12"/>
-      <c r="CH14" s="12"/>
-      <c r="CI14" s="11"/>
+      <c r="CD14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE14" s="10">
+        <v>43</v>
+      </c>
+      <c r="CF14" s="12">
+        <v>784380.95238087</v>
+      </c>
+      <c r="CG14" s="10">
+        <f t="shared" si="23"/>
+        <v>-2</v>
+      </c>
+      <c r="CH14" s="12">
+        <f t="shared" si="24"/>
+        <v>-25333.333333360031</v>
+      </c>
+      <c r="CI14" s="11">
+        <f t="shared" si="25"/>
+        <v>-3.1286756057433383E-2</v>
+      </c>
       <c r="CK14" s="14"/>
       <c r="CL14" s="13"/>
       <c r="CN14" s="12"/>
@@ -3860,10 +4050,27 @@
         <v>-0.31319967528634601</v>
       </c>
       <c r="CC15" s="14"/>
-      <c r="CD15" s="13"/>
-      <c r="CF15" s="12"/>
-      <c r="CH15" s="12"/>
-      <c r="CI15" s="11"/>
+      <c r="CD15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE15" s="10">
+        <v>159</v>
+      </c>
+      <c r="CF15" s="12">
+        <v>6124231.4285713602</v>
+      </c>
+      <c r="CG15" s="10">
+        <f t="shared" si="23"/>
+        <v>94</v>
+      </c>
+      <c r="CH15" s="12">
+        <f t="shared" si="24"/>
+        <v>3714231.4285714002</v>
+      </c>
+      <c r="CI15" s="11">
+        <f t="shared" si="25"/>
+        <v>1.5411748666271627</v>
+      </c>
       <c r="CK15" s="14"/>
       <c r="CL15" s="13"/>
       <c r="CN15" s="12"/>
@@ -4087,13 +4294,28 @@
         <f t="shared" si="22"/>
         <v>-0.39093242952524898</v>
       </c>
-      <c r="CC16" s="9"/>
+      <c r="CC16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CD16" s="9"/>
-      <c r="CE16" s="8"/>
-      <c r="CF16" s="7"/>
-      <c r="CG16" s="27"/>
-      <c r="CH16" s="28"/>
-      <c r="CI16" s="29"/>
+      <c r="CE16" s="8">
+        <v>759</v>
+      </c>
+      <c r="CF16" s="7">
+        <v>9153720.9523796495</v>
+      </c>
+      <c r="CG16" s="27">
+        <f t="shared" si="23"/>
+        <v>70</v>
+      </c>
+      <c r="CH16" s="28">
+        <f t="shared" si="24"/>
+        <v>3820445.7142855395</v>
+      </c>
+      <c r="CI16" s="29">
+        <f t="shared" si="25"/>
+        <v>0.71634137443294743</v>
+      </c>
       <c r="CK16" s="9"/>
       <c r="CL16" s="9"/>
       <c r="CM16" s="8"/>
@@ -4320,13 +4542,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC17" s="14"/>
-      <c r="CD17" s="32"/>
-      <c r="CE17" s="15"/>
+      <c r="CC17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CD17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE17" s="15">
+        <v>5542</v>
+      </c>
       <c r="CF17" s="33"/>
-      <c r="CG17" s="10"/>
-      <c r="CH17" s="12"/>
-      <c r="CI17" s="11"/>
+      <c r="CG17" s="10">
+        <f t="shared" si="23"/>
+        <v>1518</v>
+      </c>
+      <c r="CH17" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI17" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK17" s="14"/>
       <c r="CL17" s="32"/>
       <c r="CM17" s="15"/>
@@ -4534,12 +4771,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC18" s="14"/>
-      <c r="CD18" s="32"/>
+      <c r="CD18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE18" s="15"/>
       <c r="CF18" s="33"/>
-      <c r="CG18" s="10"/>
-      <c r="CH18" s="12"/>
-      <c r="CI18" s="11"/>
+      <c r="CG18" s="10">
+        <f t="shared" si="23"/>
+        <v>-5</v>
+      </c>
+      <c r="CH18" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI18" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK18" s="14"/>
       <c r="CL18" s="32"/>
       <c r="CM18" s="15"/>
@@ -4767,10 +5015,27 @@
         <v>-0.34594286378034994</v>
       </c>
       <c r="CC19" s="14"/>
-      <c r="CD19" s="13"/>
-      <c r="CF19" s="12"/>
-      <c r="CH19" s="12"/>
-      <c r="CI19" s="11"/>
+      <c r="CD19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE19" s="10">
+        <v>204</v>
+      </c>
+      <c r="CF19" s="12">
+        <v>216177.14285634996</v>
+      </c>
+      <c r="CG19" s="10">
+        <f t="shared" si="23"/>
+        <v>84</v>
+      </c>
+      <c r="CH19" s="12">
+        <f t="shared" si="24"/>
+        <v>98193.333333059942</v>
+      </c>
+      <c r="CI19" s="11">
+        <f t="shared" si="25"/>
+        <v>0.83226108505740837</v>
+      </c>
       <c r="CK19" s="14"/>
       <c r="CL19" s="13"/>
       <c r="CN19" s="12"/>
@@ -4994,10 +5259,27 @@
         <v>-0.203679873159022</v>
       </c>
       <c r="CC20" s="14"/>
-      <c r="CD20" s="13"/>
-      <c r="CF20" s="12"/>
-      <c r="CH20" s="12"/>
-      <c r="CI20" s="11"/>
+      <c r="CD20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE20" s="10">
+        <v>253</v>
+      </c>
+      <c r="CF20" s="12">
+        <v>306130.47619033</v>
+      </c>
+      <c r="CG20" s="10">
+        <f t="shared" si="23"/>
+        <v>42</v>
+      </c>
+      <c r="CH20" s="12">
+        <f t="shared" si="24"/>
+        <v>100448.57142858999</v>
+      </c>
+      <c r="CI20" s="11">
+        <f t="shared" si="25"/>
+        <v>0.48836853949280895</v>
+      </c>
       <c r="CK20" s="14"/>
       <c r="CL20" s="13"/>
       <c r="CN20" s="12"/>
@@ -5221,10 +5503,27 @@
         <v>-6.0940078645477097E-2</v>
       </c>
       <c r="CC21" s="14"/>
-      <c r="CD21" s="13"/>
-      <c r="CF21" s="12"/>
-      <c r="CH21" s="12"/>
-      <c r="CI21" s="11"/>
+      <c r="CD21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE21" s="10">
+        <v>54</v>
+      </c>
+      <c r="CF21" s="12">
+        <v>328057.14285712002</v>
+      </c>
+      <c r="CG21" s="10">
+        <f t="shared" si="23"/>
+        <v>-6</v>
+      </c>
+      <c r="CH21" s="12">
+        <f t="shared" si="24"/>
+        <v>-110895.23809524998</v>
+      </c>
+      <c r="CI21" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.25263614666959294</v>
+      </c>
       <c r="CK21" s="14"/>
       <c r="CL21" s="13"/>
       <c r="CN21" s="12"/>
@@ -5448,10 +5747,27 @@
         <v>-0.40599633411888447</v>
       </c>
       <c r="CC22" s="14"/>
-      <c r="CD22" s="13"/>
-      <c r="CF22" s="12"/>
-      <c r="CH22" s="12"/>
-      <c r="CI22" s="11"/>
+      <c r="CD22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE22" s="10">
+        <v>39</v>
+      </c>
+      <c r="CF22" s="12">
+        <v>483428.57142850995</v>
+      </c>
+      <c r="CG22" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH22" s="12">
+        <f t="shared" si="24"/>
+        <v>51333.333333329938</v>
+      </c>
+      <c r="CI22" s="11">
+        <f t="shared" si="25"/>
+        <v>0.11880096980384325</v>
+      </c>
       <c r="CK22" s="14"/>
       <c r="CL22" s="13"/>
       <c r="CN22" s="12"/>
@@ -5665,10 +5981,27 @@
         <v>-1</v>
       </c>
       <c r="CC23" s="14"/>
-      <c r="CD23" s="13"/>
-      <c r="CF23" s="12"/>
-      <c r="CH23" s="12"/>
-      <c r="CI23" s="11"/>
+      <c r="CD23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CE23" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF23" s="12">
+        <v>11514.285714279999</v>
+      </c>
+      <c r="CG23" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH23" s="12">
+        <f t="shared" si="24"/>
+        <v>11514.285714279999</v>
+      </c>
+      <c r="CI23" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK23" s="14"/>
       <c r="CL23" s="13"/>
       <c r="CN23" s="12"/>
@@ -5892,10 +6225,27 @@
         <v>-0.16751824817518249</v>
       </c>
       <c r="CC24" s="14"/>
-      <c r="CD24" s="13"/>
-      <c r="CF24" s="12"/>
-      <c r="CH24" s="12"/>
-      <c r="CI24" s="11"/>
+      <c r="CD24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE24" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF24" s="12">
+        <v>104510</v>
+      </c>
+      <c r="CG24" s="10">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="CH24" s="12">
+        <f t="shared" si="24"/>
+        <v>58890</v>
+      </c>
+      <c r="CI24" s="11">
+        <f t="shared" si="25"/>
+        <v>1.2908811924594477</v>
+      </c>
       <c r="CK24" s="14"/>
       <c r="CL24" s="13"/>
       <c r="CN24" s="12"/>
@@ -6119,10 +6469,27 @@
         <v>-0.40849879269777506</v>
       </c>
       <c r="CC25" s="14"/>
-      <c r="CD25" s="13"/>
-      <c r="CF25" s="12"/>
-      <c r="CH25" s="12"/>
-      <c r="CI25" s="11"/>
+      <c r="CD25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE25" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF25" s="12">
+        <v>336195.23809522</v>
+      </c>
+      <c r="CG25" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH25" s="12">
+        <f t="shared" si="24"/>
+        <v>153052.38095239</v>
+      </c>
+      <c r="CI25" s="11">
+        <f t="shared" si="25"/>
+        <v>0.83569942797729235</v>
+      </c>
       <c r="CK25" s="14"/>
       <c r="CL25" s="13"/>
       <c r="CN25" s="12"/>
@@ -6346,10 +6713,27 @@
         <v>-0.43693446668496028</v>
       </c>
       <c r="CC26" s="14"/>
-      <c r="CD26" s="13"/>
-      <c r="CF26" s="12"/>
-      <c r="CH26" s="12"/>
-      <c r="CI26" s="11"/>
+      <c r="CD26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE26" s="10">
+        <v>34</v>
+      </c>
+      <c r="CF26" s="12">
+        <v>621619.04761897004</v>
+      </c>
+      <c r="CG26" s="10">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="CH26" s="12">
+        <f t="shared" si="24"/>
+        <v>230476.19047616003</v>
+      </c>
+      <c r="CI26" s="11">
+        <f t="shared" si="25"/>
+        <v>0.58923788653517695</v>
+      </c>
       <c r="CK26" s="14"/>
       <c r="CL26" s="13"/>
       <c r="CN26" s="12"/>
@@ -6573,10 +6957,27 @@
         <v>-0.55976195051904498</v>
       </c>
       <c r="CC27" s="14"/>
-      <c r="CD27" s="13"/>
-      <c r="CF27" s="12"/>
-      <c r="CH27" s="12"/>
-      <c r="CI27" s="11"/>
+      <c r="CD27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE27" s="10">
+        <v>145</v>
+      </c>
+      <c r="CF27" s="12">
+        <v>5108095.2380951494</v>
+      </c>
+      <c r="CG27" s="10">
+        <f t="shared" si="23"/>
+        <v>126</v>
+      </c>
+      <c r="CH27" s="12">
+        <f t="shared" si="24"/>
+        <v>4447047.6190475496</v>
+      </c>
+      <c r="CI27" s="11">
+        <f t="shared" si="25"/>
+        <v>6.7272727272728154</v>
+      </c>
       <c r="CK27" s="14"/>
       <c r="CL27" s="13"/>
       <c r="CN27" s="12"/>
@@ -6800,13 +7201,28 @@
         <f t="shared" si="22"/>
         <v>-0.41098482874390835</v>
       </c>
-      <c r="CC28" s="9"/>
+      <c r="CC28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CD28" s="9"/>
-      <c r="CE28" s="8"/>
-      <c r="CF28" s="7"/>
-      <c r="CG28" s="27"/>
-      <c r="CH28" s="28"/>
-      <c r="CI28" s="29"/>
+      <c r="CE28" s="8">
+        <v>759</v>
+      </c>
+      <c r="CF28" s="7">
+        <v>7515727.1428559292</v>
+      </c>
+      <c r="CG28" s="27">
+        <f t="shared" si="23"/>
+        <v>274</v>
+      </c>
+      <c r="CH28" s="28">
+        <f t="shared" si="24"/>
+        <v>5040060.4761901088</v>
+      </c>
+      <c r="CI28" s="29">
+        <f t="shared" si="25"/>
+        <v>2.0358396968594983</v>
+      </c>
       <c r="CK28" s="9"/>
       <c r="CL28" s="9"/>
       <c r="CM28" s="8"/>
@@ -7033,13 +7449,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC29" s="14"/>
-      <c r="CD29" s="32"/>
-      <c r="CE29" s="15"/>
+      <c r="CC29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CD29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE29" s="15">
+        <v>3502</v>
+      </c>
       <c r="CF29" s="33"/>
-      <c r="CG29" s="10"/>
-      <c r="CH29" s="12"/>
-      <c r="CI29" s="11"/>
+      <c r="CG29" s="10">
+        <f t="shared" si="23"/>
+        <v>754</v>
+      </c>
+      <c r="CH29" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI29" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK29" s="14"/>
       <c r="CL29" s="32"/>
       <c r="CM29" s="15"/>
@@ -7247,12 +7678,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC30" s="14"/>
-      <c r="CD30" s="32"/>
+      <c r="CD30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE30" s="15"/>
       <c r="CF30" s="33"/>
-      <c r="CG30" s="10"/>
-      <c r="CH30" s="12"/>
-      <c r="CI30" s="11"/>
+      <c r="CG30" s="10">
+        <f t="shared" si="23"/>
+        <v>-1</v>
+      </c>
+      <c r="CH30" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI30" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK30" s="14"/>
       <c r="CL30" s="32"/>
       <c r="CM30" s="15"/>
@@ -7480,10 +7922,27 @@
         <v>0.15327535985335874</v>
       </c>
       <c r="CC31" s="14"/>
-      <c r="CD31" s="13"/>
-      <c r="CF31" s="12"/>
-      <c r="CH31" s="12"/>
-      <c r="CI31" s="11"/>
+      <c r="CD31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE31" s="10">
+        <v>87</v>
+      </c>
+      <c r="CF31" s="12">
+        <v>76910.476190090034</v>
+      </c>
+      <c r="CG31" s="10">
+        <f t="shared" si="23"/>
+        <v>-14</v>
+      </c>
+      <c r="CH31" s="12">
+        <f t="shared" si="24"/>
+        <v>-26407.619047550004</v>
+      </c>
+      <c r="CI31" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.25559529515919094</v>
+      </c>
       <c r="CK31" s="14"/>
       <c r="CL31" s="13"/>
       <c r="CN31" s="12"/>
@@ -7707,10 +8166,27 @@
         <v>-0.25161821315016214</v>
       </c>
       <c r="CC32" s="14"/>
-      <c r="CD32" s="13"/>
-      <c r="CF32" s="12"/>
-      <c r="CH32" s="12"/>
-      <c r="CI32" s="11"/>
+      <c r="CD32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE32" s="10">
+        <v>80</v>
+      </c>
+      <c r="CF32" s="12">
+        <v>83333.333333229995</v>
+      </c>
+      <c r="CG32" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH32" s="12">
+        <f t="shared" si="24"/>
+        <v>198.0952381100069</v>
+      </c>
+      <c r="CI32" s="11">
+        <f t="shared" si="25"/>
+        <v>2.382807130273138E-3</v>
+      </c>
       <c r="CK32" s="14"/>
       <c r="CL32" s="13"/>
       <c r="CN32" s="12"/>
@@ -7934,10 +8410,27 @@
         <v>1.0662089720679766</v>
       </c>
       <c r="CC33" s="14"/>
-      <c r="CD33" s="13"/>
-      <c r="CF33" s="12"/>
-      <c r="CH33" s="12"/>
-      <c r="CI33" s="11"/>
+      <c r="CD33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE33" s="10">
+        <v>19</v>
+      </c>
+      <c r="CF33" s="12">
+        <v>112676.19047618</v>
+      </c>
+      <c r="CG33" s="10">
+        <f t="shared" si="23"/>
+        <v>-11</v>
+      </c>
+      <c r="CH33" s="12">
+        <f t="shared" si="24"/>
+        <v>-96561.904761890008</v>
+      </c>
+      <c r="CI33" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.46149294492488274</v>
+      </c>
       <c r="CK33" s="14"/>
       <c r="CL33" s="13"/>
       <c r="CN33" s="12"/>
@@ -8161,10 +8654,27 @@
         <v>5.4496124031015132</v>
       </c>
       <c r="CC34" s="14"/>
-      <c r="CD34" s="13"/>
-      <c r="CF34" s="12"/>
-      <c r="CH34" s="12"/>
-      <c r="CI34" s="11"/>
+      <c r="CD34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE34" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF34" s="12">
+        <v>107238.09523807</v>
+      </c>
+      <c r="CG34" s="10">
+        <f t="shared" si="23"/>
+        <v>-10</v>
+      </c>
+      <c r="CH34" s="12">
+        <f t="shared" si="24"/>
+        <v>-130476.19047616003</v>
+      </c>
+      <c r="CI34" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.54887820512820562</v>
+      </c>
       <c r="CK34" s="14"/>
       <c r="CL34" s="13"/>
       <c r="CN34" s="12"/>
@@ -8368,10 +8878,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC35" s="14"/>
-      <c r="CD35" s="13"/>
-      <c r="CF35" s="12"/>
-      <c r="CH35" s="12"/>
-      <c r="CI35" s="11"/>
+      <c r="CD35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CE35" s="10">
+        <v>1</v>
+      </c>
+      <c r="CF35" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CG35" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH35" s="12">
+        <f t="shared" si="24"/>
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CI35" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK35" s="14"/>
       <c r="CL35" s="13"/>
       <c r="CN35" s="12"/>
@@ -8585,10 +9112,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC36" s="14"/>
-      <c r="CD36" s="13"/>
-      <c r="CF36" s="12"/>
-      <c r="CH36" s="12"/>
-      <c r="CI36" s="11"/>
+      <c r="CD36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE36" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF36" s="12">
+        <v>8480</v>
+      </c>
+      <c r="CG36" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH36" s="12">
+        <f t="shared" si="24"/>
+        <v>65.71428571999968</v>
+      </c>
+      <c r="CI36" s="11">
+        <f t="shared" si="25"/>
+        <v>7.8098471993261484E-3</v>
+      </c>
       <c r="CK36" s="14"/>
       <c r="CL36" s="13"/>
       <c r="CN36" s="12"/>
@@ -8795,7 +9339,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="23">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="26">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -8807,10 +9351,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC37" s="14"/>
-      <c r="CD37" s="13"/>
-      <c r="CF37" s="12"/>
-      <c r="CH37" s="12"/>
-      <c r="CI37" s="11"/>
+      <c r="CD37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE37" s="10">
+        <v>3</v>
+      </c>
+      <c r="CF37" s="12">
+        <v>84454.285714270009</v>
+      </c>
+      <c r="CG37" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH37" s="12">
+        <f t="shared" si="24"/>
+        <v>58306.666666660007</v>
+      </c>
+      <c r="CI37" s="11">
+        <f t="shared" si="25"/>
+        <v>2.2299034784197485</v>
+      </c>
       <c r="CK37" s="14"/>
       <c r="CL37" s="13"/>
       <c r="CN37" s="12"/>
@@ -9022,7 +9583,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -9034,10 +9595,27 @@
         <v>-4.3709391612534981E-2</v>
       </c>
       <c r="CC38" s="14"/>
-      <c r="CD38" s="13"/>
-      <c r="CF38" s="12"/>
-      <c r="CH38" s="12"/>
-      <c r="CI38" s="11"/>
+      <c r="CD38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE38" s="10">
+        <v>11</v>
+      </c>
+      <c r="CF38" s="12">
+        <v>180285.71428568001</v>
+      </c>
+      <c r="CG38" s="10">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="CH38" s="12">
+        <f t="shared" si="24"/>
+        <v>26095.238095230015</v>
+      </c>
+      <c r="CI38" s="11">
+        <f t="shared" si="25"/>
+        <v>0.16924027177267556</v>
+      </c>
       <c r="CK38" s="14"/>
       <c r="CL38" s="13"/>
       <c r="CN38" s="12"/>
@@ -9249,7 +9827,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -9261,10 +9839,27 @@
         <v>0.45893157702160037</v>
       </c>
       <c r="CC39" s="14"/>
-      <c r="CD39" s="13"/>
-      <c r="CF39" s="12"/>
-      <c r="CH39" s="12"/>
-      <c r="CI39" s="11"/>
+      <c r="CD39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE39" s="10">
+        <v>15</v>
+      </c>
+      <c r="CF39" s="12">
+        <v>454761.90476189001</v>
+      </c>
+      <c r="CG39" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH39" s="12">
+        <f t="shared" si="24"/>
+        <v>75022.857142860012</v>
+      </c>
+      <c r="CI39" s="11">
+        <f t="shared" si="25"/>
+        <v>0.19756424211114065</v>
+      </c>
       <c r="CK39" s="14"/>
       <c r="CL39" s="13"/>
       <c r="CN39" s="12"/>
@@ -9477,7 +10072,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -9488,13 +10083,28 @@
         <f t="shared" si="22"/>
         <v>0.5807760381895346</v>
       </c>
-      <c r="CC40" s="9"/>
+      <c r="CC40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CD40" s="9"/>
-      <c r="CE40" s="8"/>
-      <c r="CF40" s="7"/>
-      <c r="CG40" s="27"/>
-      <c r="CH40" s="28"/>
-      <c r="CI40" s="29"/>
+      <c r="CE40" s="8">
+        <v>227</v>
+      </c>
+      <c r="CF40" s="7">
+        <v>1116997.1428565499</v>
+      </c>
+      <c r="CG40" s="27">
+        <f t="shared" si="23"/>
+        <v>-22</v>
+      </c>
+      <c r="CH40" s="28">
+        <f t="shared" si="24"/>
+        <v>-84899.999999880092</v>
+      </c>
+      <c r="CI40" s="29">
+        <f t="shared" si="25"/>
+        <v>-7.0638324173154007E-2</v>
+      </c>
       <c r="CK40" s="9"/>
       <c r="CL40" s="9"/>
       <c r="CM40" s="8"/>
@@ -9710,7 +10320,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -9721,13 +10331,28 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC41" s="14"/>
-      <c r="CD41" s="32"/>
-      <c r="CE41" s="15"/>
+      <c r="CC41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CD41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CE41" s="15">
+        <v>1285</v>
+      </c>
       <c r="CF41" s="33"/>
-      <c r="CG41" s="10"/>
-      <c r="CH41" s="12"/>
-      <c r="CI41" s="11"/>
+      <c r="CG41" s="10">
+        <f t="shared" si="23"/>
+        <v>231</v>
+      </c>
+      <c r="CH41" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI41" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK41" s="14"/>
       <c r="CL41" s="32"/>
       <c r="CM41" s="15"/>
@@ -9923,7 +10548,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -9935,12 +10560,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC42" s="14"/>
-      <c r="CD42" s="32"/>
+      <c r="CD42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE42" s="15"/>
       <c r="CF42" s="33"/>
-      <c r="CG42" s="10"/>
-      <c r="CH42" s="12"/>
-      <c r="CI42" s="11"/>
+      <c r="CG42" s="10">
+        <f t="shared" si="23"/>
+        <v>-5</v>
+      </c>
+      <c r="CH42" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI42" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK42" s="14"/>
       <c r="CL42" s="32"/>
       <c r="CM42" s="15"/>
@@ -10156,7 +10792,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -10168,10 +10804,27 @@
         <v>-0.26155671044421785</v>
       </c>
       <c r="CC43" s="14"/>
-      <c r="CD43" s="13"/>
-      <c r="CF43" s="12"/>
-      <c r="CH43" s="12"/>
-      <c r="CI43" s="11"/>
+      <c r="CD43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE43" s="10">
+        <v>110</v>
+      </c>
+      <c r="CF43" s="12">
+        <v>85552.380951930012</v>
+      </c>
+      <c r="CG43" s="10">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="CH43" s="12">
+        <f t="shared" si="24"/>
+        <v>3139.9999998500134</v>
+      </c>
+      <c r="CI43" s="11">
+        <f t="shared" si="25"/>
+        <v>3.8101071265928071E-2</v>
+      </c>
       <c r="CK43" s="14"/>
       <c r="CL43" s="13"/>
       <c r="CN43" s="12"/>
@@ -10383,7 +11036,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -10395,10 +11048,27 @@
         <v>0.18373829204542183</v>
       </c>
       <c r="CC44" s="14"/>
-      <c r="CD44" s="13"/>
-      <c r="CF44" s="12"/>
-      <c r="CH44" s="12"/>
-      <c r="CI44" s="11"/>
+      <c r="CD44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE44" s="10">
+        <v>88</v>
+      </c>
+      <c r="CF44" s="12">
+        <v>88811.428571319979</v>
+      </c>
+      <c r="CG44" s="10">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
+      <c r="CH44" s="12">
+        <f t="shared" si="24"/>
+        <v>-1340.9523809300154</v>
+      </c>
+      <c r="CI44" s="11">
+        <f t="shared" si="25"/>
+        <v>-1.4874286921387718E-2</v>
+      </c>
       <c r="CK44" s="14"/>
       <c r="CL44" s="13"/>
       <c r="CN44" s="12"/>
@@ -10610,7 +11280,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -10622,10 +11292,27 @@
         <v>-0.11683599419452342</v>
       </c>
       <c r="CC45" s="14"/>
-      <c r="CD45" s="13"/>
-      <c r="CF45" s="12"/>
-      <c r="CH45" s="12"/>
-      <c r="CI45" s="11"/>
+      <c r="CD45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE45" s="10">
+        <v>21</v>
+      </c>
+      <c r="CF45" s="12">
+        <v>139443.80952379998</v>
+      </c>
+      <c r="CG45" s="10">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="CH45" s="12">
+        <f t="shared" si="24"/>
+        <v>46719.999999999971</v>
+      </c>
+      <c r="CI45" s="11">
+        <f t="shared" si="25"/>
+        <v>0.50386195562864633</v>
+      </c>
       <c r="CK45" s="14"/>
       <c r="CL45" s="13"/>
       <c r="CN45" s="12"/>
@@ -10837,7 +11524,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -10849,10 +11536,27 @@
         <v>0.20370370370373575</v>
       </c>
       <c r="CC46" s="14"/>
-      <c r="CD46" s="13"/>
-      <c r="CF46" s="12"/>
-      <c r="CH46" s="12"/>
-      <c r="CI46" s="11"/>
+      <c r="CD46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE46" s="10">
+        <v>16</v>
+      </c>
+      <c r="CF46" s="12">
+        <v>186095.23809520004</v>
+      </c>
+      <c r="CG46" s="10">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="CH46" s="12">
+        <f t="shared" si="24"/>
+        <v>74666.666666660036</v>
+      </c>
+      <c r="CI46" s="11">
+        <f t="shared" si="25"/>
+        <v>0.6700854700855996</v>
+      </c>
       <c r="CK46" s="14"/>
       <c r="CL46" s="13"/>
       <c r="CN46" s="12"/>
@@ -11044,7 +11748,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -11056,10 +11760,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC47" s="14"/>
-      <c r="CD47" s="13"/>
+      <c r="CD47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF47" s="12"/>
-      <c r="CH47" s="12"/>
-      <c r="CI47" s="11"/>
+      <c r="CG47" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH47" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI47" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK47" s="14"/>
       <c r="CL47" s="13"/>
       <c r="CN47" s="12"/>
@@ -11271,7 +11987,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -11283,10 +11999,27 @@
         <v>-0.35685071574642124</v>
       </c>
       <c r="CC48" s="14"/>
-      <c r="CD48" s="13"/>
-      <c r="CF48" s="12"/>
-      <c r="CH48" s="12"/>
-      <c r="CI48" s="11"/>
+      <c r="CD48" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE48" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF48" s="12">
+        <v>15380</v>
+      </c>
+      <c r="CG48" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH48" s="12">
+        <f t="shared" si="24"/>
+        <v>9090</v>
+      </c>
+      <c r="CI48" s="11">
+        <f t="shared" si="25"/>
+        <v>1.4451510333863276</v>
+      </c>
       <c r="CK48" s="14"/>
       <c r="CL48" s="13"/>
       <c r="CN48" s="12"/>
@@ -11498,7 +12231,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -11510,10 +12243,27 @@
         <v>-0.50517615176157249</v>
       </c>
       <c r="CC49" s="14"/>
-      <c r="CD49" s="13"/>
-      <c r="CF49" s="12"/>
-      <c r="CH49" s="12"/>
-      <c r="CI49" s="11"/>
+      <c r="CD49" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE49" s="10">
+        <v>8</v>
+      </c>
+      <c r="CF49" s="12">
+        <v>227482.85714284002</v>
+      </c>
+      <c r="CG49" s="10">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="CH49" s="12">
+        <f t="shared" si="24"/>
+        <v>175314.28571428003</v>
+      </c>
+      <c r="CI49" s="11">
+        <f t="shared" si="25"/>
+        <v>3.3605345309168881</v>
+      </c>
       <c r="CK49" s="14"/>
       <c r="CL49" s="13"/>
       <c r="CN49" s="12"/>
@@ -11725,7 +12475,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -11737,10 +12487,27 @@
         <v>-0.33999246136449529</v>
       </c>
       <c r="CC50" s="14"/>
-      <c r="CD50" s="13"/>
-      <c r="CF50" s="12"/>
-      <c r="CH50" s="12"/>
-      <c r="CI50" s="11"/>
+      <c r="CD50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE50" s="10">
+        <v>14</v>
+      </c>
+      <c r="CF50" s="12">
+        <v>210761.90476186998</v>
+      </c>
+      <c r="CG50" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH50" s="12">
+        <f t="shared" si="24"/>
+        <v>43999.999999989988</v>
+      </c>
+      <c r="CI50" s="11">
+        <f t="shared" si="25"/>
+        <v>0.26384922901197227</v>
+      </c>
       <c r="CK50" s="14"/>
       <c r="CL50" s="13"/>
       <c r="CN50" s="12"/>
@@ -11952,7 +12719,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -11964,10 +12731,27 @@
         <v>-0.50697438498605774</v>
       </c>
       <c r="CC51" s="14"/>
-      <c r="CD51" s="13"/>
-      <c r="CF51" s="12"/>
-      <c r="CH51" s="12"/>
-      <c r="CI51" s="11"/>
+      <c r="CD51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE51" s="10">
+        <v>32</v>
+      </c>
+      <c r="CF51" s="12">
+        <v>1105523.8095237699</v>
+      </c>
+      <c r="CG51" s="10">
+        <f t="shared" si="23"/>
+        <v>20</v>
+      </c>
+      <c r="CH51" s="12">
+        <f t="shared" si="24"/>
+        <v>735238.09523806989</v>
+      </c>
+      <c r="CI51" s="11">
+        <f t="shared" si="25"/>
+        <v>1.9855967078189383</v>
+      </c>
       <c r="CK51" s="14"/>
       <c r="CL51" s="13"/>
       <c r="CN51" s="12"/>
@@ -12180,7 +12964,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -12191,13 +12975,28 @@
         <f t="shared" si="22"/>
         <v>-0.35368091226180448</v>
       </c>
-      <c r="CC52" s="9"/>
+      <c r="CC52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CD52" s="9"/>
-      <c r="CE52" s="8"/>
-      <c r="CF52" s="7"/>
-      <c r="CG52" s="27"/>
-      <c r="CH52" s="28"/>
-      <c r="CI52" s="29"/>
+      <c r="CE52" s="8">
+        <v>291</v>
+      </c>
+      <c r="CF52" s="7">
+        <v>2059051.4285707299</v>
+      </c>
+      <c r="CG52" s="27">
+        <f t="shared" si="23"/>
+        <v>79</v>
+      </c>
+      <c r="CH52" s="28">
+        <f t="shared" si="24"/>
+        <v>1086828.0952379201</v>
+      </c>
+      <c r="CI52" s="29">
+        <f t="shared" si="25"/>
+        <v>1.1178790489549779</v>
+      </c>
       <c r="CK52" s="9"/>
       <c r="CL52" s="9"/>
       <c r="CM52" s="8"/>
@@ -12385,7 +13184,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -12396,13 +13195,26 @@
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CC53" s="14"/>
-      <c r="CD53" s="32"/>
+      <c r="CC53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CD53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CE53" s="15"/>
       <c r="CF53" s="33"/>
-      <c r="CG53" s="10"/>
-      <c r="CH53" s="12"/>
-      <c r="CI53" s="11"/>
+      <c r="CG53" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH53" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI53" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK53" s="14"/>
       <c r="CL53" s="32"/>
       <c r="CM53" s="15"/>
@@ -12598,7 +13410,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -12610,12 +13422,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC54" s="14"/>
-      <c r="CD54" s="32"/>
+      <c r="CD54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CE54" s="15"/>
       <c r="CF54" s="33"/>
-      <c r="CG54" s="10"/>
-      <c r="CH54" s="12"/>
-      <c r="CI54" s="11"/>
+      <c r="CG54" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH54" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI54" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK54" s="14"/>
       <c r="CL54" s="32"/>
       <c r="CM54" s="15"/>
@@ -12831,7 +13654,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -12843,10 +13666,27 @@
         <v>-0.28492376209290476</v>
       </c>
       <c r="CC55" s="14"/>
-      <c r="CD55" s="13"/>
-      <c r="CF55" s="12"/>
-      <c r="CH55" s="12"/>
-      <c r="CI55" s="11"/>
+      <c r="CD55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE55" s="10">
+        <v>114</v>
+      </c>
+      <c r="CF55" s="12">
+        <v>112772.38095190004</v>
+      </c>
+      <c r="CG55" s="10">
+        <f t="shared" si="23"/>
+        <v>-4</v>
+      </c>
+      <c r="CH55" s="12">
+        <f t="shared" si="24"/>
+        <v>10624.761904769985</v>
+      </c>
+      <c r="CI55" s="11">
+        <f t="shared" si="25"/>
+        <v>0.10401379889107165</v>
+      </c>
       <c r="CK55" s="14"/>
       <c r="CL55" s="13"/>
       <c r="CN55" s="12"/>
@@ -13058,7 +13898,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -13070,10 +13910,27 @@
         <v>1.3282677695419092E-2</v>
       </c>
       <c r="CC56" s="14"/>
-      <c r="CD56" s="13"/>
-      <c r="CF56" s="12"/>
-      <c r="CH56" s="12"/>
-      <c r="CI56" s="11"/>
+      <c r="CD56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE56" s="10">
+        <v>68</v>
+      </c>
+      <c r="CF56" s="12">
+        <v>77828.571428499999</v>
+      </c>
+      <c r="CG56" s="10">
+        <f t="shared" si="23"/>
+        <v>-21</v>
+      </c>
+      <c r="CH56" s="12">
+        <f t="shared" si="24"/>
+        <v>-22505.714285690003</v>
+      </c>
+      <c r="CI56" s="11">
+        <f t="shared" si="25"/>
+        <v>-0.22430731554514952</v>
+      </c>
       <c r="CK56" s="14"/>
       <c r="CL56" s="13"/>
       <c r="CN56" s="12"/>
@@ -13285,7 +14142,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -13297,10 +14154,27 @@
         <v>-0.21089097572150597</v>
       </c>
       <c r="CC57" s="14"/>
-      <c r="CD57" s="13"/>
-      <c r="CF57" s="12"/>
-      <c r="CH57" s="12"/>
-      <c r="CI57" s="11"/>
+      <c r="CD57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE57" s="10">
+        <v>26</v>
+      </c>
+      <c r="CF57" s="12">
+        <v>161180.95238094003</v>
+      </c>
+      <c r="CG57" s="10">
+        <f t="shared" si="23"/>
+        <v>7</v>
+      </c>
+      <c r="CH57" s="12">
+        <f t="shared" si="24"/>
+        <v>29933.333333340008</v>
+      </c>
+      <c r="CI57" s="11">
+        <f t="shared" si="25"/>
+        <v>0.22806762934483393</v>
+      </c>
       <c r="CK57" s="14"/>
       <c r="CL57" s="13"/>
       <c r="CN57" s="12"/>
@@ -13512,7 +14386,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -13524,10 +14398,27 @@
         <v>-0.76402116402122544</v>
       </c>
       <c r="CC58" s="14"/>
-      <c r="CD58" s="13"/>
-      <c r="CF58" s="12"/>
-      <c r="CH58" s="12"/>
-      <c r="CI58" s="11"/>
+      <c r="CD58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CE58" s="10">
+        <v>9</v>
+      </c>
+      <c r="CF58" s="12">
+        <v>97714.28571425</v>
+      </c>
+      <c r="CG58" s="10">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="CH58" s="12">
+        <f t="shared" si="24"/>
+        <v>55238.095238080001</v>
+      </c>
+      <c r="CI58" s="11">
+        <f t="shared" si="25"/>
+        <v>1.3004484304935418</v>
+      </c>
       <c r="CK58" s="14"/>
       <c r="CL58" s="13"/>
       <c r="CN58" s="12"/>
@@ -13714,7 +14605,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -13726,10 +14617,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC59" s="14"/>
-      <c r="CD59" s="13"/>
+      <c r="CD59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CF59" s="12"/>
-      <c r="CH59" s="12"/>
-      <c r="CI59" s="11"/>
+      <c r="CG59" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH59" s="12">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="CI59" s="11" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CK59" s="14"/>
       <c r="CL59" s="13"/>
       <c r="CN59" s="12"/>
@@ -13936,7 +14839,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -13948,10 +14851,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CC60" s="14"/>
-      <c r="CD60" s="13"/>
-      <c r="CF60" s="12"/>
-      <c r="CH60" s="12"/>
-      <c r="CI60" s="11"/>
+      <c r="CD60" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE60" s="10">
+        <v>2</v>
+      </c>
+      <c r="CF60" s="12">
+        <v>8780</v>
+      </c>
+      <c r="CG60" s="10">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="CH60" s="12">
+        <f t="shared" si="24"/>
+        <v>2490</v>
+      </c>
+      <c r="CI60" s="11">
+        <f t="shared" si="25"/>
+        <v>0.3958664546899841</v>
+      </c>
       <c r="CK60" s="14"/>
       <c r="CL60" s="13"/>
       <c r="CN60" s="12"/>
@@ -14163,7 +15083,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -14175,10 +15095,27 @@
         <v>-0.65357142857144235</v>
       </c>
       <c r="CC61" s="14"/>
-      <c r="CD61" s="13"/>
-      <c r="CF61" s="12"/>
-      <c r="CH61" s="12"/>
-      <c r="CI61" s="11"/>
+      <c r="CD61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CE61" s="10">
+        <v>3</v>
+      </c>
+      <c r="CF61" s="12">
+        <v>91142.857142840003</v>
+      </c>
+      <c r="CG61" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="CH61" s="12">
+        <f t="shared" si="24"/>
+        <v>8000</v>
+      </c>
+      <c r="CI61" s="11">
+        <f t="shared" si="25"/>
+        <v>9.62199312714975E-2</v>
+      </c>
       <c r="CK61" s="14"/>
       <c r="CL61" s="13"/>
       <c r="CN61" s="12"/>
@@ -14390,7 +15327,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -14402,10 +15339,27 @@
         <v>-0.19971919971913504</v>
       </c>
       <c r="CC62" s="14"/>
-      <c r="CD62" s="13"/>
-      <c r="CF62" s="12"/>
-      <c r="CH62" s="12"/>
-      <c r="CI62" s="11"/>
+      <c r="CD62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE62" s="10">
+        <v>29</v>
+      </c>
+      <c r="CF62" s="12">
+        <v>380761.90476187004</v>
+      </c>
+      <c r="CG62" s="10">
+        <f t="shared" si="23"/>
+        <v>19</v>
+      </c>
+      <c r="CH62" s="12">
+        <f t="shared" si="24"/>
+        <v>163619.04761903003</v>
+      </c>
+      <c r="CI62" s="11">
+        <f t="shared" si="25"/>
+        <v>0.75350877192980292</v>
+      </c>
       <c r="CK62" s="14"/>
       <c r="CL62" s="13"/>
       <c r="CN62" s="12"/>
@@ -14617,7 +15571,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -14629,10 +15583,27 @@
         <v>-0.36087127603525215</v>
       </c>
       <c r="CC63" s="14"/>
-      <c r="CD63" s="13"/>
-      <c r="CF63" s="12"/>
-      <c r="CH63" s="12"/>
-      <c r="CI63" s="11"/>
+      <c r="CD63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CE63" s="10">
+        <v>18</v>
+      </c>
+      <c r="CF63" s="12">
+        <v>585904.76190473</v>
+      </c>
+      <c r="CG63" s="10">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="CH63" s="12">
+        <f t="shared" si="24"/>
+        <v>129563.80952379992</v>
+      </c>
+      <c r="CI63" s="11">
+        <f t="shared" si="25"/>
+        <v>0.28391887435876384</v>
+      </c>
       <c r="CK63" s="14"/>
       <c r="CL63" s="13"/>
       <c r="CN63" s="12"/>
@@ -14845,7 +15816,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -14856,13 +15827,28 @@
         <f t="shared" si="22"/>
         <v>-0.371875469355818</v>
       </c>
-      <c r="CC64" s="9"/>
+      <c r="CC64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CD64" s="9"/>
-      <c r="CE64" s="8"/>
-      <c r="CF64" s="7"/>
-      <c r="CG64" s="27"/>
-      <c r="CH64" s="28"/>
-      <c r="CI64" s="29"/>
+      <c r="CE64" s="8">
+        <v>269</v>
+      </c>
+      <c r="CF64" s="7">
+        <v>1516085.71428503</v>
+      </c>
+      <c r="CG64" s="27">
+        <f t="shared" si="23"/>
+        <v>11</v>
+      </c>
+      <c r="CH64" s="28">
+        <f t="shared" si="24"/>
+        <v>376963.33333332976</v>
+      </c>
+      <c r="CI64" s="29">
+        <f t="shared" si="25"/>
+        <v>0.33092434986519093</v>
+      </c>
       <c r="CK64" s="9"/>
       <c r="CL64" s="9"/>
       <c r="CM64" s="8"/>
@@ -15079,7 +16065,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -15090,13 +16076,28 @@
         <f t="shared" si="22"/>
         <v>-0.34719833949510465</v>
       </c>
-      <c r="CC65" s="4"/>
+      <c r="CC65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CD65" s="4"/>
-      <c r="CE65" s="3"/>
-      <c r="CF65" s="2"/>
-      <c r="CG65" s="6"/>
-      <c r="CH65" s="5"/>
-      <c r="CI65" s="30"/>
+      <c r="CE65" s="3">
+        <v>2305</v>
+      </c>
+      <c r="CF65" s="2">
+        <v>21361582.380947892</v>
+      </c>
+      <c r="CG65" s="6">
+        <f t="shared" si="23"/>
+        <v>412</v>
+      </c>
+      <c r="CH65" s="5">
+        <f t="shared" si="24"/>
+        <v>10239397.619047023</v>
+      </c>
+      <c r="CI65" s="30">
+        <f t="shared" si="25"/>
+        <v>0.92062826128569275</v>
+      </c>
       <c r="CK65" s="4"/>
       <c r="CL65" s="4"/>
       <c r="CM65" s="3"/>
@@ -15120,7 +16121,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="108" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15132,7 +16133,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15144,7 +16145,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15156,7 +16157,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15168,7 +16169,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15180,7 +16181,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15192,7 +16193,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15204,7 +16205,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15216,7 +16217,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15228,7 +16229,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15240,19 +16241,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{DDBF6E41-C389-2344-92BB-6A5E3B3BC008}">
-            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>CG5:CI65</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15264,7 +16253,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -15275,6 +16264,18 @@
           </x14:cfRule>
           <xm:sqref>CW5:CY65</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>CG5:CI65</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE5153-9DA8-AD4E-9EFD-EC02B1CCAF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490BD7D8-3A23-4342-8E84-D2A47E139A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="13840" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -559,12 +559,7 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1885,10 +1880,13 @@
       <c r="CD6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CE6" s="15">
+        <v>15</v>
+      </c>
       <c r="CF6" s="33"/>
       <c r="CG6" s="10">
         <f t="shared" si="23"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="CH6" s="12">
         <f t="shared" si="24"/>
@@ -4774,11 +4772,13 @@
       <c r="CD18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE18" s="15"/>
+      <c r="CE18" s="15">
+        <v>13</v>
+      </c>
       <c r="CF18" s="33"/>
       <c r="CG18" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="CH18" s="12">
         <f t="shared" si="24"/>
@@ -7681,11 +7681,13 @@
       <c r="CD30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE30" s="15"/>
+      <c r="CE30" s="15">
+        <v>3</v>
+      </c>
       <c r="CF30" s="33"/>
       <c r="CG30" s="10">
         <f t="shared" si="23"/>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CH30" s="12">
         <f t="shared" si="24"/>
@@ -10563,11 +10565,13 @@
       <c r="CD42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE42" s="15"/>
+      <c r="CE42" s="15">
+        <v>7</v>
+      </c>
       <c r="CF42" s="33"/>
       <c r="CG42" s="10">
         <f t="shared" si="23"/>
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="CH42" s="12">
         <f t="shared" si="24"/>
@@ -16241,6 +16245,18 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>CG5:CI65</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
@@ -16264,18 +16280,6 @@
           </x14:cfRule>
           <xm:sqref>CW5:CY65</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
-            <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFF0000"/>
-              </font>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>CG5:CI65</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490BD7D8-3A23-4342-8E84-D2A47E139A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE836E5-63B5-A549-AD2F-CD6D457EF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13840" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5400" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="46">
   <si>
     <t>總計</t>
   </si>
@@ -228,6 +228,14 @@
   </si>
   <si>
     <t>03/08~03/14</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/15~03/21</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1082,7 +1090,11 @@
       </c>
       <c r="CD1" s="26"/>
       <c r="CF1" s="25"/>
-      <c r="CK1" s="26"/>
+      <c r="CK1" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="CL1" s="26"/>
+      <c r="CN1" s="25"/>
       <c r="CS1" s="26"/>
     </row>
     <row r="2" spans="1:103" s="20" customFormat="1" ht="18">
@@ -1156,7 +1168,9 @@
       <c r="CG2" s="21"/>
       <c r="CH2" s="21"/>
       <c r="CI2" s="21"/>
-      <c r="CK2" s="22"/>
+      <c r="CK2" s="20" t="s">
+        <v>45</v>
+      </c>
       <c r="CL2" s="21"/>
       <c r="CN2" s="21"/>
       <c r="CO2" s="21"/>
@@ -1409,13 +1423,27 @@
       <c r="CI4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="CK4" s="19"/>
-      <c r="CL4" s="19"/>
-      <c r="CM4" s="18"/>
-      <c r="CN4" s="17"/>
-      <c r="CO4" s="16"/>
-      <c r="CP4" s="16"/>
-      <c r="CQ4" s="16"/>
+      <c r="CK4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CL4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CM4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CN4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CO4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CQ4" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="CS4" s="19"/>
       <c r="CT4" s="19"/>
       <c r="CU4" s="18"/>
@@ -1669,13 +1697,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CJ5" s="38"/>
-      <c r="CK5" s="14"/>
-      <c r="CL5" s="32"/>
-      <c r="CM5" s="15"/>
+      <c r="CK5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CL5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM5" s="15">
+        <v>6082</v>
+      </c>
       <c r="CN5" s="33"/>
-      <c r="CO5" s="10"/>
-      <c r="CP5" s="12"/>
-      <c r="CQ5" s="11"/>
+      <c r="CO5" s="10">
+        <f t="shared" ref="CO5:CO65" si="26">CM5-CE5</f>
+        <v>-404</v>
+      </c>
+      <c r="CP5" s="12">
+        <f t="shared" ref="CP5:CP65" si="27">CN5-CF5</f>
+        <v>0</v>
+      </c>
+      <c r="CQ5" s="11" t="e">
+        <f t="shared" ref="CQ5:CQ65" si="28">(CN5-CF5)/CF5</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CR5" s="38"/>
       <c r="CS5" s="14"/>
       <c r="CT5" s="32"/>
@@ -1897,11 +1940,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK6" s="14"/>
-      <c r="CL6" s="32"/>
+      <c r="CL6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CN6" s="33"/>
-      <c r="CO6" s="10"/>
-      <c r="CP6" s="12"/>
-      <c r="CQ6" s="11"/>
+      <c r="CO6" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP6" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ6" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS6" s="14"/>
       <c r="CT6" s="32"/>
       <c r="CV6" s="33"/>
@@ -2143,10 +2197,27 @@
         <v>-3.9739672708067282E-2</v>
       </c>
       <c r="CK7" s="14"/>
-      <c r="CL7" s="13"/>
-      <c r="CN7" s="12"/>
-      <c r="CP7" s="12"/>
-      <c r="CQ7" s="11"/>
+      <c r="CL7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM7" s="10">
+        <v>171</v>
+      </c>
+      <c r="CN7" s="12">
+        <v>178639.99999928992</v>
+      </c>
+      <c r="CO7" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP7" s="12">
+        <f t="shared" si="27"/>
+        <v>-39869.523809400009</v>
+      </c>
+      <c r="CQ7" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.18246126353882261</v>
+      </c>
       <c r="CS7" s="14"/>
       <c r="CT7" s="13"/>
       <c r="CV7" s="12"/>
@@ -2387,10 +2458,27 @@
         <v>-9.1248074625875322E-2</v>
       </c>
       <c r="CK8" s="14"/>
-      <c r="CL8" s="13"/>
-      <c r="CN8" s="12"/>
-      <c r="CP8" s="12"/>
-      <c r="CQ8" s="11"/>
+      <c r="CL8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM8" s="10">
+        <v>217</v>
+      </c>
+      <c r="CN8" s="12">
+        <v>242963.80952367</v>
+      </c>
+      <c r="CO8" s="10">
+        <f t="shared" si="26"/>
+        <v>-16</v>
+      </c>
+      <c r="CP8" s="12">
+        <f t="shared" si="27"/>
+        <v>-37419.047619019926</v>
+      </c>
+      <c r="CQ8" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.13345697379771318</v>
+      </c>
       <c r="CS8" s="14"/>
       <c r="CT8" s="13"/>
       <c r="CV8" s="12"/>
@@ -2631,10 +2719,27 @@
         <v>2.0457961621817462E-2</v>
       </c>
       <c r="CK9" s="14"/>
-      <c r="CL9" s="13"/>
-      <c r="CN9" s="12"/>
-      <c r="CP9" s="12"/>
-      <c r="CQ9" s="11"/>
+      <c r="CL9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM9" s="10">
+        <v>70</v>
+      </c>
+      <c r="CN9" s="12">
+        <v>455047.61904759996</v>
+      </c>
+      <c r="CO9" s="10">
+        <f t="shared" si="26"/>
+        <v>-5</v>
+      </c>
+      <c r="CP9" s="12">
+        <f t="shared" si="27"/>
+        <v>-42809.523809530016</v>
+      </c>
+      <c r="CQ9" s="11">
+        <f t="shared" si="28"/>
+        <v>-8.5987565758025214E-2</v>
+      </c>
       <c r="CS9" s="14"/>
       <c r="CT9" s="13"/>
       <c r="CV9" s="12"/>
@@ -2875,10 +2980,27 @@
         <v>0.13501760198801455</v>
       </c>
       <c r="CK10" s="14"/>
-      <c r="CL10" s="13"/>
-      <c r="CN10" s="12"/>
-      <c r="CP10" s="12"/>
-      <c r="CQ10" s="11"/>
+      <c r="CL10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM10" s="10">
+        <v>35</v>
+      </c>
+      <c r="CN10" s="12">
+        <v>483333.33333326003</v>
+      </c>
+      <c r="CO10" s="10">
+        <f t="shared" si="26"/>
+        <v>-4</v>
+      </c>
+      <c r="CP10" s="12">
+        <f t="shared" si="27"/>
+        <v>-38666.666666670004</v>
+      </c>
+      <c r="CQ10" s="11">
+        <f t="shared" si="28"/>
+        <v>-7.407407407409039E-2</v>
+      </c>
       <c r="CS10" s="14"/>
       <c r="CT10" s="13"/>
       <c r="CV10" s="12"/>
@@ -3094,10 +3216,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK11" s="14"/>
-      <c r="CL11" s="13"/>
+      <c r="CL11" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN11" s="12"/>
-      <c r="CP11" s="12"/>
-      <c r="CQ11" s="11"/>
+      <c r="CO11" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP11" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ11" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS11" s="14"/>
       <c r="CT11" s="13"/>
       <c r="CV11" s="12"/>
@@ -3338,10 +3472,27 @@
         <v>-5.84315735520246E-2</v>
       </c>
       <c r="CK12" s="14"/>
-      <c r="CL12" s="13"/>
-      <c r="CN12" s="12"/>
-      <c r="CP12" s="12"/>
-      <c r="CQ12" s="11"/>
+      <c r="CL12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM12" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN12" s="12">
+        <v>64090</v>
+      </c>
+      <c r="CO12" s="10">
+        <f t="shared" si="26"/>
+        <v>5</v>
+      </c>
+      <c r="CP12" s="12">
+        <f t="shared" si="27"/>
+        <v>27350</v>
+      </c>
+      <c r="CQ12" s="11">
+        <f t="shared" si="28"/>
+        <v>0.74442025040827431</v>
+      </c>
       <c r="CS12" s="14"/>
       <c r="CT12" s="13"/>
       <c r="CV12" s="12"/>
@@ -3582,10 +3733,27 @@
         <v>0.16751719189620934</v>
       </c>
       <c r="CK13" s="14"/>
-      <c r="CL13" s="13"/>
-      <c r="CN13" s="12"/>
-      <c r="CP13" s="12"/>
-      <c r="CQ13" s="11"/>
+      <c r="CL13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM13" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>341723.80952377006</v>
+      </c>
+      <c r="CO13" s="10">
+        <f t="shared" si="26"/>
+        <v>-10</v>
+      </c>
+      <c r="CP13" s="12">
+        <f t="shared" si="27"/>
+        <v>-347895.23809520988</v>
+      </c>
+      <c r="CQ13" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.50447452009391824</v>
+      </c>
       <c r="CS13" s="14"/>
       <c r="CT13" s="13"/>
       <c r="CV13" s="12"/>
@@ -3826,10 +3994,27 @@
         <v>-3.1286756057433383E-2</v>
       </c>
       <c r="CK14" s="14"/>
-      <c r="CL14" s="13"/>
-      <c r="CN14" s="12"/>
-      <c r="CP14" s="12"/>
-      <c r="CQ14" s="11"/>
+      <c r="CL14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM14" s="10">
+        <v>24</v>
+      </c>
+      <c r="CN14" s="12">
+        <v>438571.42857138999</v>
+      </c>
+      <c r="CO14" s="10">
+        <f t="shared" si="26"/>
+        <v>-19</v>
+      </c>
+      <c r="CP14" s="12">
+        <f t="shared" si="27"/>
+        <v>-345809.52380948002</v>
+      </c>
+      <c r="CQ14" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.44086935405535715</v>
+      </c>
       <c r="CS14" s="14"/>
       <c r="CT14" s="13"/>
       <c r="CV14" s="12"/>
@@ -4070,10 +4255,27 @@
         <v>1.5411748666271627</v>
       </c>
       <c r="CK15" s="14"/>
-      <c r="CL15" s="13"/>
-      <c r="CN15" s="12"/>
-      <c r="CP15" s="12"/>
-      <c r="CQ15" s="11"/>
+      <c r="CL15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM15" s="10">
+        <v>115</v>
+      </c>
+      <c r="CN15" s="12">
+        <v>4159523.8095237301</v>
+      </c>
+      <c r="CO15" s="10">
+        <f t="shared" si="26"/>
+        <v>-44</v>
+      </c>
+      <c r="CP15" s="12">
+        <f t="shared" si="27"/>
+        <v>-1964707.6190476301</v>
+      </c>
+      <c r="CQ15" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.32080884629566497</v>
+      </c>
       <c r="CS15" s="14"/>
       <c r="CT15" s="13"/>
       <c r="CV15" s="12"/>
@@ -4314,13 +4516,28 @@
         <f t="shared" si="25"/>
         <v>0.71634137443294743</v>
       </c>
-      <c r="CK16" s="9"/>
+      <c r="CK16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CL16" s="9"/>
-      <c r="CM16" s="8"/>
-      <c r="CN16" s="7"/>
-      <c r="CO16" s="27"/>
-      <c r="CP16" s="28"/>
-      <c r="CQ16" s="29"/>
+      <c r="CM16" s="8">
+        <v>651</v>
+      </c>
+      <c r="CN16" s="7">
+        <v>6363893.8095227107</v>
+      </c>
+      <c r="CO16" s="27">
+        <f t="shared" si="26"/>
+        <v>-108</v>
+      </c>
+      <c r="CP16" s="28">
+        <f t="shared" si="27"/>
+        <v>-2789827.1428569388</v>
+      </c>
+      <c r="CQ16" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.30477520096695548</v>
+      </c>
       <c r="CS16" s="9"/>
       <c r="CT16" s="9"/>
       <c r="CU16" s="8"/>
@@ -4562,13 +4779,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK17" s="14"/>
-      <c r="CL17" s="32"/>
-      <c r="CM17" s="15"/>
+      <c r="CK17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CL17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM17" s="15">
+        <v>5349</v>
+      </c>
       <c r="CN17" s="33"/>
-      <c r="CO17" s="10"/>
-      <c r="CP17" s="12"/>
-      <c r="CQ17" s="11"/>
+      <c r="CO17" s="10">
+        <f t="shared" si="26"/>
+        <v>-193</v>
+      </c>
+      <c r="CP17" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ17" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS17" s="14"/>
       <c r="CT17" s="32"/>
       <c r="CU17" s="15"/>
@@ -4789,12 +5021,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK18" s="14"/>
-      <c r="CL18" s="32"/>
+      <c r="CL18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM18" s="15"/>
       <c r="CN18" s="33"/>
-      <c r="CO18" s="10"/>
-      <c r="CP18" s="12"/>
-      <c r="CQ18" s="11"/>
+      <c r="CO18" s="10">
+        <f t="shared" si="26"/>
+        <v>-13</v>
+      </c>
+      <c r="CP18" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ18" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS18" s="14"/>
       <c r="CT18" s="32"/>
       <c r="CU18" s="15"/>
@@ -5037,10 +5280,27 @@
         <v>0.83226108505740837</v>
       </c>
       <c r="CK19" s="14"/>
-      <c r="CL19" s="13"/>
-      <c r="CN19" s="12"/>
-      <c r="CP19" s="12"/>
-      <c r="CQ19" s="11"/>
+      <c r="CL19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM19" s="10">
+        <v>211</v>
+      </c>
+      <c r="CN19" s="12">
+        <v>232219.04761820004</v>
+      </c>
+      <c r="CO19" s="10">
+        <f t="shared" si="26"/>
+        <v>7</v>
+      </c>
+      <c r="CP19" s="12">
+        <f t="shared" si="27"/>
+        <v>16041.904761850077</v>
+      </c>
+      <c r="CQ19" s="11">
+        <f t="shared" si="28"/>
+        <v>7.4207219828554896E-2</v>
+      </c>
       <c r="CS19" s="14"/>
       <c r="CT19" s="13"/>
       <c r="CV19" s="12"/>
@@ -5281,10 +5541,27 @@
         <v>0.48836853949280895</v>
       </c>
       <c r="CK20" s="14"/>
-      <c r="CL20" s="13"/>
-      <c r="CN20" s="12"/>
-      <c r="CP20" s="12"/>
-      <c r="CQ20" s="11"/>
+      <c r="CL20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM20" s="10">
+        <v>219</v>
+      </c>
+      <c r="CN20" s="12">
+        <v>218466.66666655001</v>
+      </c>
+      <c r="CO20" s="10">
+        <f t="shared" si="26"/>
+        <v>-34</v>
+      </c>
+      <c r="CP20" s="12">
+        <f t="shared" si="27"/>
+        <v>-87663.809523779986</v>
+      </c>
+      <c r="CQ20" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.28636093542440028</v>
+      </c>
       <c r="CS20" s="14"/>
       <c r="CT20" s="13"/>
       <c r="CV20" s="12"/>
@@ -5525,10 +5802,27 @@
         <v>-0.25263614666959294</v>
       </c>
       <c r="CK21" s="14"/>
-      <c r="CL21" s="13"/>
-      <c r="CN21" s="12"/>
-      <c r="CP21" s="12"/>
-      <c r="CQ21" s="11"/>
+      <c r="CL21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM21" s="10">
+        <v>61</v>
+      </c>
+      <c r="CN21" s="12">
+        <v>369134.28571425995</v>
+      </c>
+      <c r="CO21" s="10">
+        <f t="shared" si="26"/>
+        <v>7</v>
+      </c>
+      <c r="CP21" s="12">
+        <f t="shared" si="27"/>
+        <v>41077.14285713993</v>
+      </c>
+      <c r="CQ21" s="11">
+        <f t="shared" si="28"/>
+        <v>0.12521337746037256</v>
+      </c>
       <c r="CS21" s="14"/>
       <c r="CT21" s="13"/>
       <c r="CV21" s="12"/>
@@ -5769,10 +6063,27 @@
         <v>0.11880096980384325</v>
       </c>
       <c r="CK22" s="14"/>
-      <c r="CL22" s="13"/>
-      <c r="CN22" s="12"/>
-      <c r="CP22" s="12"/>
-      <c r="CQ22" s="11"/>
+      <c r="CL22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM22" s="10">
+        <v>48</v>
+      </c>
+      <c r="CN22" s="12">
+        <v>595904.76190469007</v>
+      </c>
+      <c r="CO22" s="10">
+        <f t="shared" si="26"/>
+        <v>9</v>
+      </c>
+      <c r="CP22" s="12">
+        <f t="shared" si="27"/>
+        <v>112476.19047618011</v>
+      </c>
+      <c r="CQ22" s="11">
+        <f t="shared" si="28"/>
+        <v>0.23266351457841633</v>
+      </c>
       <c r="CS22" s="14"/>
       <c r="CT22" s="13"/>
       <c r="CV22" s="12"/>
@@ -6003,10 +6314,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK23" s="14"/>
-      <c r="CL23" s="13"/>
-      <c r="CN23" s="12"/>
-      <c r="CP23" s="12"/>
-      <c r="CQ23" s="11"/>
+      <c r="CL23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CM23" s="10">
+        <v>16</v>
+      </c>
+      <c r="CN23" s="12">
+        <v>90340</v>
+      </c>
+      <c r="CO23" s="10">
+        <f t="shared" si="26"/>
+        <v>14</v>
+      </c>
+      <c r="CP23" s="12">
+        <f t="shared" si="27"/>
+        <v>78825.714285719994</v>
+      </c>
+      <c r="CQ23" s="11">
+        <f t="shared" si="28"/>
+        <v>6.8459057071999236</v>
+      </c>
       <c r="CS23" s="14"/>
       <c r="CT23" s="13"/>
       <c r="CV23" s="12"/>
@@ -6247,10 +6575,22 @@
         <v>1.2908811924594477</v>
       </c>
       <c r="CK24" s="14"/>
-      <c r="CL24" s="13"/>
+      <c r="CL24" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CN24" s="12"/>
-      <c r="CP24" s="12"/>
-      <c r="CQ24" s="11"/>
+      <c r="CO24" s="10">
+        <f t="shared" si="26"/>
+        <v>-19</v>
+      </c>
+      <c r="CP24" s="12">
+        <f t="shared" si="27"/>
+        <v>-104510</v>
+      </c>
+      <c r="CQ24" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS24" s="14"/>
       <c r="CT24" s="13"/>
       <c r="CV24" s="12"/>
@@ -6491,10 +6831,27 @@
         <v>0.83569942797729235</v>
       </c>
       <c r="CK25" s="14"/>
-      <c r="CL25" s="13"/>
-      <c r="CN25" s="12"/>
-      <c r="CP25" s="12"/>
-      <c r="CQ25" s="11"/>
+      <c r="CL25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM25" s="10">
+        <v>5</v>
+      </c>
+      <c r="CN25" s="12">
+        <v>139528.57142856001</v>
+      </c>
+      <c r="CO25" s="10">
+        <f t="shared" si="26"/>
+        <v>-4</v>
+      </c>
+      <c r="CP25" s="12">
+        <f t="shared" si="27"/>
+        <v>-196666.66666665999</v>
+      </c>
+      <c r="CQ25" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.5849775498930726</v>
+      </c>
       <c r="CS25" s="14"/>
       <c r="CT25" s="13"/>
       <c r="CV25" s="12"/>
@@ -6735,10 +7092,27 @@
         <v>0.58923788653517695</v>
       </c>
       <c r="CK26" s="14"/>
-      <c r="CL26" s="13"/>
-      <c r="CN26" s="12"/>
-      <c r="CP26" s="12"/>
-      <c r="CQ26" s="11"/>
+      <c r="CL26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM26" s="10">
+        <v>39</v>
+      </c>
+      <c r="CN26" s="12">
+        <v>642761.90476185002</v>
+      </c>
+      <c r="CO26" s="10">
+        <f t="shared" si="26"/>
+        <v>5</v>
+      </c>
+      <c r="CP26" s="12">
+        <f t="shared" si="27"/>
+        <v>21142.857142879977</v>
+      </c>
+      <c r="CQ26" s="11">
+        <f t="shared" si="28"/>
+        <v>3.4012563199060437E-2</v>
+      </c>
       <c r="CS26" s="14"/>
       <c r="CT26" s="13"/>
       <c r="CV26" s="12"/>
@@ -6979,10 +7353,27 @@
         <v>6.7272727272728154</v>
       </c>
       <c r="CK27" s="14"/>
-      <c r="CL27" s="13"/>
-      <c r="CN27" s="12"/>
-      <c r="CP27" s="12"/>
-      <c r="CQ27" s="11"/>
+      <c r="CL27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM27" s="10">
+        <v>188</v>
+      </c>
+      <c r="CN27" s="12">
+        <v>6769714.2857141895</v>
+      </c>
+      <c r="CO27" s="10">
+        <f t="shared" si="26"/>
+        <v>43</v>
+      </c>
+      <c r="CP27" s="12">
+        <f t="shared" si="27"/>
+        <v>1661619.0476190401</v>
+      </c>
+      <c r="CQ27" s="11">
+        <f t="shared" si="28"/>
+        <v>0.32529132096579144</v>
+      </c>
       <c r="CS27" s="14"/>
       <c r="CT27" s="13"/>
       <c r="CV27" s="12"/>
@@ -7223,13 +7614,28 @@
         <f t="shared" si="25"/>
         <v>2.0358396968594983</v>
       </c>
-      <c r="CK28" s="9"/>
+      <c r="CK28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CL28" s="9"/>
-      <c r="CM28" s="8"/>
-      <c r="CN28" s="7"/>
-      <c r="CO28" s="27"/>
-      <c r="CP28" s="28"/>
-      <c r="CQ28" s="29"/>
+      <c r="CM28" s="8">
+        <v>787</v>
+      </c>
+      <c r="CN28" s="7">
+        <v>9058069.5238083005</v>
+      </c>
+      <c r="CO28" s="27">
+        <f t="shared" si="26"/>
+        <v>28</v>
+      </c>
+      <c r="CP28" s="28">
+        <f t="shared" si="27"/>
+        <v>1542342.3809523713</v>
+      </c>
+      <c r="CQ28" s="29">
+        <f t="shared" si="28"/>
+        <v>0.20521532403134726</v>
+      </c>
       <c r="CS28" s="9"/>
       <c r="CT28" s="9"/>
       <c r="CU28" s="8"/>
@@ -7471,13 +7877,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK29" s="14"/>
-      <c r="CL29" s="32"/>
-      <c r="CM29" s="15"/>
+      <c r="CK29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CL29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM29" s="15">
+        <v>3439</v>
+      </c>
       <c r="CN29" s="33"/>
-      <c r="CO29" s="10"/>
-      <c r="CP29" s="12"/>
-      <c r="CQ29" s="11"/>
+      <c r="CO29" s="10">
+        <f t="shared" si="26"/>
+        <v>-63</v>
+      </c>
+      <c r="CP29" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ29" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS29" s="14"/>
       <c r="CT29" s="32"/>
       <c r="CU29" s="15"/>
@@ -7698,12 +8119,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK30" s="14"/>
-      <c r="CL30" s="32"/>
+      <c r="CL30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM30" s="15"/>
       <c r="CN30" s="33"/>
-      <c r="CO30" s="10"/>
-      <c r="CP30" s="12"/>
-      <c r="CQ30" s="11"/>
+      <c r="CO30" s="10">
+        <f t="shared" si="26"/>
+        <v>-3</v>
+      </c>
+      <c r="CP30" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ30" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS30" s="14"/>
       <c r="CT30" s="32"/>
       <c r="CU30" s="15"/>
@@ -7946,10 +8378,27 @@
         <v>-0.25559529515919094</v>
       </c>
       <c r="CK31" s="14"/>
-      <c r="CL31" s="13"/>
-      <c r="CN31" s="12"/>
-      <c r="CP31" s="12"/>
-      <c r="CQ31" s="11"/>
+      <c r="CL31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM31" s="10">
+        <v>71</v>
+      </c>
+      <c r="CN31" s="12">
+        <v>66044.761904450017</v>
+      </c>
+      <c r="CO31" s="10">
+        <f t="shared" si="26"/>
+        <v>-16</v>
+      </c>
+      <c r="CP31" s="12">
+        <f t="shared" si="27"/>
+        <v>-10865.714285640017</v>
+      </c>
+      <c r="CQ31" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.14127742830228468</v>
+      </c>
       <c r="CS31" s="14"/>
       <c r="CT31" s="13"/>
       <c r="CV31" s="12"/>
@@ -8190,10 +8639,27 @@
         <v>2.382807130273138E-3</v>
       </c>
       <c r="CK32" s="14"/>
-      <c r="CL32" s="13"/>
-      <c r="CN32" s="12"/>
-      <c r="CP32" s="12"/>
-      <c r="CQ32" s="11"/>
+      <c r="CL32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM32" s="10">
+        <v>77</v>
+      </c>
+      <c r="CN32" s="12">
+        <v>78773.333333229995</v>
+      </c>
+      <c r="CO32" s="10">
+        <f t="shared" si="26"/>
+        <v>-3</v>
+      </c>
+      <c r="CP32" s="12">
+        <f t="shared" si="27"/>
+        <v>-4560</v>
+      </c>
+      <c r="CQ32" s="11">
+        <f t="shared" si="28"/>
+        <v>-5.4720000000067853E-2</v>
+      </c>
       <c r="CS32" s="14"/>
       <c r="CT32" s="13"/>
       <c r="CV32" s="12"/>
@@ -8434,10 +8900,27 @@
         <v>-0.46149294492488274</v>
       </c>
       <c r="CK33" s="14"/>
-      <c r="CL33" s="13"/>
-      <c r="CN33" s="12"/>
-      <c r="CP33" s="12"/>
-      <c r="CQ33" s="11"/>
+      <c r="CL33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM33" s="10">
+        <v>25</v>
+      </c>
+      <c r="CN33" s="12">
+        <v>172619.04761904001</v>
+      </c>
+      <c r="CO33" s="10">
+        <f t="shared" si="26"/>
+        <v>6</v>
+      </c>
+      <c r="CP33" s="12">
+        <f t="shared" si="27"/>
+        <v>59942.857142860012</v>
+      </c>
+      <c r="CQ33" s="11">
+        <f t="shared" si="28"/>
+        <v>0.53199222381885614</v>
+      </c>
       <c r="CS33" s="14"/>
       <c r="CT33" s="13"/>
       <c r="CV33" s="12"/>
@@ -8678,10 +9161,27 @@
         <v>-0.54887820512820562</v>
       </c>
       <c r="CK34" s="14"/>
-      <c r="CL34" s="13"/>
-      <c r="CN34" s="12"/>
-      <c r="CP34" s="12"/>
-      <c r="CQ34" s="11"/>
+      <c r="CL34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM34" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN34" s="12">
+        <v>127142.85714282002</v>
+      </c>
+      <c r="CO34" s="10">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="CP34" s="12">
+        <f t="shared" si="27"/>
+        <v>19904.761904750019</v>
+      </c>
+      <c r="CQ34" s="11">
+        <f t="shared" si="28"/>
+        <v>0.18561278863225966</v>
+      </c>
       <c r="CS34" s="14"/>
       <c r="CT34" s="13"/>
       <c r="CV34" s="12"/>
@@ -8902,10 +9402,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK35" s="14"/>
-      <c r="CL35" s="13"/>
+      <c r="CL35" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN35" s="12"/>
-      <c r="CP35" s="12"/>
-      <c r="CQ35" s="11"/>
+      <c r="CO35" s="10">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="CP35" s="12">
+        <f t="shared" si="27"/>
+        <v>-8857.1428571399993</v>
+      </c>
+      <c r="CQ35" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS35" s="14"/>
       <c r="CT35" s="13"/>
       <c r="CV35" s="12"/>
@@ -9136,10 +9648,27 @@
         <v>7.8098471993261484E-3</v>
       </c>
       <c r="CK36" s="14"/>
-      <c r="CL36" s="13"/>
-      <c r="CN36" s="12"/>
-      <c r="CP36" s="12"/>
-      <c r="CQ36" s="11"/>
+      <c r="CL36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM36" s="10">
+        <v>2</v>
+      </c>
+      <c r="CN36" s="12">
+        <v>8180</v>
+      </c>
+      <c r="CO36" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP36" s="12">
+        <f t="shared" si="27"/>
+        <v>-300</v>
+      </c>
+      <c r="CQ36" s="11">
+        <f t="shared" si="28"/>
+        <v>-3.5377358490566037E-2</v>
+      </c>
       <c r="CS36" s="14"/>
       <c r="CT36" s="13"/>
       <c r="CV36" s="12"/>
@@ -9341,7 +9870,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="26">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="29">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -9375,10 +9904,27 @@
         <v>2.2299034784197485</v>
       </c>
       <c r="CK37" s="14"/>
-      <c r="CL37" s="13"/>
-      <c r="CN37" s="12"/>
-      <c r="CP37" s="12"/>
-      <c r="CQ37" s="11"/>
+      <c r="CL37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM37" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN37" s="12">
+        <v>47047.619047610002</v>
+      </c>
+      <c r="CO37" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP37" s="12">
+        <f t="shared" si="27"/>
+        <v>-37406.666666660007</v>
+      </c>
+      <c r="CQ37" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.44292206547357615</v>
+      </c>
       <c r="CS37" s="14"/>
       <c r="CT37" s="13"/>
       <c r="CV37" s="12"/>
@@ -9585,7 +10131,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -9619,10 +10165,27 @@
         <v>0.16924027177267556</v>
       </c>
       <c r="CK38" s="14"/>
-      <c r="CL38" s="13"/>
-      <c r="CN38" s="12"/>
-      <c r="CP38" s="12"/>
-      <c r="CQ38" s="11"/>
+      <c r="CL38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM38" s="10">
+        <v>14</v>
+      </c>
+      <c r="CN38" s="12">
+        <v>246190.47619043995</v>
+      </c>
+      <c r="CO38" s="10">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="CP38" s="12">
+        <f t="shared" si="27"/>
+        <v>65904.761904759944</v>
+      </c>
+      <c r="CQ38" s="11">
+        <f t="shared" si="28"/>
+        <v>0.36555731642900741</v>
+      </c>
       <c r="CS38" s="14"/>
       <c r="CT38" s="13"/>
       <c r="CV38" s="12"/>
@@ -9829,7 +10392,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -9863,10 +10426,27 @@
         <v>0.19756424211114065</v>
       </c>
       <c r="CK39" s="14"/>
-      <c r="CL39" s="13"/>
-      <c r="CN39" s="12"/>
-      <c r="CP39" s="12"/>
-      <c r="CQ39" s="11"/>
+      <c r="CL39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM39" s="10">
+        <v>13</v>
+      </c>
+      <c r="CN39" s="12">
+        <v>457809.52380949992</v>
+      </c>
+      <c r="CO39" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP39" s="12">
+        <f t="shared" si="27"/>
+        <v>3047.6190476099146</v>
+      </c>
+      <c r="CQ39" s="11">
+        <f t="shared" si="28"/>
+        <v>6.7015706806084069E-3</v>
+      </c>
       <c r="CS39" s="14"/>
       <c r="CT39" s="13"/>
       <c r="CV39" s="12"/>
@@ -10074,7 +10654,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -10107,13 +10687,28 @@
         <f t="shared" si="25"/>
         <v>-7.0638324173154007E-2</v>
       </c>
-      <c r="CK40" s="9"/>
+      <c r="CK40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CL40" s="9"/>
-      <c r="CM40" s="8"/>
-      <c r="CN40" s="7"/>
-      <c r="CO40" s="27"/>
-      <c r="CP40" s="28"/>
-      <c r="CQ40" s="29"/>
+      <c r="CM40" s="8">
+        <v>213</v>
+      </c>
+      <c r="CN40" s="7">
+        <v>1203807.6190470899</v>
+      </c>
+      <c r="CO40" s="27">
+        <f t="shared" si="26"/>
+        <v>-14</v>
+      </c>
+      <c r="CP40" s="28">
+        <f t="shared" si="27"/>
+        <v>86810.476190540008</v>
+      </c>
+      <c r="CQ40" s="29">
+        <f t="shared" si="28"/>
+        <v>7.7717724477374628E-2</v>
+      </c>
       <c r="CS40" s="9"/>
       <c r="CT40" s="9"/>
       <c r="CU40" s="8"/>
@@ -10322,7 +10917,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -10355,13 +10950,28 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK41" s="14"/>
-      <c r="CL41" s="32"/>
-      <c r="CM41" s="15"/>
+      <c r="CK41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CL41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CM41" s="15">
+        <v>1323</v>
+      </c>
       <c r="CN41" s="33"/>
-      <c r="CO41" s="10"/>
-      <c r="CP41" s="12"/>
-      <c r="CQ41" s="11"/>
+      <c r="CO41" s="10">
+        <f t="shared" si="26"/>
+        <v>38</v>
+      </c>
+      <c r="CP41" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ41" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS41" s="14"/>
       <c r="CT41" s="32"/>
       <c r="CU41" s="15"/>
@@ -10550,7 +11160,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -10582,12 +11192,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK42" s="14"/>
-      <c r="CL42" s="32"/>
+      <c r="CL42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM42" s="15"/>
       <c r="CN42" s="33"/>
-      <c r="CO42" s="10"/>
-      <c r="CP42" s="12"/>
-      <c r="CQ42" s="11"/>
+      <c r="CO42" s="10">
+        <f t="shared" si="26"/>
+        <v>-7</v>
+      </c>
+      <c r="CP42" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ42" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS42" s="14"/>
       <c r="CT42" s="32"/>
       <c r="CU42" s="15"/>
@@ -10796,7 +11417,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -10830,10 +11451,27 @@
         <v>3.8101071265928071E-2</v>
       </c>
       <c r="CK43" s="14"/>
-      <c r="CL43" s="13"/>
-      <c r="CN43" s="12"/>
-      <c r="CP43" s="12"/>
-      <c r="CQ43" s="11"/>
+      <c r="CL43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM43" s="10">
+        <v>98</v>
+      </c>
+      <c r="CN43" s="12">
+        <v>89394.285713870035</v>
+      </c>
+      <c r="CO43" s="10">
+        <f t="shared" si="26"/>
+        <v>-12</v>
+      </c>
+      <c r="CP43" s="12">
+        <f t="shared" si="27"/>
+        <v>3841.9047619400226</v>
+      </c>
+      <c r="CQ43" s="11">
+        <f t="shared" si="28"/>
+        <v>4.4907046644309105E-2</v>
+      </c>
       <c r="CS43" s="14"/>
       <c r="CT43" s="13"/>
       <c r="CV43" s="12"/>
@@ -11040,7 +11678,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -11074,10 +11712,27 @@
         <v>-1.4874286921387718E-2</v>
       </c>
       <c r="CK44" s="14"/>
-      <c r="CL44" s="13"/>
-      <c r="CN44" s="12"/>
-      <c r="CP44" s="12"/>
-      <c r="CQ44" s="11"/>
+      <c r="CL44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM44" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN44" s="12">
+        <v>66047.619047519998</v>
+      </c>
+      <c r="CO44" s="10">
+        <f t="shared" si="26"/>
+        <v>-13</v>
+      </c>
+      <c r="CP44" s="12">
+        <f t="shared" si="27"/>
+        <v>-22763.809523799981</v>
+      </c>
+      <c r="CQ44" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.25631621841911384</v>
+      </c>
       <c r="CS44" s="14"/>
       <c r="CT44" s="13"/>
       <c r="CV44" s="12"/>
@@ -11284,7 +11939,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -11318,10 +11973,27 @@
         <v>0.50386195562864633</v>
       </c>
       <c r="CK45" s="14"/>
-      <c r="CL45" s="13"/>
-      <c r="CN45" s="12"/>
-      <c r="CP45" s="12"/>
-      <c r="CQ45" s="11"/>
+      <c r="CL45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM45" s="10">
+        <v>10</v>
+      </c>
+      <c r="CN45" s="12">
+        <v>62761.904761899998</v>
+      </c>
+      <c r="CO45" s="10">
+        <f t="shared" si="26"/>
+        <v>-11</v>
+      </c>
+      <c r="CP45" s="12">
+        <f t="shared" si="27"/>
+        <v>-76681.90476189999</v>
+      </c>
+      <c r="CQ45" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.54991257786034653</v>
+      </c>
       <c r="CS45" s="14"/>
       <c r="CT45" s="13"/>
       <c r="CV45" s="12"/>
@@ -11528,7 +12200,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -11562,10 +12234,27 @@
         <v>0.6700854700855996</v>
       </c>
       <c r="CK46" s="14"/>
-      <c r="CL46" s="13"/>
-      <c r="CN46" s="12"/>
-      <c r="CP46" s="12"/>
-      <c r="CQ46" s="11"/>
+      <c r="CL46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM46" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN46" s="12">
+        <v>137333.33333331</v>
+      </c>
+      <c r="CO46" s="10">
+        <f t="shared" si="26"/>
+        <v>-8</v>
+      </c>
+      <c r="CP46" s="12">
+        <f t="shared" si="27"/>
+        <v>-48761.904761890037</v>
+      </c>
+      <c r="CQ46" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.26202661207776362</v>
+      </c>
       <c r="CS46" s="14"/>
       <c r="CT46" s="13"/>
       <c r="CV46" s="12"/>
@@ -11752,7 +12441,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -11781,10 +12470,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK47" s="14"/>
-      <c r="CL47" s="13"/>
+      <c r="CL47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN47" s="12"/>
-      <c r="CP47" s="12"/>
-      <c r="CQ47" s="11"/>
+      <c r="CO47" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP47" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ47" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS47" s="14"/>
       <c r="CT47" s="13"/>
       <c r="CV47" s="12"/>
@@ -11991,7 +12692,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -12025,10 +12726,27 @@
         <v>1.4451510333863276</v>
       </c>
       <c r="CK48" s="14"/>
-      <c r="CL48" s="13"/>
-      <c r="CN48" s="12"/>
-      <c r="CP48" s="12"/>
-      <c r="CQ48" s="11"/>
+      <c r="CL48" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM48" s="10">
+        <v>4</v>
+      </c>
+      <c r="CN48" s="12">
+        <v>20260</v>
+      </c>
+      <c r="CO48" s="10">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="CP48" s="12">
+        <f t="shared" si="27"/>
+        <v>4880</v>
+      </c>
+      <c r="CQ48" s="11">
+        <f t="shared" si="28"/>
+        <v>0.31729518855656696</v>
+      </c>
       <c r="CS48" s="14"/>
       <c r="CT48" s="13"/>
       <c r="CV48" s="12"/>
@@ -12235,7 +12953,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -12269,10 +12987,22 @@
         <v>3.3605345309168881</v>
       </c>
       <c r="CK49" s="14"/>
-      <c r="CL49" s="13"/>
+      <c r="CL49" s="13" t="s">
+        <v>4</v>
+      </c>
       <c r="CN49" s="12"/>
-      <c r="CP49" s="12"/>
-      <c r="CQ49" s="11"/>
+      <c r="CO49" s="10">
+        <f t="shared" si="26"/>
+        <v>-8</v>
+      </c>
+      <c r="CP49" s="12">
+        <f t="shared" si="27"/>
+        <v>-227482.85714284002</v>
+      </c>
+      <c r="CQ49" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS49" s="14"/>
       <c r="CT49" s="13"/>
       <c r="CV49" s="12"/>
@@ -12479,7 +13209,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -12513,10 +13243,27 @@
         <v>0.26384922901197227</v>
       </c>
       <c r="CK50" s="14"/>
-      <c r="CL50" s="13"/>
-      <c r="CN50" s="12"/>
-      <c r="CP50" s="12"/>
-      <c r="CQ50" s="11"/>
+      <c r="CL50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM50" s="10">
+        <v>7</v>
+      </c>
+      <c r="CN50" s="12">
+        <v>91333.333333310002</v>
+      </c>
+      <c r="CO50" s="10">
+        <f t="shared" si="26"/>
+        <v>-7</v>
+      </c>
+      <c r="CP50" s="12">
+        <f t="shared" si="27"/>
+        <v>-119428.57142855998</v>
+      </c>
+      <c r="CQ50" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.56665160415729177</v>
+      </c>
       <c r="CS50" s="14"/>
       <c r="CT50" s="13"/>
       <c r="CV50" s="12"/>
@@ -12723,7 +13470,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -12757,10 +13504,27 @@
         <v>1.9855967078189383</v>
       </c>
       <c r="CK51" s="14"/>
-      <c r="CL51" s="13"/>
-      <c r="CN51" s="12"/>
-      <c r="CP51" s="12"/>
-      <c r="CQ51" s="11"/>
+      <c r="CL51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM51" s="10">
+        <v>26</v>
+      </c>
+      <c r="CN51" s="12">
+        <v>965142.85714284005</v>
+      </c>
+      <c r="CO51" s="10">
+        <f t="shared" si="26"/>
+        <v>-6</v>
+      </c>
+      <c r="CP51" s="12">
+        <f t="shared" si="27"/>
+        <v>-140380.95238092984</v>
+      </c>
+      <c r="CQ51" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.12698139214333357</v>
+      </c>
       <c r="CS51" s="14"/>
       <c r="CT51" s="13"/>
       <c r="CV51" s="12"/>
@@ -12968,7 +13732,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -13001,13 +13765,28 @@
         <f t="shared" si="25"/>
         <v>1.1178790489549779</v>
       </c>
-      <c r="CK52" s="9"/>
+      <c r="CK52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CL52" s="9"/>
-      <c r="CM52" s="8"/>
-      <c r="CN52" s="7"/>
-      <c r="CO52" s="27"/>
-      <c r="CP52" s="28"/>
-      <c r="CQ52" s="29"/>
+      <c r="CM52" s="8">
+        <v>228</v>
+      </c>
+      <c r="CN52" s="7">
+        <v>1432273.33333275</v>
+      </c>
+      <c r="CO52" s="27">
+        <f t="shared" si="26"/>
+        <v>-63</v>
+      </c>
+      <c r="CP52" s="28">
+        <f t="shared" si="27"/>
+        <v>-626778.0952379799</v>
+      </c>
+      <c r="CQ52" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.30440137946095486</v>
+      </c>
       <c r="CS52" s="9"/>
       <c r="CT52" s="9"/>
       <c r="CU52" s="8"/>
@@ -13188,7 +13967,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -13219,13 +13998,26 @@
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CK53" s="14"/>
-      <c r="CL53" s="32"/>
+      <c r="CK53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CL53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CM53" s="15"/>
       <c r="CN53" s="33"/>
-      <c r="CO53" s="10"/>
-      <c r="CP53" s="12"/>
-      <c r="CQ53" s="11"/>
+      <c r="CO53" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP53" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ53" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS53" s="14"/>
       <c r="CT53" s="32"/>
       <c r="CU53" s="15"/>
@@ -13414,7 +14206,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -13444,12 +14236,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK54" s="14"/>
-      <c r="CL54" s="32"/>
+      <c r="CL54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CM54" s="15"/>
       <c r="CN54" s="33"/>
-      <c r="CO54" s="10"/>
-      <c r="CP54" s="12"/>
-      <c r="CQ54" s="11"/>
+      <c r="CO54" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP54" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ54" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS54" s="14"/>
       <c r="CT54" s="32"/>
       <c r="CU54" s="15"/>
@@ -13658,7 +14461,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -13692,10 +14495,27 @@
         <v>0.10401379889107165</v>
       </c>
       <c r="CK55" s="14"/>
-      <c r="CL55" s="13"/>
-      <c r="CN55" s="12"/>
-      <c r="CP55" s="12"/>
-      <c r="CQ55" s="11"/>
+      <c r="CL55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM55" s="10">
+        <v>75</v>
+      </c>
+      <c r="CN55" s="12">
+        <v>75446.666666359975</v>
+      </c>
+      <c r="CO55" s="10">
+        <f t="shared" si="26"/>
+        <v>-39</v>
+      </c>
+      <c r="CP55" s="12">
+        <f t="shared" si="27"/>
+        <v>-37325.71428554006</v>
+      </c>
+      <c r="CQ55" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.33098276342556177</v>
+      </c>
       <c r="CS55" s="14"/>
       <c r="CT55" s="13"/>
       <c r="CV55" s="12"/>
@@ -13902,7 +14722,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -13936,10 +14756,27 @@
         <v>-0.22430731554514952</v>
       </c>
       <c r="CK56" s="14"/>
-      <c r="CL56" s="13"/>
-      <c r="CN56" s="12"/>
-      <c r="CP56" s="12"/>
-      <c r="CQ56" s="11"/>
+      <c r="CL56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM56" s="10">
+        <v>59</v>
+      </c>
+      <c r="CN56" s="12">
+        <v>68485.714285609996</v>
+      </c>
+      <c r="CO56" s="10">
+        <f t="shared" si="26"/>
+        <v>-9</v>
+      </c>
+      <c r="CP56" s="12">
+        <f t="shared" si="27"/>
+        <v>-9342.8571428900032</v>
+      </c>
+      <c r="CQ56" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.12004405286396851</v>
+      </c>
       <c r="CS56" s="14"/>
       <c r="CT56" s="13"/>
       <c r="CV56" s="12"/>
@@ -14146,7 +14983,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -14180,10 +15017,27 @@
         <v>0.22806762934483393</v>
       </c>
       <c r="CK57" s="14"/>
-      <c r="CL57" s="13"/>
-      <c r="CN57" s="12"/>
-      <c r="CP57" s="12"/>
-      <c r="CQ57" s="11"/>
+      <c r="CL57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM57" s="10">
+        <v>11</v>
+      </c>
+      <c r="CN57" s="12">
+        <v>69895.238095230001</v>
+      </c>
+      <c r="CO57" s="10">
+        <f t="shared" si="26"/>
+        <v>-15</v>
+      </c>
+      <c r="CP57" s="12">
+        <f t="shared" si="27"/>
+        <v>-91285.714285710026</v>
+      </c>
+      <c r="CQ57" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.5663554715197523</v>
+      </c>
       <c r="CS57" s="14"/>
       <c r="CT57" s="13"/>
       <c r="CV57" s="12"/>
@@ -14390,7 +15244,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -14424,10 +15278,27 @@
         <v>1.3004484304935418</v>
       </c>
       <c r="CK58" s="14"/>
-      <c r="CL58" s="13"/>
-      <c r="CN58" s="12"/>
-      <c r="CP58" s="12"/>
-      <c r="CQ58" s="11"/>
+      <c r="CL58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM58" s="10">
+        <v>8</v>
+      </c>
+      <c r="CN58" s="12">
+        <v>90190.47619044999</v>
+      </c>
+      <c r="CO58" s="10">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="CP58" s="12">
+        <f t="shared" si="27"/>
+        <v>-7523.8095238000096</v>
+      </c>
+      <c r="CQ58" s="11">
+        <f t="shared" si="28"/>
+        <v>-7.6998050682191982E-2</v>
+      </c>
       <c r="CS58" s="14"/>
       <c r="CT58" s="13"/>
       <c r="CV58" s="12"/>
@@ -14609,7 +15480,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -14638,10 +15509,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CK59" s="14"/>
-      <c r="CL59" s="13"/>
+      <c r="CL59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CN59" s="12"/>
-      <c r="CP59" s="12"/>
-      <c r="CQ59" s="11"/>
+      <c r="CO59" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="CP59" s="12">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="CQ59" s="11" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="CS59" s="14"/>
       <c r="CT59" s="13"/>
       <c r="CV59" s="12"/>
@@ -14843,7 +15726,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -14877,10 +15760,22 @@
         <v>0.3958664546899841</v>
       </c>
       <c r="CK60" s="14"/>
-      <c r="CL60" s="13"/>
+      <c r="CL60" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CN60" s="12"/>
-      <c r="CP60" s="12"/>
-      <c r="CQ60" s="11"/>
+      <c r="CO60" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP60" s="12">
+        <f t="shared" si="27"/>
+        <v>-8780</v>
+      </c>
+      <c r="CQ60" s="11">
+        <f t="shared" si="28"/>
+        <v>-1</v>
+      </c>
       <c r="CS60" s="14"/>
       <c r="CT60" s="13"/>
       <c r="CV60" s="12"/>
@@ -15087,7 +15982,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -15121,10 +16016,27 @@
         <v>9.62199312714975E-2</v>
       </c>
       <c r="CK61" s="14"/>
-      <c r="CL61" s="13"/>
-      <c r="CN61" s="12"/>
-      <c r="CP61" s="12"/>
-      <c r="CQ61" s="11"/>
+      <c r="CL61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CM61" s="10">
+        <v>1</v>
+      </c>
+      <c r="CN61" s="12">
+        <v>27523.809523799999</v>
+      </c>
+      <c r="CO61" s="10">
+        <f t="shared" si="26"/>
+        <v>-2</v>
+      </c>
+      <c r="CP61" s="12">
+        <f t="shared" si="27"/>
+        <v>-63619.047619040008</v>
+      </c>
+      <c r="CQ61" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.69801462904915956</v>
+      </c>
       <c r="CS61" s="14"/>
       <c r="CT61" s="13"/>
       <c r="CV61" s="12"/>
@@ -15331,7 +16243,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -15365,10 +16277,27 @@
         <v>0.75350877192980292</v>
       </c>
       <c r="CK62" s="14"/>
-      <c r="CL62" s="13"/>
-      <c r="CN62" s="12"/>
-      <c r="CP62" s="12"/>
-      <c r="CQ62" s="11"/>
+      <c r="CL62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CM62" s="10">
+        <v>7</v>
+      </c>
+      <c r="CN62" s="12">
+        <v>91333.333333310002</v>
+      </c>
+      <c r="CO62" s="10">
+        <f t="shared" si="26"/>
+        <v>-22</v>
+      </c>
+      <c r="CP62" s="12">
+        <f t="shared" si="27"/>
+        <v>-289428.57142856007</v>
+      </c>
+      <c r="CQ62" s="11">
+        <f t="shared" si="28"/>
+        <v>-0.76013006503255576</v>
+      </c>
       <c r="CS62" s="14"/>
       <c r="CT62" s="13"/>
       <c r="CV62" s="12"/>
@@ -15575,7 +16504,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -15609,10 +16538,27 @@
         <v>0.28391887435876384</v>
       </c>
       <c r="CK63" s="14"/>
-      <c r="CL63" s="13"/>
-      <c r="CN63" s="12"/>
-      <c r="CP63" s="12"/>
-      <c r="CQ63" s="11"/>
+      <c r="CL63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CM63" s="10">
+        <v>20</v>
+      </c>
+      <c r="CN63" s="12">
+        <v>659047.61904759007</v>
+      </c>
+      <c r="CO63" s="10">
+        <f t="shared" si="26"/>
+        <v>2</v>
+      </c>
+      <c r="CP63" s="12">
+        <f t="shared" si="27"/>
+        <v>73142.85714286007</v>
+      </c>
+      <c r="CQ63" s="11">
+        <f t="shared" si="28"/>
+        <v>0.12483745123538241</v>
+      </c>
       <c r="CS63" s="14"/>
       <c r="CT63" s="13"/>
       <c r="CV63" s="12"/>
@@ -15820,7 +16766,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -15853,13 +16799,28 @@
         <f t="shared" si="25"/>
         <v>0.33092434986519093</v>
       </c>
-      <c r="CK64" s="9"/>
+      <c r="CK64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CL64" s="9"/>
-      <c r="CM64" s="8"/>
-      <c r="CN64" s="7"/>
-      <c r="CO64" s="27"/>
-      <c r="CP64" s="28"/>
-      <c r="CQ64" s="29"/>
+      <c r="CM64" s="8">
+        <v>181</v>
+      </c>
+      <c r="CN64" s="7">
+        <v>1081922.8571423502</v>
+      </c>
+      <c r="CO64" s="27">
+        <f t="shared" si="26"/>
+        <v>-88</v>
+      </c>
+      <c r="CP64" s="28">
+        <f t="shared" si="27"/>
+        <v>-434162.85714267986</v>
+      </c>
+      <c r="CQ64" s="29">
+        <f t="shared" si="28"/>
+        <v>-0.28637091758853916</v>
+      </c>
       <c r="CS64" s="9"/>
       <c r="CT64" s="9"/>
       <c r="CU64" s="8"/>
@@ -16069,7 +17030,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -16102,13 +17063,28 @@
         <f t="shared" si="25"/>
         <v>0.92062826128569275</v>
       </c>
-      <c r="CK65" s="4"/>
+      <c r="CK65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CL65" s="4"/>
-      <c r="CM65" s="3"/>
-      <c r="CN65" s="2"/>
-      <c r="CO65" s="6"/>
-      <c r="CP65" s="5"/>
-      <c r="CQ65" s="30"/>
+      <c r="CM65" s="3">
+        <v>2060</v>
+      </c>
+      <c r="CN65" s="2">
+        <v>19139967.142853197</v>
+      </c>
+      <c r="CO65" s="6">
+        <f t="shared" si="26"/>
+        <v>-245</v>
+      </c>
+      <c r="CP65" s="5">
+        <f t="shared" si="27"/>
+        <v>-2221615.2380946949</v>
+      </c>
+      <c r="CQ65" s="30">
+        <f t="shared" si="28"/>
+        <v>-0.10400049951712022</v>
+      </c>
       <c r="CS65" s="4"/>
       <c r="CT65" s="4"/>
       <c r="CU65" s="3"/>
@@ -16125,7 +17101,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="109" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16137,7 +17113,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16149,7 +17125,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16161,7 +17137,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16173,7 +17149,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16185,7 +17161,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16197,7 +17173,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16209,7 +17185,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16221,7 +17197,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16233,7 +17209,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16245,7 +17221,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16257,7 +17233,7 @@
           <xm:sqref>CG5:CI65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{00C895F4-D5E3-F04E-93CB-E795A6DC8C2F}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -16269,7 +17245,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE836E5-63B5-A549-AD2F-CD6D457EF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD8DBD-14A9-6541-81BE-2391B270B987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="680" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="14640" yWindow="1640" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -1943,10 +1943,13 @@
       <c r="CL6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CM6" s="15">
+        <v>15</v>
+      </c>
       <c r="CN6" s="33"/>
       <c r="CO6" s="10">
         <f t="shared" si="26"/>
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="CP6" s="12">
         <f t="shared" si="27"/>
@@ -5024,11 +5027,13 @@
       <c r="CL18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM18" s="15"/>
+      <c r="CM18" s="15">
+        <v>15</v>
+      </c>
       <c r="CN18" s="33"/>
       <c r="CO18" s="10">
         <f t="shared" si="26"/>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="CP18" s="12">
         <f t="shared" si="27"/>
@@ -8122,11 +8127,13 @@
       <c r="CL30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM30" s="15"/>
+      <c r="CM30" s="15">
+        <v>5</v>
+      </c>
       <c r="CN30" s="33"/>
       <c r="CO30" s="10">
         <f t="shared" si="26"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="CP30" s="12">
         <f t="shared" si="27"/>
@@ -11195,11 +11202,13 @@
       <c r="CL42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM42" s="15"/>
+      <c r="CM42" s="15">
+        <v>6</v>
+      </c>
       <c r="CN42" s="33"/>
       <c r="CO42" s="10">
         <f t="shared" si="26"/>
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="CP42" s="12">
         <f t="shared" si="27"/>
@@ -14221,7 +14230,9 @@
       <c r="CD54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CE54" s="15"/>
+      <c r="CE54" s="15">
+        <v>0</v>
+      </c>
       <c r="CF54" s="33"/>
       <c r="CG54" s="10">
         <f t="shared" si="23"/>
@@ -14239,11 +14250,13 @@
       <c r="CL54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CM54" s="15"/>
+      <c r="CM54" s="15">
+        <v>2</v>
+      </c>
       <c r="CN54" s="33"/>
       <c r="CO54" s="10">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CP54" s="12">
         <f t="shared" si="27"/>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD8DBD-14A9-6541-81BE-2391B270B987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FB02E-9673-9447-A447-22229F527E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14640" yWindow="1640" windowWidth="19520" windowHeight="20160" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5640" yWindow="1520" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="48">
   <si>
     <t>總計</t>
   </si>
@@ -236,6 +236,14 @@
   </si>
   <si>
     <t>03/15~03/21</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26Q2W13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03/22~03/28</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -567,7 +575,12 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1095,7 +1108,11 @@
       </c>
       <c r="CL1" s="26"/>
       <c r="CN1" s="25"/>
-      <c r="CS1" s="26"/>
+      <c r="CS1" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="CT1" s="26"/>
+      <c r="CV1" s="25"/>
     </row>
     <row r="2" spans="1:103" s="20" customFormat="1" ht="18">
       <c r="A2" s="23" t="s">
@@ -1176,7 +1193,9 @@
       <c r="CO2" s="21"/>
       <c r="CP2" s="21"/>
       <c r="CQ2" s="21"/>
-      <c r="CS2" s="22"/>
+      <c r="CS2" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="CT2" s="21"/>
       <c r="CV2" s="21"/>
       <c r="CW2" s="21"/>
@@ -1444,13 +1463,27 @@
       <c r="CQ4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="CS4" s="19"/>
-      <c r="CT4" s="19"/>
-      <c r="CU4" s="18"/>
-      <c r="CV4" s="17"/>
-      <c r="CW4" s="16"/>
-      <c r="CX4" s="16"/>
-      <c r="CY4" s="16"/>
+      <c r="CS4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="CT4" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="CU4" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="CV4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="CW4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CX4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="CY4" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:103" s="39" customFormat="1" ht="22" customHeight="1">
       <c r="A5" s="14">
@@ -1720,13 +1753,28 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CR5" s="38"/>
-      <c r="CS5" s="14"/>
-      <c r="CT5" s="32"/>
-      <c r="CU5" s="15"/>
+      <c r="CS5" s="14">
+        <v>75</v>
+      </c>
+      <c r="CT5" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU5" s="15">
+        <v>6354</v>
+      </c>
       <c r="CV5" s="33"/>
-      <c r="CW5" s="10"/>
-      <c r="CX5" s="12"/>
-      <c r="CY5" s="11"/>
+      <c r="CW5" s="10">
+        <f t="shared" ref="CW5:CW65" si="29">CU5-CM5</f>
+        <v>272</v>
+      </c>
+      <c r="CX5" s="12">
+        <f t="shared" ref="CX5:CX65" si="30">CV5-CN5</f>
+        <v>0</v>
+      </c>
+      <c r="CY5" s="11" t="e">
+        <f t="shared" ref="CY5:CY65" si="31">(CV5-CN5)/CN5</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="6" spans="1:103" s="15" customFormat="1" ht="22" customHeight="1">
       <c r="A6" s="14"/>
@@ -1960,11 +2008,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS6" s="14"/>
-      <c r="CT6" s="32"/>
+      <c r="CT6" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CV6" s="33"/>
-      <c r="CW6" s="10"/>
-      <c r="CX6" s="12"/>
-      <c r="CY6" s="11"/>
+      <c r="CW6" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX6" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY6" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="7" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A7" s="14"/>
@@ -2222,10 +2281,27 @@
         <v>-0.18246126353882261</v>
       </c>
       <c r="CS7" s="14"/>
-      <c r="CT7" s="13"/>
-      <c r="CV7" s="12"/>
-      <c r="CX7" s="12"/>
-      <c r="CY7" s="11"/>
+      <c r="CT7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU7" s="10">
+        <v>197</v>
+      </c>
+      <c r="CV7" s="12">
+        <v>210633.33333257007</v>
+      </c>
+      <c r="CW7" s="10">
+        <f t="shared" si="29"/>
+        <v>26</v>
+      </c>
+      <c r="CX7" s="12">
+        <f t="shared" si="30"/>
+        <v>31993.333333280141</v>
+      </c>
+      <c r="CY7" s="11">
+        <f t="shared" si="31"/>
+        <v>0.17909389461155012</v>
+      </c>
     </row>
     <row r="8" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A8" s="14"/>
@@ -2483,10 +2559,27 @@
         <v>-0.13345697379771318</v>
       </c>
       <c r="CS8" s="14"/>
-      <c r="CT8" s="13"/>
-      <c r="CV8" s="12"/>
-      <c r="CX8" s="12"/>
-      <c r="CY8" s="11"/>
+      <c r="CT8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU8" s="10">
+        <v>237</v>
+      </c>
+      <c r="CV8" s="12">
+        <v>348669.52380933991</v>
+      </c>
+      <c r="CW8" s="10">
+        <f t="shared" si="29"/>
+        <v>20</v>
+      </c>
+      <c r="CX8" s="12">
+        <f t="shared" si="30"/>
+        <v>105705.71428566991</v>
+      </c>
+      <c r="CY8" s="11">
+        <f t="shared" si="31"/>
+        <v>0.43506773495569451</v>
+      </c>
     </row>
     <row r="9" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A9" s="14"/>
@@ -2744,10 +2837,27 @@
         <v>-8.5987565758025214E-2</v>
       </c>
       <c r="CS9" s="14"/>
-      <c r="CT9" s="13"/>
-      <c r="CV9" s="12"/>
-      <c r="CX9" s="12"/>
-      <c r="CY9" s="11"/>
+      <c r="CT9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU9" s="10">
+        <v>72</v>
+      </c>
+      <c r="CV9" s="12">
+        <v>452887.61904760997</v>
+      </c>
+      <c r="CW9" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX9" s="12">
+        <f t="shared" si="30"/>
+        <v>-2159.9999999899883</v>
+      </c>
+      <c r="CY9" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.7467559648170423E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A10" s="14"/>
@@ -3005,10 +3115,27 @@
         <v>-7.407407407409039E-2</v>
       </c>
       <c r="CS10" s="14"/>
-      <c r="CT10" s="13"/>
-      <c r="CV10" s="12"/>
-      <c r="CX10" s="12"/>
-      <c r="CY10" s="11"/>
+      <c r="CT10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU10" s="10">
+        <v>54</v>
+      </c>
+      <c r="CV10" s="12">
+        <v>929142.85714277998</v>
+      </c>
+      <c r="CW10" s="10">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="CX10" s="12">
+        <f t="shared" si="30"/>
+        <v>445809.52380951995</v>
+      </c>
+      <c r="CY10" s="11">
+        <f t="shared" si="31"/>
+        <v>0.92236453201983637</v>
+      </c>
     </row>
     <row r="11" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A11" s="14"/>
@@ -3236,10 +3363,27 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS11" s="14"/>
-      <c r="CT11" s="13"/>
-      <c r="CV11" s="12"/>
-      <c r="CX11" s="12"/>
-      <c r="CY11" s="11"/>
+      <c r="CT11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU11" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV11" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CW11" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX11" s="12">
+        <f t="shared" si="30"/>
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CY11" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="12" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A12" s="14"/>
@@ -3497,10 +3641,27 @@
         <v>0.74442025040827431</v>
       </c>
       <c r="CS12" s="14"/>
-      <c r="CT12" s="13"/>
-      <c r="CV12" s="12"/>
-      <c r="CX12" s="12"/>
-      <c r="CY12" s="11"/>
+      <c r="CT12" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU12" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV12" s="12">
+        <v>46420</v>
+      </c>
+      <c r="CW12" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX12" s="12">
+        <f t="shared" si="30"/>
+        <v>-17670</v>
+      </c>
+      <c r="CY12" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.27570603838352314</v>
+      </c>
     </row>
     <row r="13" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A13" s="14"/>
@@ -3758,10 +3919,27 @@
         <v>-0.50447452009391824</v>
       </c>
       <c r="CS13" s="14"/>
-      <c r="CT13" s="13"/>
-      <c r="CV13" s="12"/>
-      <c r="CX13" s="12"/>
-      <c r="CY13" s="11"/>
+      <c r="CT13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU13" s="10">
+        <v>5</v>
+      </c>
+      <c r="CV13" s="12">
+        <v>275423.80952379998</v>
+      </c>
+      <c r="CW13" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX13" s="12">
+        <f t="shared" si="30"/>
+        <v>-66299.999999970081</v>
+      </c>
+      <c r="CY13" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.19401633176326363</v>
+      </c>
     </row>
     <row r="14" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A14" s="14"/>
@@ -4019,10 +4197,27 @@
         <v>-0.44086935405535715</v>
       </c>
       <c r="CS14" s="14"/>
-      <c r="CT14" s="13"/>
-      <c r="CV14" s="12"/>
-      <c r="CX14" s="12"/>
-      <c r="CY14" s="11"/>
+      <c r="CT14" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU14" s="10">
+        <v>89</v>
+      </c>
+      <c r="CV14" s="12">
+        <v>1702285.7142856203</v>
+      </c>
+      <c r="CW14" s="10">
+        <f t="shared" si="29"/>
+        <v>65</v>
+      </c>
+      <c r="CX14" s="12">
+        <f t="shared" si="30"/>
+        <v>1263714.2857142303</v>
+      </c>
+      <c r="CY14" s="11">
+        <f t="shared" si="31"/>
+        <v>2.8814332247558272</v>
+      </c>
     </row>
     <row r="15" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A15" s="14"/>
@@ -4280,10 +4475,27 @@
         <v>-0.32080884629566497</v>
       </c>
       <c r="CS15" s="14"/>
-      <c r="CT15" s="13"/>
-      <c r="CV15" s="12"/>
-      <c r="CX15" s="12"/>
-      <c r="CY15" s="11"/>
+      <c r="CT15" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU15" s="10">
+        <v>333</v>
+      </c>
+      <c r="CV15" s="12">
+        <v>13040666.666666551</v>
+      </c>
+      <c r="CW15" s="10">
+        <f t="shared" si="29"/>
+        <v>218</v>
+      </c>
+      <c r="CX15" s="12">
+        <f t="shared" si="30"/>
+        <v>8881142.857142821</v>
+      </c>
+      <c r="CY15" s="11">
+        <f t="shared" si="31"/>
+        <v>2.1351345163137125</v>
+      </c>
     </row>
     <row r="16" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -4541,13 +4753,28 @@
         <f t="shared" si="28"/>
         <v>-0.30477520096695548</v>
       </c>
-      <c r="CS16" s="9"/>
+      <c r="CS16" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="CT16" s="9"/>
-      <c r="CU16" s="8"/>
-      <c r="CV16" s="7"/>
-      <c r="CW16" s="27"/>
-      <c r="CX16" s="28"/>
-      <c r="CY16" s="29"/>
+      <c r="CU16" s="8">
+        <v>996</v>
+      </c>
+      <c r="CV16" s="7">
+        <v>17014986.666665412</v>
+      </c>
+      <c r="CW16" s="27">
+        <f t="shared" si="29"/>
+        <v>345</v>
+      </c>
+      <c r="CX16" s="28">
+        <f t="shared" si="30"/>
+        <v>10651092.857142702</v>
+      </c>
+      <c r="CY16" s="29">
+        <f t="shared" si="31"/>
+        <v>1.6736754534157647</v>
+      </c>
     </row>
     <row r="17" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A17" s="14">
@@ -4804,13 +5031,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS17" s="14"/>
-      <c r="CT17" s="32"/>
-      <c r="CU17" s="15"/>
+      <c r="CS17" s="14">
+        <v>76</v>
+      </c>
+      <c r="CT17" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU17" s="15">
+        <v>4216</v>
+      </c>
       <c r="CV17" s="33"/>
-      <c r="CW17" s="10"/>
-      <c r="CX17" s="12"/>
-      <c r="CY17" s="11"/>
+      <c r="CW17" s="10">
+        <f t="shared" si="29"/>
+        <v>-1133</v>
+      </c>
+      <c r="CX17" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY17" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="18" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A18" s="14"/>
@@ -5044,12 +5286,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS18" s="14"/>
-      <c r="CT18" s="32"/>
+      <c r="CT18" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU18" s="15"/>
       <c r="CV18" s="33"/>
-      <c r="CW18" s="10"/>
-      <c r="CX18" s="12"/>
-      <c r="CY18" s="11"/>
+      <c r="CW18" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX18" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY18" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="19" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A19" s="14"/>
@@ -5307,10 +5560,27 @@
         <v>7.4207219828554896E-2</v>
       </c>
       <c r="CS19" s="14"/>
-      <c r="CT19" s="13"/>
-      <c r="CV19" s="12"/>
-      <c r="CX19" s="12"/>
-      <c r="CY19" s="11"/>
+      <c r="CT19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU19" s="10">
+        <v>181</v>
+      </c>
+      <c r="CV19" s="12">
+        <v>194270.47618971989</v>
+      </c>
+      <c r="CW19" s="10">
+        <f t="shared" si="29"/>
+        <v>-30</v>
+      </c>
+      <c r="CX19" s="12">
+        <f t="shared" si="30"/>
+        <v>-37948.571428480151</v>
+      </c>
+      <c r="CY19" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.16341713488926543</v>
+      </c>
     </row>
     <row r="20" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A20" s="14"/>
@@ -5568,10 +5838,27 @@
         <v>-0.28636093542440028</v>
       </c>
       <c r="CS20" s="14"/>
-      <c r="CT20" s="13"/>
-      <c r="CV20" s="12"/>
-      <c r="CX20" s="12"/>
-      <c r="CY20" s="11"/>
+      <c r="CT20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU20" s="10">
+        <v>150</v>
+      </c>
+      <c r="CV20" s="12">
+        <v>180562.85714273</v>
+      </c>
+      <c r="CW20" s="10">
+        <f t="shared" si="29"/>
+        <v>-69</v>
+      </c>
+      <c r="CX20" s="12">
+        <f t="shared" si="30"/>
+        <v>-37903.809523820004</v>
+      </c>
+      <c r="CY20" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.17349928070113019</v>
+      </c>
     </row>
     <row r="21" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A21" s="14"/>
@@ -5829,10 +6116,27 @@
         <v>0.12521337746037256</v>
       </c>
       <c r="CS21" s="14"/>
-      <c r="CT21" s="13"/>
-      <c r="CV21" s="12"/>
-      <c r="CX21" s="12"/>
-      <c r="CY21" s="11"/>
+      <c r="CT21" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU21" s="10">
+        <v>58</v>
+      </c>
+      <c r="CV21" s="12">
+        <v>362304.76190474001</v>
+      </c>
+      <c r="CW21" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX21" s="12">
+        <f t="shared" si="30"/>
+        <v>-6829.5238095199456</v>
+      </c>
+      <c r="CY21" s="11">
+        <f t="shared" si="31"/>
+        <v>-1.8501461592236257E-2</v>
+      </c>
     </row>
     <row r="22" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A22" s="14"/>
@@ -6090,10 +6394,27 @@
         <v>0.23266351457841633</v>
       </c>
       <c r="CS22" s="14"/>
-      <c r="CT22" s="13"/>
-      <c r="CV22" s="12"/>
-      <c r="CX22" s="12"/>
-      <c r="CY22" s="11"/>
+      <c r="CT22" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU22" s="10">
+        <v>31</v>
+      </c>
+      <c r="CV22" s="12">
+        <v>380857.14285708003</v>
+      </c>
+      <c r="CW22" s="10">
+        <f t="shared" si="29"/>
+        <v>-17</v>
+      </c>
+      <c r="CX22" s="12">
+        <f t="shared" si="30"/>
+        <v>-215047.61904761003</v>
+      </c>
+      <c r="CY22" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.36087581908265581</v>
+      </c>
     </row>
     <row r="23" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A23" s="14"/>
@@ -6341,10 +6662,27 @@
         <v>6.8459057071999236</v>
       </c>
       <c r="CS23" s="14"/>
-      <c r="CT23" s="13"/>
-      <c r="CV23" s="12"/>
-      <c r="CX23" s="12"/>
-      <c r="CY23" s="11"/>
+      <c r="CT23" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU23" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV23" s="12">
+        <v>8857.1428571399993</v>
+      </c>
+      <c r="CW23" s="10">
+        <f t="shared" si="29"/>
+        <v>-15</v>
+      </c>
+      <c r="CX23" s="12">
+        <f t="shared" si="30"/>
+        <v>-81482.857142859997</v>
+      </c>
+      <c r="CY23" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.90195768367124196</v>
+      </c>
     </row>
     <row r="24" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A24" s="14"/>
@@ -6597,10 +6935,27 @@
         <v>-1</v>
       </c>
       <c r="CS24" s="14"/>
-      <c r="CT24" s="13"/>
-      <c r="CV24" s="12"/>
-      <c r="CX24" s="12"/>
-      <c r="CY24" s="11"/>
+      <c r="CT24" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU24" s="10">
+        <v>10</v>
+      </c>
+      <c r="CV24" s="12">
+        <v>62700</v>
+      </c>
+      <c r="CW24" s="10">
+        <f t="shared" si="29"/>
+        <v>10</v>
+      </c>
+      <c r="CX24" s="12">
+        <f t="shared" si="30"/>
+        <v>62700</v>
+      </c>
+      <c r="CY24" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="25" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A25" s="14"/>
@@ -6858,10 +7213,27 @@
         <v>-0.5849775498930726</v>
       </c>
       <c r="CS25" s="14"/>
-      <c r="CT25" s="13"/>
-      <c r="CV25" s="12"/>
-      <c r="CX25" s="12"/>
-      <c r="CY25" s="11"/>
+      <c r="CT25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU25" s="10">
+        <v>5</v>
+      </c>
+      <c r="CV25" s="12">
+        <v>228757.14285713001</v>
+      </c>
+      <c r="CW25" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX25" s="12">
+        <f t="shared" si="30"/>
+        <v>89228.571428569994</v>
+      </c>
+      <c r="CY25" s="11">
+        <f t="shared" si="31"/>
+        <v>0.63950035834958641</v>
+      </c>
     </row>
     <row r="26" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A26" s="14"/>
@@ -7119,10 +7491,27 @@
         <v>3.4012563199060437E-2</v>
       </c>
       <c r="CS26" s="14"/>
-      <c r="CT26" s="13"/>
-      <c r="CV26" s="12"/>
-      <c r="CX26" s="12"/>
-      <c r="CY26" s="11"/>
+      <c r="CT26" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU26" s="10">
+        <v>36</v>
+      </c>
+      <c r="CV26" s="12">
+        <v>573428.57142852002</v>
+      </c>
+      <c r="CW26" s="10">
+        <f t="shared" si="29"/>
+        <v>-3</v>
+      </c>
+      <c r="CX26" s="12">
+        <f t="shared" si="30"/>
+        <v>-69333.333333329996</v>
+      </c>
+      <c r="CY26" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.10786783227145162</v>
+      </c>
     </row>
     <row r="27" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A27" s="14"/>
@@ -7380,10 +7769,27 @@
         <v>0.32529132096579144</v>
       </c>
       <c r="CS27" s="14"/>
-      <c r="CT27" s="13"/>
-      <c r="CV27" s="12"/>
-      <c r="CX27" s="12"/>
-      <c r="CY27" s="11"/>
+      <c r="CT27" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU27" s="10">
+        <v>126</v>
+      </c>
+      <c r="CV27" s="12">
+        <v>4788952.38095228</v>
+      </c>
+      <c r="CW27" s="10">
+        <f t="shared" si="29"/>
+        <v>-62</v>
+      </c>
+      <c r="CX27" s="12">
+        <f t="shared" si="30"/>
+        <v>-1980761.9047619095</v>
+      </c>
+      <c r="CY27" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.29259165470865123</v>
+      </c>
     </row>
     <row r="28" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A28" s="9" t="s">
@@ -7641,13 +8047,28 @@
         <f t="shared" si="28"/>
         <v>0.20521532403134726</v>
       </c>
-      <c r="CS28" s="9"/>
+      <c r="CS28" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="CT28" s="9"/>
-      <c r="CU28" s="8"/>
-      <c r="CV28" s="7"/>
-      <c r="CW28" s="27"/>
-      <c r="CX28" s="28"/>
-      <c r="CY28" s="29"/>
+      <c r="CU28" s="8">
+        <v>598</v>
+      </c>
+      <c r="CV28" s="7">
+        <v>6780690.4761893395</v>
+      </c>
+      <c r="CW28" s="27">
+        <f t="shared" si="29"/>
+        <v>-189</v>
+      </c>
+      <c r="CX28" s="28">
+        <f t="shared" si="30"/>
+        <v>-2277379.047618961</v>
+      </c>
+      <c r="CY28" s="29">
+        <f t="shared" si="31"/>
+        <v>-0.25141991255786678</v>
+      </c>
     </row>
     <row r="29" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A29" s="14">
@@ -7904,13 +8325,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS29" s="14"/>
-      <c r="CT29" s="32"/>
-      <c r="CU29" s="15"/>
+      <c r="CS29" s="14">
+        <v>77</v>
+      </c>
+      <c r="CT29" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU29" s="15">
+        <v>3195</v>
+      </c>
       <c r="CV29" s="33"/>
-      <c r="CW29" s="10"/>
-      <c r="CX29" s="12"/>
-      <c r="CY29" s="11"/>
+      <c r="CW29" s="10">
+        <f t="shared" si="29"/>
+        <v>-244</v>
+      </c>
+      <c r="CX29" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY29" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="30" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A30" s="14"/>
@@ -8144,12 +8580,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS30" s="14"/>
-      <c r="CT30" s="32"/>
+      <c r="CT30" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU30" s="15"/>
       <c r="CV30" s="33"/>
-      <c r="CW30" s="10"/>
-      <c r="CX30" s="12"/>
-      <c r="CY30" s="11"/>
+      <c r="CW30" s="10">
+        <f t="shared" si="29"/>
+        <v>-5</v>
+      </c>
+      <c r="CX30" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY30" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="31" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A31" s="14"/>
@@ -8407,10 +8854,27 @@
         <v>-0.14127742830228468</v>
       </c>
       <c r="CS31" s="14"/>
-      <c r="CT31" s="13"/>
-      <c r="CV31" s="12"/>
-      <c r="CX31" s="12"/>
-      <c r="CY31" s="11"/>
+      <c r="CT31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU31" s="10">
+        <v>115</v>
+      </c>
+      <c r="CV31" s="12">
+        <v>98313.333332900031</v>
+      </c>
+      <c r="CW31" s="10">
+        <f t="shared" si="29"/>
+        <v>44</v>
+      </c>
+      <c r="CX31" s="12">
+        <f t="shared" si="30"/>
+        <v>32268.571428450014</v>
+      </c>
+      <c r="CY31" s="11">
+        <f t="shared" si="31"/>
+        <v>0.48858638441507951</v>
+      </c>
     </row>
     <row r="32" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A32" s="14"/>
@@ -8668,10 +9132,27 @@
         <v>-5.4720000000067853E-2</v>
       </c>
       <c r="CS32" s="14"/>
-      <c r="CT32" s="13"/>
-      <c r="CV32" s="12"/>
-      <c r="CX32" s="12"/>
-      <c r="CY32" s="11"/>
+      <c r="CT32" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU32" s="10">
+        <v>54</v>
+      </c>
+      <c r="CV32" s="12">
+        <v>61199.999999920008</v>
+      </c>
+      <c r="CW32" s="10">
+        <f t="shared" si="29"/>
+        <v>-23</v>
+      </c>
+      <c r="CX32" s="12">
+        <f t="shared" si="30"/>
+        <v>-17573.333333309987</v>
+      </c>
+      <c r="CY32" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.22308733920107957</v>
+      </c>
     </row>
     <row r="33" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A33" s="14"/>
@@ -8929,10 +9410,27 @@
         <v>0.53199222381885614</v>
       </c>
       <c r="CS33" s="14"/>
-      <c r="CT33" s="13"/>
-      <c r="CV33" s="12"/>
-      <c r="CX33" s="12"/>
-      <c r="CY33" s="11"/>
+      <c r="CT33" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU33" s="10">
+        <v>14</v>
+      </c>
+      <c r="CV33" s="12">
+        <v>84748.571428559997</v>
+      </c>
+      <c r="CW33" s="10">
+        <f t="shared" si="29"/>
+        <v>-11</v>
+      </c>
+      <c r="CX33" s="12">
+        <f t="shared" si="30"/>
+        <v>-87870.476190480011</v>
+      </c>
+      <c r="CY33" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.50904275862073423</v>
+      </c>
     </row>
     <row r="34" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A34" s="14"/>
@@ -9190,10 +9688,27 @@
         <v>0.18561278863225966</v>
       </c>
       <c r="CS34" s="14"/>
-      <c r="CT34" s="13"/>
-      <c r="CV34" s="12"/>
-      <c r="CX34" s="12"/>
-      <c r="CY34" s="11"/>
+      <c r="CT34" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU34" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV34" s="12">
+        <v>124952.38095235001</v>
+      </c>
+      <c r="CW34" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX34" s="12">
+        <f t="shared" si="30"/>
+        <v>-2190.4761904700135</v>
+      </c>
+      <c r="CY34" s="11">
+        <f t="shared" si="31"/>
+        <v>-1.7228464419432103E-2</v>
+      </c>
     </row>
     <row r="35" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A35" s="14"/>
@@ -9426,10 +9941,27 @@
         <v>-1</v>
       </c>
       <c r="CS35" s="14"/>
-      <c r="CT35" s="13"/>
-      <c r="CV35" s="12"/>
-      <c r="CX35" s="12"/>
-      <c r="CY35" s="11"/>
+      <c r="CT35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="CU35" s="10">
+        <v>2</v>
+      </c>
+      <c r="CV35" s="12">
+        <v>5314.2857142800003</v>
+      </c>
+      <c r="CW35" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX35" s="12">
+        <f t="shared" si="30"/>
+        <v>5314.2857142800003</v>
+      </c>
+      <c r="CY35" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="36" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A36" s="14"/>
@@ -9677,10 +10209,22 @@
         <v>-3.5377358490566037E-2</v>
       </c>
       <c r="CS36" s="14"/>
-      <c r="CT36" s="13"/>
+      <c r="CT36" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV36" s="12"/>
-      <c r="CX36" s="12"/>
-      <c r="CY36" s="11"/>
+      <c r="CW36" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX36" s="12">
+        <f t="shared" si="30"/>
+        <v>-8180</v>
+      </c>
+      <c r="CY36" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="37" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A37" s="14"/>
@@ -9877,7 +10421,7 @@
         <v>26147.619047609998</v>
       </c>
       <c r="BY37" s="10">
-        <f t="shared" ref="BY37:BY65" si="29">BW37-BO37</f>
+        <f t="shared" ref="BY37:BY65" si="32">BW37-BO37</f>
         <v>1</v>
       </c>
       <c r="BZ37" s="12">
@@ -9933,10 +10477,22 @@
         <v>-0.44292206547357615</v>
       </c>
       <c r="CS37" s="14"/>
-      <c r="CT37" s="13"/>
+      <c r="CT37" s="13" t="s">
+        <v>4</v>
+      </c>
       <c r="CV37" s="12"/>
-      <c r="CX37" s="12"/>
-      <c r="CY37" s="11"/>
+      <c r="CW37" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX37" s="12">
+        <f t="shared" si="30"/>
+        <v>-47047.619047610002</v>
+      </c>
+      <c r="CY37" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="38" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A38" s="14"/>
@@ -10138,7 +10694,7 @@
         <v>154190.47619044999</v>
       </c>
       <c r="BY38" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ38" s="12">
@@ -10194,10 +10750,27 @@
         <v>0.36555731642900741</v>
       </c>
       <c r="CS38" s="14"/>
-      <c r="CT38" s="13"/>
-      <c r="CV38" s="12"/>
-      <c r="CX38" s="12"/>
-      <c r="CY38" s="11"/>
+      <c r="CT38" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU38" s="10">
+        <v>7</v>
+      </c>
+      <c r="CV38" s="12">
+        <v>145523.80952379</v>
+      </c>
+      <c r="CW38" s="10">
+        <f t="shared" si="29"/>
+        <v>-7</v>
+      </c>
+      <c r="CX38" s="12">
+        <f t="shared" si="30"/>
+        <v>-100666.66666664995</v>
+      </c>
+      <c r="CY38" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.40889748549322247</v>
+      </c>
     </row>
     <row r="39" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A39" s="14"/>
@@ -10399,7 +10972,7 @@
         <v>379739.04761903</v>
       </c>
       <c r="BY39" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>4</v>
       </c>
       <c r="BZ39" s="12">
@@ -10455,10 +11028,27 @@
         <v>6.7015706806084069E-3</v>
       </c>
       <c r="CS39" s="14"/>
-      <c r="CT39" s="13"/>
-      <c r="CV39" s="12"/>
-      <c r="CX39" s="12"/>
-      <c r="CY39" s="11"/>
+      <c r="CT39" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU39" s="10">
+        <v>21</v>
+      </c>
+      <c r="CV39" s="12">
+        <v>737020.95238092006</v>
+      </c>
+      <c r="CW39" s="10">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="CX39" s="12">
+        <f t="shared" si="30"/>
+        <v>279211.42857142014</v>
+      </c>
+      <c r="CY39" s="11">
+        <f t="shared" si="31"/>
+        <v>0.60988558352404088</v>
+      </c>
     </row>
     <row r="40" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -10661,7 +11251,7 @@
         <v>1201897.14285643</v>
       </c>
       <c r="BY40" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ40" s="28">
@@ -10716,13 +11306,28 @@
         <f t="shared" si="28"/>
         <v>7.7717724477374628E-2</v>
       </c>
-      <c r="CS40" s="9"/>
+      <c r="CS40" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="CT40" s="9"/>
-      <c r="CU40" s="8"/>
-      <c r="CV40" s="7"/>
-      <c r="CW40" s="27"/>
-      <c r="CX40" s="28"/>
-      <c r="CY40" s="29"/>
+      <c r="CU40" s="8">
+        <v>221</v>
+      </c>
+      <c r="CV40" s="7">
+        <v>1257073.3333327202</v>
+      </c>
+      <c r="CW40" s="27">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="CX40" s="28">
+        <f t="shared" si="30"/>
+        <v>53265.714285630267</v>
+      </c>
+      <c r="CY40" s="29">
+        <f t="shared" si="31"/>
+        <v>4.4247696594406291E-2</v>
+      </c>
     </row>
     <row r="41" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A41" s="14">
@@ -10924,7 +11529,7 @@
       </c>
       <c r="BX41" s="33"/>
       <c r="BY41" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-543</v>
       </c>
       <c r="BZ41" s="12">
@@ -10979,13 +11584,28 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS41" s="14"/>
-      <c r="CT41" s="32"/>
-      <c r="CU41" s="15"/>
+      <c r="CS41" s="14">
+        <v>81</v>
+      </c>
+      <c r="CT41" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="CU41" s="15">
+        <v>1229</v>
+      </c>
       <c r="CV41" s="33"/>
-      <c r="CW41" s="10"/>
-      <c r="CX41" s="12"/>
-      <c r="CY41" s="11"/>
+      <c r="CW41" s="10">
+        <f t="shared" si="29"/>
+        <v>-94</v>
+      </c>
+      <c r="CX41" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY41" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="42" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A42" s="14"/>
@@ -11167,7 +11787,7 @@
       </c>
       <c r="BX42" s="33"/>
       <c r="BY42" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-4</v>
       </c>
       <c r="BZ42" s="12">
@@ -11219,12 +11839,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS42" s="14"/>
-      <c r="CT42" s="32"/>
+      <c r="CT42" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU42" s="15"/>
       <c r="CV42" s="33"/>
-      <c r="CW42" s="10"/>
-      <c r="CX42" s="12"/>
-      <c r="CY42" s="11"/>
+      <c r="CW42" s="10">
+        <f t="shared" si="29"/>
+        <v>-6</v>
+      </c>
+      <c r="CX42" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY42" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="43" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A43" s="14"/>
@@ -11426,7 +12057,7 @@
         <v>82412.380952079999</v>
       </c>
       <c r="BY43" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-55</v>
       </c>
       <c r="BZ43" s="12">
@@ -11482,10 +12113,27 @@
         <v>4.4907046644309105E-2</v>
       </c>
       <c r="CS43" s="14"/>
-      <c r="CT43" s="13"/>
-      <c r="CV43" s="12"/>
-      <c r="CX43" s="12"/>
-      <c r="CY43" s="11"/>
+      <c r="CT43" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU43" s="10">
+        <v>96</v>
+      </c>
+      <c r="CV43" s="12">
+        <v>85103.809523370001</v>
+      </c>
+      <c r="CW43" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX43" s="12">
+        <f t="shared" si="30"/>
+        <v>-4290.4761905000341</v>
+      </c>
+      <c r="CY43" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.7994971448542402E-2</v>
+      </c>
     </row>
     <row r="44" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A44" s="14"/>
@@ -11687,7 +12335,7 @@
         <v>90152.380952249994</v>
       </c>
       <c r="BY44" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>3</v>
       </c>
       <c r="BZ44" s="12">
@@ -11743,10 +12391,27 @@
         <v>-0.25631621841911384</v>
       </c>
       <c r="CS44" s="14"/>
-      <c r="CT44" s="13"/>
-      <c r="CV44" s="12"/>
-      <c r="CX44" s="12"/>
-      <c r="CY44" s="11"/>
+      <c r="CT44" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU44" s="10">
+        <v>61</v>
+      </c>
+      <c r="CV44" s="12">
+        <v>57428.571428510018</v>
+      </c>
+      <c r="CW44" s="10">
+        <f t="shared" si="29"/>
+        <v>-14</v>
+      </c>
+      <c r="CX44" s="12">
+        <f t="shared" si="30"/>
+        <v>-8619.0476190099798</v>
+      </c>
+      <c r="CY44" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.13049747656775848</v>
+      </c>
     </row>
     <row r="45" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A45" s="14"/>
@@ -11948,7 +12613,7 @@
         <v>92723.80952380001</v>
       </c>
       <c r="BY45" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="BZ45" s="12">
@@ -12004,10 +12669,27 @@
         <v>-0.54991257786034653</v>
       </c>
       <c r="CS45" s="14"/>
-      <c r="CT45" s="13"/>
-      <c r="CV45" s="12"/>
-      <c r="CX45" s="12"/>
-      <c r="CY45" s="11"/>
+      <c r="CT45" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU45" s="10">
+        <v>12</v>
+      </c>
+      <c r="CV45" s="12">
+        <v>84647.619047610002</v>
+      </c>
+      <c r="CW45" s="10">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="CX45" s="12">
+        <f t="shared" si="30"/>
+        <v>21885.714285710004</v>
+      </c>
+      <c r="CY45" s="11">
+        <f t="shared" si="31"/>
+        <v>0.34871016691953338</v>
+      </c>
     </row>
     <row r="46" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A46" s="14"/>
@@ -12209,7 +12891,7 @@
         <v>111428.57142854</v>
       </c>
       <c r="BY46" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>2</v>
       </c>
       <c r="BZ46" s="12">
@@ -12265,10 +12947,27 @@
         <v>-0.26202661207776362</v>
       </c>
       <c r="CS46" s="14"/>
-      <c r="CT46" s="13"/>
-      <c r="CV46" s="12"/>
-      <c r="CX46" s="12"/>
-      <c r="CY46" s="11"/>
+      <c r="CT46" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU46" s="10">
+        <v>13</v>
+      </c>
+      <c r="CV46" s="12">
+        <v>130190.47619044001</v>
+      </c>
+      <c r="CW46" s="10">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="CX46" s="12">
+        <f t="shared" si="30"/>
+        <v>-7142.8571428699943</v>
+      </c>
+      <c r="CY46" s="11">
+        <f t="shared" si="31"/>
+        <v>-5.2011095700518505E-2</v>
+      </c>
     </row>
     <row r="47" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A47" s="14"/>
@@ -12450,7 +13149,7 @@
       </c>
       <c r="BX47" s="12"/>
       <c r="BY47" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ47" s="12">
@@ -12496,10 +13195,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS47" s="14"/>
-      <c r="CT47" s="13"/>
+      <c r="CT47" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CV47" s="12"/>
-      <c r="CX47" s="12"/>
-      <c r="CY47" s="11"/>
+      <c r="CW47" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX47" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY47" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="48" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A48" s="14"/>
@@ -12701,7 +13412,7 @@
         <v>6290</v>
       </c>
       <c r="BY48" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ48" s="12">
@@ -12757,10 +13468,22 @@
         <v>0.31729518855656696</v>
       </c>
       <c r="CS48" s="14"/>
-      <c r="CT48" s="13"/>
+      <c r="CT48" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV48" s="12"/>
-      <c r="CX48" s="12"/>
-      <c r="CY48" s="11"/>
+      <c r="CW48" s="10">
+        <f t="shared" si="29"/>
+        <v>-4</v>
+      </c>
+      <c r="CX48" s="12">
+        <f t="shared" si="30"/>
+        <v>-20260</v>
+      </c>
+      <c r="CY48" s="11">
+        <f t="shared" si="31"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="49" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A49" s="14"/>
@@ -12962,7 +13685,7 @@
         <v>52168.571428559997</v>
       </c>
       <c r="BY49" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="BZ49" s="12">
@@ -13013,10 +13736,27 @@
         <v>-1</v>
       </c>
       <c r="CS49" s="14"/>
-      <c r="CT49" s="13"/>
-      <c r="CV49" s="12"/>
-      <c r="CX49" s="12"/>
-      <c r="CY49" s="11"/>
+      <c r="CT49" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU49" s="10">
+        <v>1</v>
+      </c>
+      <c r="CV49" s="12">
+        <v>25619.04761904</v>
+      </c>
+      <c r="CW49" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX49" s="12">
+        <f t="shared" si="30"/>
+        <v>25619.04761904</v>
+      </c>
+      <c r="CY49" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="50" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A50" s="14"/>
@@ -13218,7 +13958,7 @@
         <v>166761.90476188</v>
       </c>
       <c r="BY50" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-6</v>
       </c>
       <c r="BZ50" s="12">
@@ -13274,10 +14014,27 @@
         <v>-0.56665160415729177</v>
       </c>
       <c r="CS50" s="14"/>
-      <c r="CT50" s="13"/>
-      <c r="CV50" s="12"/>
-      <c r="CX50" s="12"/>
-      <c r="CY50" s="11"/>
+      <c r="CT50" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU50" s="10">
+        <v>11</v>
+      </c>
+      <c r="CV50" s="12">
+        <v>191142.85714283001</v>
+      </c>
+      <c r="CW50" s="10">
+        <f t="shared" si="29"/>
+        <v>4</v>
+      </c>
+      <c r="CX50" s="12">
+        <f t="shared" si="30"/>
+        <v>99809.523809520004</v>
+      </c>
+      <c r="CY50" s="11">
+        <f t="shared" si="31"/>
+        <v>1.0928050052140019</v>
+      </c>
     </row>
     <row r="51" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A51" s="14"/>
@@ -13479,7 +14236,7 @@
         <v>370285.7142857</v>
       </c>
       <c r="BY51" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-12</v>
       </c>
       <c r="BZ51" s="12">
@@ -13535,10 +14292,27 @@
         <v>-0.12698139214333357</v>
       </c>
       <c r="CS51" s="14"/>
-      <c r="CT51" s="13"/>
-      <c r="CV51" s="12"/>
-      <c r="CX51" s="12"/>
-      <c r="CY51" s="11"/>
+      <c r="CT51" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU51" s="10">
+        <v>24</v>
+      </c>
+      <c r="CV51" s="12">
+        <v>868190.47619043</v>
+      </c>
+      <c r="CW51" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX51" s="12">
+        <f t="shared" si="30"/>
+        <v>-96952.380952410051</v>
+      </c>
+      <c r="CY51" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.10045391750545921</v>
+      </c>
     </row>
     <row r="52" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A52" s="9" t="s">
@@ -13741,7 +14515,7 @@
         <v>972223.33333280997</v>
       </c>
       <c r="BY52" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-72</v>
       </c>
       <c r="BZ52" s="28">
@@ -13796,13 +14570,28 @@
         <f t="shared" si="28"/>
         <v>-0.30440137946095486</v>
       </c>
-      <c r="CS52" s="9"/>
+      <c r="CS52" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="CT52" s="9"/>
-      <c r="CU52" s="8"/>
-      <c r="CV52" s="7"/>
-      <c r="CW52" s="27"/>
-      <c r="CX52" s="28"/>
-      <c r="CY52" s="29"/>
+      <c r="CU52" s="8">
+        <v>218</v>
+      </c>
+      <c r="CV52" s="7">
+        <v>1442322.85714223</v>
+      </c>
+      <c r="CW52" s="27">
+        <f t="shared" si="29"/>
+        <v>-10</v>
+      </c>
+      <c r="CX52" s="28">
+        <f t="shared" si="30"/>
+        <v>10049.523809480015</v>
+      </c>
+      <c r="CY52" s="29">
+        <f t="shared" si="31"/>
+        <v>7.016484616170173E-3</v>
+      </c>
     </row>
     <row r="53" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A53" s="14">
@@ -13976,7 +14765,7 @@
       <c r="BW53" s="15"/>
       <c r="BX53" s="33"/>
       <c r="BY53" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ53" s="12">
@@ -14027,13 +14816,26 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="CS53" s="14"/>
-      <c r="CT53" s="32"/>
+      <c r="CS53" s="14">
+        <v>84</v>
+      </c>
+      <c r="CT53" s="32" t="s">
+        <v>20</v>
+      </c>
       <c r="CU53" s="15"/>
       <c r="CV53" s="33"/>
-      <c r="CW53" s="10"/>
-      <c r="CX53" s="12"/>
-      <c r="CY53" s="11"/>
+      <c r="CW53" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX53" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY53" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="54" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A54" s="14"/>
@@ -14215,7 +15017,7 @@
       </c>
       <c r="BX54" s="33"/>
       <c r="BY54" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-3</v>
       </c>
       <c r="BZ54" s="12">
@@ -14267,12 +15069,23 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS54" s="14"/>
-      <c r="CT54" s="32"/>
+      <c r="CT54" s="32" t="s">
+        <v>21</v>
+      </c>
       <c r="CU54" s="15"/>
       <c r="CV54" s="33"/>
-      <c r="CW54" s="10"/>
-      <c r="CX54" s="12"/>
-      <c r="CY54" s="11"/>
+      <c r="CW54" s="10">
+        <f t="shared" si="29"/>
+        <v>-2</v>
+      </c>
+      <c r="CX54" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY54" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="55" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A55" s="14"/>
@@ -14474,7 +15287,7 @@
         <v>102147.61904713005</v>
       </c>
       <c r="BY55" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-32</v>
       </c>
       <c r="BZ55" s="12">
@@ -14530,10 +15343,27 @@
         <v>-0.33098276342556177</v>
       </c>
       <c r="CS55" s="14"/>
-      <c r="CT55" s="13"/>
-      <c r="CV55" s="12"/>
-      <c r="CX55" s="12"/>
-      <c r="CY55" s="11"/>
+      <c r="CT55" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU55" s="10">
+        <v>86</v>
+      </c>
+      <c r="CV55" s="12">
+        <v>90476.190475840005</v>
+      </c>
+      <c r="CW55" s="10">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="CX55" s="12">
+        <f t="shared" si="30"/>
+        <v>15029.52380948003</v>
+      </c>
+      <c r="CY55" s="11">
+        <f t="shared" si="31"/>
+        <v>0.1992072608846133</v>
+      </c>
     </row>
     <row r="56" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A56" s="14"/>
@@ -14735,7 +15565,7 @@
         <v>100334.28571419</v>
       </c>
       <c r="BY56" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-15</v>
       </c>
       <c r="BZ56" s="12">
@@ -14791,10 +15621,27 @@
         <v>-0.12004405286396851</v>
       </c>
       <c r="CS56" s="14"/>
-      <c r="CT56" s="13"/>
-      <c r="CV56" s="12"/>
-      <c r="CX56" s="12"/>
-      <c r="CY56" s="11"/>
+      <c r="CT56" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU56" s="10">
+        <v>78</v>
+      </c>
+      <c r="CV56" s="12">
+        <v>79542.857142770008</v>
+      </c>
+      <c r="CW56" s="10">
+        <f t="shared" si="29"/>
+        <v>19</v>
+      </c>
+      <c r="CX56" s="12">
+        <f t="shared" si="30"/>
+        <v>11057.142857160012</v>
+      </c>
+      <c r="CY56" s="11">
+        <f t="shared" si="31"/>
+        <v>0.16145181476895692</v>
+      </c>
     </row>
     <row r="57" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A57" s="14"/>
@@ -14996,7 +15843,7 @@
         <v>131247.61904760002</v>
       </c>
       <c r="BY57" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-7</v>
       </c>
       <c r="BZ57" s="12">
@@ -15052,10 +15899,27 @@
         <v>-0.5663554715197523</v>
       </c>
       <c r="CS57" s="14"/>
-      <c r="CT57" s="13"/>
-      <c r="CV57" s="12"/>
-      <c r="CX57" s="12"/>
-      <c r="CY57" s="11"/>
+      <c r="CT57" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU57" s="10">
+        <v>10</v>
+      </c>
+      <c r="CV57" s="12">
+        <v>67047.619047610002</v>
+      </c>
+      <c r="CW57" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX57" s="12">
+        <f t="shared" si="30"/>
+        <v>-2847.619047619999</v>
+      </c>
+      <c r="CY57" s="11">
+        <f t="shared" si="31"/>
+        <v>-4.0741245401299156E-2</v>
+      </c>
     </row>
     <row r="58" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A58" s="14"/>
@@ -15257,7 +16121,7 @@
         <v>42476.190476169999</v>
       </c>
       <c r="BY58" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-11</v>
       </c>
       <c r="BZ58" s="12">
@@ -15313,10 +16177,27 @@
         <v>-7.6998050682191982E-2</v>
       </c>
       <c r="CS58" s="14"/>
-      <c r="CT58" s="13"/>
-      <c r="CV58" s="12"/>
-      <c r="CX58" s="12"/>
-      <c r="CY58" s="11"/>
+      <c r="CT58" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="CU58" s="10">
+        <v>8</v>
+      </c>
+      <c r="CV58" s="12">
+        <v>98285.714285690003</v>
+      </c>
+      <c r="CW58" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX58" s="12">
+        <f t="shared" si="30"/>
+        <v>8095.2380952400126</v>
+      </c>
+      <c r="CY58" s="11">
+        <f t="shared" si="31"/>
+        <v>8.9757127771958628E-2</v>
+      </c>
     </row>
     <row r="59" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A59" s="14"/>
@@ -15493,7 +16374,7 @@
       </c>
       <c r="BX59" s="12"/>
       <c r="BY59" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="BZ59" s="12">
@@ -15539,10 +16420,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="CS59" s="14"/>
-      <c r="CT59" s="13"/>
+      <c r="CT59" s="13" t="s">
+        <v>6</v>
+      </c>
       <c r="CV59" s="12"/>
-      <c r="CX59" s="12"/>
-      <c r="CY59" s="11"/>
+      <c r="CW59" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX59" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY59" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="60" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A60" s="14"/>
@@ -15739,7 +16632,7 @@
         <v>6290</v>
       </c>
       <c r="BY60" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="BZ60" s="12">
@@ -15790,10 +16683,22 @@
         <v>-1</v>
       </c>
       <c r="CS60" s="14"/>
-      <c r="CT60" s="13"/>
+      <c r="CT60" s="13" t="s">
+        <v>5</v>
+      </c>
       <c r="CV60" s="12"/>
-      <c r="CX60" s="12"/>
-      <c r="CY60" s="11"/>
+      <c r="CW60" s="10">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="CX60" s="12">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="CY60" s="11" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="61" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A61" s="14"/>
@@ -15995,7 +16900,7 @@
         <v>83142.857142840003</v>
       </c>
       <c r="BY61" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-3</v>
       </c>
       <c r="BZ61" s="12">
@@ -16051,10 +16956,27 @@
         <v>-0.69801462904915956</v>
       </c>
       <c r="CS61" s="14"/>
-      <c r="CT61" s="13"/>
-      <c r="CV61" s="12"/>
-      <c r="CX61" s="12"/>
-      <c r="CY61" s="11"/>
+      <c r="CT61" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="CU61" s="10">
+        <v>2</v>
+      </c>
+      <c r="CV61" s="12">
+        <v>96952.380952370004</v>
+      </c>
+      <c r="CW61" s="10">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="CX61" s="12">
+        <f t="shared" si="30"/>
+        <v>69428.571428570009</v>
+      </c>
+      <c r="CY61" s="11">
+        <f t="shared" si="31"/>
+        <v>2.5224913494817902</v>
+      </c>
     </row>
     <row r="62" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A62" s="14"/>
@@ -16256,7 +17178,7 @@
         <v>217142.85714284002</v>
       </c>
       <c r="BY62" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-6</v>
       </c>
       <c r="BZ62" s="12">
@@ -16312,10 +17234,27 @@
         <v>-0.76013006503255576</v>
       </c>
       <c r="CS62" s="14"/>
-      <c r="CT62" s="13"/>
-      <c r="CV62" s="12"/>
-      <c r="CX62" s="12"/>
-      <c r="CY62" s="11"/>
+      <c r="CT62" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="CU62" s="10">
+        <v>6</v>
+      </c>
+      <c r="CV62" s="12">
+        <v>83974.285714259997</v>
+      </c>
+      <c r="CW62" s="10">
+        <f t="shared" si="29"/>
+        <v>-1</v>
+      </c>
+      <c r="CX62" s="12">
+        <f t="shared" si="30"/>
+        <v>-7359.0476190500049</v>
+      </c>
+      <c r="CY62" s="11">
+        <f t="shared" si="31"/>
+        <v>-8.0573514077210417E-2</v>
+      </c>
     </row>
     <row r="63" spans="1:103" s="10" customFormat="1" ht="20" customHeight="1">
       <c r="A63" s="14"/>
@@ -16517,7 +17456,7 @@
         <v>456340.95238093007</v>
       </c>
       <c r="BY63" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-9</v>
       </c>
       <c r="BZ63" s="12">
@@ -16573,10 +17512,27 @@
         <v>0.12483745123538241</v>
       </c>
       <c r="CS63" s="14"/>
-      <c r="CT63" s="13"/>
-      <c r="CV63" s="12"/>
-      <c r="CX63" s="12"/>
-      <c r="CY63" s="11"/>
+      <c r="CT63" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CU63" s="10">
+        <v>15</v>
+      </c>
+      <c r="CV63" s="12">
+        <v>526812.38095234998</v>
+      </c>
+      <c r="CW63" s="10">
+        <f t="shared" si="29"/>
+        <v>-5</v>
+      </c>
+      <c r="CX63" s="12">
+        <f t="shared" si="30"/>
+        <v>-132235.23809524009</v>
+      </c>
+      <c r="CY63" s="11">
+        <f t="shared" si="31"/>
+        <v>-0.20064595375723729</v>
+      </c>
     </row>
     <row r="64" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -16779,7 +17735,7 @@
         <v>1139122.3809517003</v>
       </c>
       <c r="BY64" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-82</v>
       </c>
       <c r="BZ64" s="28">
@@ -16834,13 +17790,28 @@
         <f t="shared" si="28"/>
         <v>-0.28637091758853916</v>
       </c>
-      <c r="CS64" s="9"/>
+      <c r="CS64" s="9" t="s">
+        <v>1</v>
+      </c>
       <c r="CT64" s="9"/>
-      <c r="CU64" s="8"/>
-      <c r="CV64" s="7"/>
-      <c r="CW64" s="27"/>
-      <c r="CX64" s="28"/>
-      <c r="CY64" s="29"/>
+      <c r="CU64" s="8">
+        <v>205</v>
+      </c>
+      <c r="CV64" s="7">
+        <v>1043091.4285708901</v>
+      </c>
+      <c r="CW64" s="27">
+        <f t="shared" si="29"/>
+        <v>24</v>
+      </c>
+      <c r="CX64" s="28">
+        <f t="shared" si="30"/>
+        <v>-38831.42857146007</v>
+      </c>
+      <c r="CY64" s="29">
+        <f t="shared" si="31"/>
+        <v>-3.5891125060454256E-2</v>
+      </c>
     </row>
     <row r="65" spans="1:103" s="1" customFormat="1" ht="20" customHeight="1">
       <c r="A65" s="4" t="s">
@@ -17043,7 +18014,7 @@
         <v>11122184.761900868</v>
       </c>
       <c r="BY65" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>-669</v>
       </c>
       <c r="BZ65" s="5">
@@ -17098,13 +18069,28 @@
         <f t="shared" si="28"/>
         <v>-0.10400049951712022</v>
       </c>
-      <c r="CS65" s="4"/>
+      <c r="CS65" s="4" t="s">
+        <v>0</v>
+      </c>
       <c r="CT65" s="4"/>
-      <c r="CU65" s="3"/>
-      <c r="CV65" s="2"/>
-      <c r="CW65" s="6"/>
-      <c r="CX65" s="5"/>
-      <c r="CY65" s="30"/>
+      <c r="CU65" s="3">
+        <v>2238</v>
+      </c>
+      <c r="CV65" s="2">
+        <v>27538164.761900596</v>
+      </c>
+      <c r="CW65" s="6">
+        <f t="shared" si="29"/>
+        <v>178</v>
+      </c>
+      <c r="CX65" s="5">
+        <f t="shared" si="30"/>
+        <v>8398197.6190473996</v>
+      </c>
+      <c r="CY65" s="30">
+        <f t="shared" si="31"/>
+        <v>0.43877805830942923</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -17114,7 +18100,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="110" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
+          <x14:cfRule type="containsText" priority="111" operator="containsText" id="{84E91190-11E8-AE4A-9A8E-E0B241655290}">
             <xm:f>NOT(ISERROR(SEARCH("-",E7)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17126,7 +18112,7 @@
           <xm:sqref>E7:G65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
+          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{CCFCC0A6-CB12-AB49-93FE-0A85BBD26278}">
             <xm:f>NOT(ISERROR(SEARCH("-",M5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17138,7 +18124,7 @@
           <xm:sqref>M5:O65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
+          <x14:cfRule type="containsText" priority="13" operator="containsText" id="{77E3898A-1BFA-D640-9BA9-3433EFE4A95F}">
             <xm:f>NOT(ISERROR(SEARCH("-",U5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17150,7 +18136,7 @@
           <xm:sqref>U5:W65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
+          <x14:cfRule type="containsText" priority="12" operator="containsText" id="{D9706009-D5AD-2741-B804-EFED1C726C5E}">
             <xm:f>NOT(ISERROR(SEARCH("-",AC5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17162,7 +18148,7 @@
           <xm:sqref>AC5:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{0ED7C4E6-BDE3-3246-BC08-84A539C7A360}">
             <xm:f>NOT(ISERROR(SEARCH("-",AJ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17174,7 +18160,7 @@
           <xm:sqref>AJ5:AM65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
+          <x14:cfRule type="containsText" priority="9" operator="containsText" id="{6F25B2E1-166C-A14E-8434-CB8394590228}">
             <xm:f>NOT(ISERROR(SEARCH("-",AS5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17186,7 +18172,7 @@
           <xm:sqref>AS5:AU65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
+          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{B91A5596-3F8E-6648-95BA-8781A9ECC29E}">
             <xm:f>NOT(ISERROR(SEARCH("-",BA5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17198,7 +18184,7 @@
           <xm:sqref>BA5:BC65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="6" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
+          <x14:cfRule type="containsText" priority="7" operator="containsText" id="{E93B6814-05C6-8F46-A383-0AA3B037BA87}">
             <xm:f>NOT(ISERROR(SEARCH("-",BI5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17210,7 +18196,7 @@
           <xm:sqref>BI5:BK65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
+          <x14:cfRule type="containsText" priority="5" operator="containsText" id="{C5C117FA-A310-C347-B988-7B736BE0F8CB}">
             <xm:f>NOT(ISERROR(SEARCH("-",BQ5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17222,7 +18208,7 @@
           <xm:sqref>BQ5:BS65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{8AD91545-A880-0646-B88D-4021F4CD6A07}">
             <xm:f>NOT(ISERROR(SEARCH("-",BY5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17234,7 +18220,7 @@
           <xm:sqref>BY5:CA65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{6A1FAD57-8B56-AD43-BC86-FE7B8B27DAC3}">
             <xm:f>NOT(ISERROR(SEARCH("-",CG5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17246,7 +18232,7 @@
           <xm:sqref>CG5:CI65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{F04093BB-F5FD-F043-B0A6-2D2AB47A2695}">
             <xm:f>NOT(ISERROR(SEARCH("-",CO5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -17258,7 +18244,7 @@
           <xm:sqref>CO5:CQ65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="14" operator="containsText" id="{4126E041-CCDA-FB44-8F91-ACB733D36FB3}">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{3F8775C0-1F6C-794D-A1A7-74CBBEDF3DB8}">
             <xm:f>NOT(ISERROR(SEARCH("-",CW5)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FB02E-9673-9447-A447-22229F527E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9B78C3-8F78-B243-AAD2-5B893325A92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="1520" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
+    <workbookView xWindow="5640" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
   <sheets>
     <sheet name="26Q2" sheetId="2" r:id="rId1"/>
@@ -575,12 +575,7 @@
     <cellStyle name="一般 2" xfId="2" xr:uid="{0CB5398D-811F-454E-A670-53B654D1D081}"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>

--- a/data/FY26Q2.xlsx
+++ b/data/FY26Q2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/morio/GitHub/QBR/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9B78C3-8F78-B243-AAD2-5B893325A92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DF30A3-16D2-5140-A737-64237F2E0D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5640" yWindow="700" windowWidth="19540" windowHeight="20180" xr2:uid="{021FACC0-6583-9245-81B4-0A7BE4D712CF}"/>
   </bookViews>
@@ -2006,10 +2006,13 @@
       <c r="CT6" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="CU6" s="15">
+        <v>18</v>
+      </c>
       <c r="CV6" s="33"/>
       <c r="CW6" s="10">
         <f t="shared" si="29"/>
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="CX6" s="12">
         <f t="shared" si="30"/>
@@ -5284,11 +5287,13 @@
       <c r="CT18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU18" s="15"/>
+      <c r="CU18" s="15">
+        <v>15</v>
+      </c>
       <c r="CV18" s="33"/>
       <c r="CW18" s="10">
         <f t="shared" si="29"/>
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="CX18" s="12">
         <f t="shared" si="30"/>
@@ -8578,11 +8583,13 @@
       <c r="CT30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU30" s="15"/>
+      <c r="CU30" s="15">
+        <v>4</v>
+      </c>
       <c r="CV30" s="33"/>
       <c r="CW30" s="10">
         <f t="shared" si="29"/>
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="CX30" s="12">
         <f t="shared" si="30"/>
@@ -11837,11 +11844,13 @@
       <c r="CT42" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU42" s="15"/>
+      <c r="CU42" s="15">
+        <v>4</v>
+      </c>
       <c r="CV42" s="33"/>
       <c r="CW42" s="10">
         <f t="shared" si="29"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="CX42" s="12">
         <f t="shared" si="30"/>
@@ -15067,11 +15076,13 @@
       <c r="CT54" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="CU54" s="15"/>
+      <c r="CU54" s="15">
+        <v>1</v>
+      </c>
       <c r="CV54" s="33"/>
       <c r="CW54" s="10">
         <f t="shared" si="29"/>
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="CX54" s="12">
         <f t="shared" si="30"/>
